--- a/MaxImporta_Modelos_Importacao.xlsx
+++ b/MaxImporta_Modelos_Importacao.xlsx
@@ -600,35 +600,41 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Descrição do Produto</t>
+          <t>Descrição do Produto
+(máx. 100 caracteres)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Cód. CST2
-(ex: 00,10,20, 60)</t>
+(ex: 00,10,20, 60)
+(máx. 2 caracteres)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Código Interno
-do Produto</t>
+do Produto
+(máx. 50 caracteres)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Unidade
-(ex: PC, KG, CX)</t>
+(ex: PC, KG, CX)
+(máx. 10 caracteres)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Código NCM</t>
+          <t>Código NCM
+(máx. 10 caracteres)</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Aplicação</t>
+          <t>Aplicação
+(texto longo, sem limite)</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -664,7 +670,8 @@
       <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Tipo
-P=Produto  S=Serviço</t>
+P=Produto  S=Serviço
+(máx. 1 caractere)</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -675,7 +682,8 @@
       </c>
       <c r="O2" s="11" t="inlineStr">
         <is>
-          <t>Cód. CSOSN (ex: 101,102,500)</t>
+          <t>Cód. CSOSN (ex: 101,102,500)
+(máx. 3 caracteres)</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
@@ -704,12 +712,14 @@
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>Localizador</t>
+          <t>Localizador
+(máx. 20 caracteres)</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>Prateleira</t>
+          <t>Prateleira
+(máx. 20 caracteres)</t>
         </is>
       </c>
       <c r="V2" s="3" t="inlineStr">
@@ -721,37 +731,43 @@
       <c r="W2" s="3" t="inlineStr">
         <is>
           <t>Classe do Produto
-(auto-criada)</t>
+(auto-criada)
+(máx. 50 caracteres)</t>
         </is>
       </c>
       <c r="X2" s="3" t="inlineStr">
         <is>
           <t>Código CEST
-(lookup proCEST)</t>
+(lookup proCEST)
+(máx. 10 caracteres)</t>
         </is>
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
           <t>Nome do Fabricante
-(auto-criado)</t>
+(auto-criado)
+(máx. 50 caracteres)</t>
         </is>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
           <t>Grupo do Produto
-(auto-criado)</t>
+(auto-criado)
+(máx. 50 caracteres)</t>
         </is>
       </c>
       <c r="AA2" s="3" t="inlineStr">
         <is>
           <t>SubGrupo do Produto
-(auto-criado)</t>
+(auto-criado)
+(máx. 50 caracteres)</t>
         </is>
       </c>
       <c r="AB2" s="3" t="inlineStr">
         <is>
           <t>Código EAN /
-Código de Barras</t>
+Código de Barras
+(máx. 20 caracteres)</t>
         </is>
       </c>
     </row>
@@ -6948,46 +6964,54 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>CPF / CNPJ
-(sem pontuação)</t>
+(sem pontuação)
+(máx. 20 caracteres)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Razão Social /
-Nome Completo</t>
+Nome Completo
+(máx. 50 caracteres)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Nome Fantasia</t>
+          <t>Nome Fantasia
+(máx. 50 caracteres)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>RG / Insc. Estadual
-(ou ISENTO)</t>
+(ou ISENTO)
+(máx. 20 caracteres)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Endereço de
-Faturamento</t>
+Faturamento
+(máx. 120 caracteres)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Número do
-Endereço</t>
+Endereço
+(máx. 10 caracteres)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Bairro</t>
+          <t>Bairro
+(máx. 70 caracteres)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Cidade</t>
+          <t>Cidade
+(máx. 30 caracteres)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -6999,13 +7023,15 @@
       <c r="K2" s="2" t="inlineStr">
         <is>
           <t>UF
-(ex: TO, SP, GO)</t>
+(ex: TO, SP, GO)
+(máx. 2 caracteres)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
           <t>CEP
-(8 dígitos, sem hífen)</t>
+(8 dígitos, sem hífen)
+(máx. 9 caracteres)</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -7022,12 +7048,14 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>E-mail</t>
+          <t>E-mail
+(máx. 254 caracteres)</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Telefone</t>
+          <t>Telefone
+(máx. 20 caracteres)</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
@@ -10972,13 +11000,15 @@
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>CPF / CNPJ
-(lookup cliente)</t>
+(lookup cliente)
+(máx. 20 caracteres)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Nome do Cliente
-no Lançamento</t>
+no Lançamento
+(máx. 50 caracteres)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -11014,23 +11044,27 @@
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Tipo Conta
-R=Receber  P=Pagar</t>
+R=Receber  P=Pagar
+(máx. 1 caractere)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Pago
-C=Quitado  N=Aberto  S=Parcial</t>
+C=Quitado  N=Aberto  S=Parcial
+(máx. 1 caractere)</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Nº do Documento</t>
+          <t>Nº do Documento
+(máx. 30 caracteres)</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Observação</t>
+          <t>Observação
+(máx. 1000 caracteres)</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -11041,7 +11075,8 @@
       <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Nosso Número
-(boleto)</t>
+(boleto)
+(máx. 30 caracteres)</t>
         </is>
       </c>
     </row>

--- a/MaxImporta_Modelos_Importacao.xlsx
+++ b/MaxImporta_Modelos_Importacao.xlsx
@@ -560,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB203"/>
+  <dimension ref="A1:AC203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="15" customWidth="1" style="10" min="1" max="1"/>
@@ -587,7 +587,7 @@
     <row r="1" ht="19.95" customHeight="1" s="10">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>MAX_IMPORTA  |  Produtos  (INSERT = sem proId / UPDATE = proId obrigatorio)</t>
+          <t>MAX_IMPORTA  |  Produtos    INSERT = sem proId (preencha os campos em vermelho)  |  UPDATE = so o proId e obrigatorio; celula VAZIA mantem o valor do banco</t>
         </is>
       </c>
     </row>
@@ -611,159 +611,166 @@
 (máx. 2 caracteres)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Cód. CST1 — origem
+(um dígito de 0 a 9)
+0 = Nacional</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Código Interno
 do Produto
 (máx. 50 caracteres)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Unidade
 (ex: PC, KG, CX)
 (máx. 10 caracteres)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Código NCM
 (máx. 10 caracteres)</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Aplicação
 (texto longo, sem limite)</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Balança
 0=Não  1=Sim</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Med. Venda
 (decimal 18,5)</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>Múltiplo
 (decimal 18,5)</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>Peso
 (decimal 18,5)</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Qtd. com Entrada
 (decimal 18,5)</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Tipo
 P=Produto  S=Serviço
 (máx. 1 caractere)</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>Preço Atacado
 (decimal 18,5)</t>
         </is>
       </c>
-      <c r="O2" s="11" t="inlineStr">
+      <c r="P2" s="11" t="inlineStr">
         <is>
           <t>Cód. CSOSN (ex: 101,102,500)
 (máx. 3 caracteres)</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>Custo
 (decimal 18,5)</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>Desativado
 -1=Sim  0=Não</t>
         </is>
       </c>
-      <c r="R2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>Estoque Atual
 (decimal 18,5)</t>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>Estoque Mínimo
 (decimal 18,5)</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>Localizador
 (máx. 20 caracteres)</t>
         </is>
       </c>
-      <c r="U2" s="3" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>Prateleira
 (máx. 20 caracteres)</t>
         </is>
       </c>
-      <c r="V2" s="3" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>Preço de Venda
 (decimal 18,5)</t>
         </is>
       </c>
-      <c r="W2" s="3" t="inlineStr">
+      <c r="X2" s="3" t="inlineStr">
         <is>
           <t>Classe do Produto
 (auto-criada)
 (máx. 50 caracteres)</t>
         </is>
       </c>
-      <c r="X2" s="3" t="inlineStr">
+      <c r="Y2" s="3" t="inlineStr">
         <is>
           <t>Código CEST
 (lookup proCEST)
 (máx. 10 caracteres)</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
+      <c r="Z2" s="3" t="inlineStr">
         <is>
           <t>Nome do Fabricante
 (auto-criado)
 (máx. 50 caracteres)</t>
         </is>
       </c>
-      <c r="Z2" s="3" t="inlineStr">
+      <c r="AA2" s="3" t="inlineStr">
         <is>
           <t>Grupo do Produto
 (auto-criado)
 (máx. 50 caracteres)</t>
         </is>
       </c>
-      <c r="AA2" s="3" t="inlineStr">
+      <c r="AB2" s="3" t="inlineStr">
         <is>
           <t>SubGrupo do Produto
 (auto-criado)
 (máx. 50 caracteres)</t>
         </is>
       </c>
-      <c r="AB2" s="3" t="inlineStr">
+      <c r="AC2" s="3" t="inlineStr">
         <is>
           <t>Código EAN /
 Código de Barras
@@ -787,127 +794,132 @@
           <t>proCodCst2</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>proCodCst1</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>proCodigo</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>proUn</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>ncmCodigoNCM</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>proAplicacao</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>proBalanca</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>proMedVenda</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>proMultiplo</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>proPeso</t>
         </is>
       </c>
-      <c r="L3" s="6" t="inlineStr">
+      <c r="M3" s="6" t="inlineStr">
         <is>
           <t>proQtdComEntrada</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="N3" s="6" t="inlineStr">
         <is>
           <t>proTipo</t>
         </is>
       </c>
-      <c r="N3" s="6" t="inlineStr">
+      <c r="O3" s="6" t="inlineStr">
         <is>
           <t>proAtacado</t>
         </is>
       </c>
-      <c r="O3" s="6" t="inlineStr">
+      <c r="P3" s="6" t="inlineStr">
         <is>
           <t>proCodCSOSN</t>
         </is>
       </c>
-      <c r="P3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="inlineStr">
         <is>
           <t>proCusto</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>proDesativaProd</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="S3" s="6" t="inlineStr">
         <is>
           <t>proEstoqueAtual</t>
         </is>
       </c>
-      <c r="S3" s="6" t="inlineStr">
+      <c r="T3" s="6" t="inlineStr">
         <is>
           <t>proEstoqueMin</t>
         </is>
       </c>
-      <c r="T3" s="6" t="inlineStr">
+      <c r="U3" s="6" t="inlineStr">
         <is>
           <t>proLocalizador</t>
         </is>
       </c>
-      <c r="U3" s="6" t="inlineStr">
+      <c r="V3" s="6" t="inlineStr">
         <is>
           <t>proPrateleira</t>
         </is>
       </c>
-      <c r="V3" s="6" t="inlineStr">
+      <c r="W3" s="6" t="inlineStr">
         <is>
           <t>proVenda</t>
         </is>
       </c>
-      <c r="W3" s="6" t="inlineStr">
+      <c r="X3" s="6" t="inlineStr">
         <is>
           <t>pclDescricao</t>
         </is>
       </c>
-      <c r="X3" s="6" t="inlineStr">
+      <c r="Y3" s="6" t="inlineStr">
         <is>
           <t>cesCodigo</t>
         </is>
       </c>
-      <c r="Y3" s="6" t="inlineStr">
+      <c r="Z3" s="6" t="inlineStr">
         <is>
           <t>fabNome</t>
         </is>
       </c>
-      <c r="Z3" s="6" t="inlineStr">
+      <c r="AA3" s="6" t="inlineStr">
         <is>
           <t>gdpNome</t>
         </is>
       </c>
-      <c r="AA3" s="6" t="inlineStr">
+      <c r="AB3" s="6" t="inlineStr">
         <is>
           <t>sgpNome</t>
         </is>
       </c>
-      <c r="AB3" s="6" t="inlineStr">
+      <c r="AC3" s="6" t="inlineStr">
         <is>
           <t>cdbCodigo</t>
         </is>
@@ -917,7 +929,6 @@
       <c r="A4" s="7" t="n"/>
       <c r="B4" s="7" t="n"/>
       <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
       <c r="E4" s="7" t="n"/>
       <c r="F4" s="7" t="n"/>
       <c r="G4" s="7" t="n"/>
@@ -942,12 +953,12 @@
       <c r="Z4" s="7" t="n"/>
       <c r="AA4" s="7" t="n"/>
       <c r="AB4" s="7" t="n"/>
+      <c r="AC4" s="7" t="n"/>
     </row>
     <row r="5" ht="16.05" customHeight="1" s="10">
       <c r="A5" s="8" t="n"/>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
       <c r="E5" s="8" t="n"/>
       <c r="F5" s="8" t="n"/>
       <c r="G5" s="8" t="n"/>
@@ -972,12 +983,12 @@
       <c r="Z5" s="8" t="n"/>
       <c r="AA5" s="8" t="n"/>
       <c r="AB5" s="8" t="n"/>
+      <c r="AC5" s="8" t="n"/>
     </row>
     <row r="6" ht="16.05" customHeight="1" s="10">
       <c r="A6" s="7" t="n"/>
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
@@ -1002,12 +1013,12 @@
       <c r="Z6" s="7" t="n"/>
       <c r="AA6" s="7" t="n"/>
       <c r="AB6" s="7" t="n"/>
+      <c r="AC6" s="7" t="n"/>
     </row>
     <row r="7" ht="16.05" customHeight="1" s="10">
       <c r="A7" s="8" t="n"/>
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -1032,12 +1043,12 @@
       <c r="Z7" s="8" t="n"/>
       <c r="AA7" s="8" t="n"/>
       <c r="AB7" s="8" t="n"/>
+      <c r="AC7" s="8" t="n"/>
     </row>
     <row r="8" ht="16.05" customHeight="1" s="10">
       <c r="A8" s="7" t="n"/>
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
@@ -1062,12 +1073,12 @@
       <c r="Z8" s="7" t="n"/>
       <c r="AA8" s="7" t="n"/>
       <c r="AB8" s="7" t="n"/>
+      <c r="AC8" s="7" t="n"/>
     </row>
     <row r="9" ht="16.05" customHeight="1" s="10">
       <c r="A9" s="8" t="n"/>
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -1092,12 +1103,12 @@
       <c r="Z9" s="8" t="n"/>
       <c r="AA9" s="8" t="n"/>
       <c r="AB9" s="8" t="n"/>
+      <c r="AC9" s="8" t="n"/>
     </row>
     <row r="10" ht="16.05" customHeight="1" s="10">
       <c r="A10" s="7" t="n"/>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
@@ -1122,12 +1133,12 @@
       <c r="Z10" s="7" t="n"/>
       <c r="AA10" s="7" t="n"/>
       <c r="AB10" s="7" t="n"/>
+      <c r="AC10" s="7" t="n"/>
     </row>
     <row r="11" ht="16.05" customHeight="1" s="10">
       <c r="A11" s="8" t="n"/>
       <c r="B11" s="8" t="n"/>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
@@ -1152,12 +1163,12 @@
       <c r="Z11" s="8" t="n"/>
       <c r="AA11" s="8" t="n"/>
       <c r="AB11" s="8" t="n"/>
+      <c r="AC11" s="8" t="n"/>
     </row>
     <row r="12" ht="16.05" customHeight="1" s="10">
       <c r="A12" s="7" t="n"/>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
@@ -1182,12 +1193,12 @@
       <c r="Z12" s="7" t="n"/>
       <c r="AA12" s="7" t="n"/>
       <c r="AB12" s="7" t="n"/>
+      <c r="AC12" s="7" t="n"/>
     </row>
     <row r="13" ht="16.05" customHeight="1" s="10">
       <c r="A13" s="8" t="n"/>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n"/>
@@ -1212,12 +1223,12 @@
       <c r="Z13" s="8" t="n"/>
       <c r="AA13" s="8" t="n"/>
       <c r="AB13" s="8" t="n"/>
+      <c r="AC13" s="8" t="n"/>
     </row>
     <row r="14" ht="16.05" customHeight="1" s="10">
       <c r="A14" s="7" t="n"/>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
@@ -1242,12 +1253,12 @@
       <c r="Z14" s="7" t="n"/>
       <c r="AA14" s="7" t="n"/>
       <c r="AB14" s="7" t="n"/>
+      <c r="AC14" s="7" t="n"/>
     </row>
     <row r="15" ht="16.05" customHeight="1" s="10">
       <c r="A15" s="8" t="n"/>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -1272,12 +1283,12 @@
       <c r="Z15" s="8" t="n"/>
       <c r="AA15" s="8" t="n"/>
       <c r="AB15" s="8" t="n"/>
+      <c r="AC15" s="8" t="n"/>
     </row>
     <row r="16" ht="16.05" customHeight="1" s="10">
       <c r="A16" s="7" t="n"/>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
@@ -1302,12 +1313,12 @@
       <c r="Z16" s="7" t="n"/>
       <c r="AA16" s="7" t="n"/>
       <c r="AB16" s="7" t="n"/>
+      <c r="AC16" s="7" t="n"/>
     </row>
     <row r="17" ht="16.05" customHeight="1" s="10">
       <c r="A17" s="8" t="n"/>
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
@@ -1332,12 +1343,12 @@
       <c r="Z17" s="8" t="n"/>
       <c r="AA17" s="8" t="n"/>
       <c r="AB17" s="8" t="n"/>
+      <c r="AC17" s="8" t="n"/>
     </row>
     <row r="18" ht="16.05" customHeight="1" s="10">
       <c r="A18" s="7" t="n"/>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
@@ -1362,12 +1373,12 @@
       <c r="Z18" s="7" t="n"/>
       <c r="AA18" s="7" t="n"/>
       <c r="AB18" s="7" t="n"/>
+      <c r="AC18" s="7" t="n"/>
     </row>
     <row r="19" ht="16.05" customHeight="1" s="10">
       <c r="A19" s="8" t="n"/>
       <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -1392,12 +1403,12 @@
       <c r="Z19" s="8" t="n"/>
       <c r="AA19" s="8" t="n"/>
       <c r="AB19" s="8" t="n"/>
+      <c r="AC19" s="8" t="n"/>
     </row>
     <row r="20" ht="16.05" customHeight="1" s="10">
       <c r="A20" s="7" t="n"/>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
@@ -1422,12 +1433,12 @@
       <c r="Z20" s="7" t="n"/>
       <c r="AA20" s="7" t="n"/>
       <c r="AB20" s="7" t="n"/>
+      <c r="AC20" s="7" t="n"/>
     </row>
     <row r="21" ht="16.05" customHeight="1" s="10">
       <c r="A21" s="8" t="n"/>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
@@ -1452,12 +1463,12 @@
       <c r="Z21" s="8" t="n"/>
       <c r="AA21" s="8" t="n"/>
       <c r="AB21" s="8" t="n"/>
+      <c r="AC21" s="8" t="n"/>
     </row>
     <row r="22" ht="16.05" customHeight="1" s="10">
       <c r="A22" s="7" t="n"/>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
@@ -1482,12 +1493,12 @@
       <c r="Z22" s="7" t="n"/>
       <c r="AA22" s="7" t="n"/>
       <c r="AB22" s="7" t="n"/>
+      <c r="AC22" s="7" t="n"/>
     </row>
     <row r="23" ht="16.05" customHeight="1" s="10">
       <c r="A23" s="8" t="n"/>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
@@ -1512,12 +1523,12 @@
       <c r="Z23" s="8" t="n"/>
       <c r="AA23" s="8" t="n"/>
       <c r="AB23" s="8" t="n"/>
+      <c r="AC23" s="8" t="n"/>
     </row>
     <row r="24" ht="16.05" customHeight="1" s="10">
       <c r="A24" s="7" t="n"/>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
@@ -1542,12 +1553,12 @@
       <c r="Z24" s="7" t="n"/>
       <c r="AA24" s="7" t="n"/>
       <c r="AB24" s="7" t="n"/>
+      <c r="AC24" s="7" t="n"/>
     </row>
     <row r="25" ht="16.05" customHeight="1" s="10">
       <c r="A25" s="8" t="n"/>
       <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
@@ -1572,12 +1583,12 @@
       <c r="Z25" s="8" t="n"/>
       <c r="AA25" s="8" t="n"/>
       <c r="AB25" s="8" t="n"/>
+      <c r="AC25" s="8" t="n"/>
     </row>
     <row r="26" ht="16.05" customHeight="1" s="10">
       <c r="A26" s="7" t="n"/>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
@@ -1602,12 +1613,12 @@
       <c r="Z26" s="7" t="n"/>
       <c r="AA26" s="7" t="n"/>
       <c r="AB26" s="7" t="n"/>
+      <c r="AC26" s="7" t="n"/>
     </row>
     <row r="27" ht="16.05" customHeight="1" s="10">
       <c r="A27" s="8" t="n"/>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -1632,12 +1643,12 @@
       <c r="Z27" s="8" t="n"/>
       <c r="AA27" s="8" t="n"/>
       <c r="AB27" s="8" t="n"/>
+      <c r="AC27" s="8" t="n"/>
     </row>
     <row r="28" ht="16.05" customHeight="1" s="10">
       <c r="A28" s="7" t="n"/>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
@@ -1662,12 +1673,12 @@
       <c r="Z28" s="7" t="n"/>
       <c r="AA28" s="7" t="n"/>
       <c r="AB28" s="7" t="n"/>
+      <c r="AC28" s="7" t="n"/>
     </row>
     <row r="29" ht="16.05" customHeight="1" s="10">
       <c r="A29" s="8" t="n"/>
       <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -1692,12 +1703,12 @@
       <c r="Z29" s="8" t="n"/>
       <c r="AA29" s="8" t="n"/>
       <c r="AB29" s="8" t="n"/>
+      <c r="AC29" s="8" t="n"/>
     </row>
     <row r="30" ht="16.05" customHeight="1" s="10">
       <c r="A30" s="7" t="n"/>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="7" t="n"/>
@@ -1722,12 +1733,12 @@
       <c r="Z30" s="7" t="n"/>
       <c r="AA30" s="7" t="n"/>
       <c r="AB30" s="7" t="n"/>
+      <c r="AC30" s="7" t="n"/>
     </row>
     <row r="31" ht="16.05" customHeight="1" s="10">
       <c r="A31" s="8" t="n"/>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
@@ -1752,12 +1763,12 @@
       <c r="Z31" s="8" t="n"/>
       <c r="AA31" s="8" t="n"/>
       <c r="AB31" s="8" t="n"/>
+      <c r="AC31" s="8" t="n"/>
     </row>
     <row r="32" ht="16.05" customHeight="1" s="10">
       <c r="A32" s="7" t="n"/>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
@@ -1782,12 +1793,12 @@
       <c r="Z32" s="7" t="n"/>
       <c r="AA32" s="7" t="n"/>
       <c r="AB32" s="7" t="n"/>
+      <c r="AC32" s="7" t="n"/>
     </row>
     <row r="33" ht="16.05" customHeight="1" s="10">
       <c r="A33" s="8" t="n"/>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -1812,12 +1823,12 @@
       <c r="Z33" s="8" t="n"/>
       <c r="AA33" s="8" t="n"/>
       <c r="AB33" s="8" t="n"/>
+      <c r="AC33" s="8" t="n"/>
     </row>
     <row r="34" ht="16.05" customHeight="1" s="10">
       <c r="A34" s="7" t="n"/>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
@@ -1842,12 +1853,12 @@
       <c r="Z34" s="7" t="n"/>
       <c r="AA34" s="7" t="n"/>
       <c r="AB34" s="7" t="n"/>
+      <c r="AC34" s="7" t="n"/>
     </row>
     <row r="35" ht="16.05" customHeight="1" s="10">
       <c r="A35" s="8" t="n"/>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
@@ -1872,12 +1883,12 @@
       <c r="Z35" s="8" t="n"/>
       <c r="AA35" s="8" t="n"/>
       <c r="AB35" s="8" t="n"/>
+      <c r="AC35" s="8" t="n"/>
     </row>
     <row r="36" ht="16.05" customHeight="1" s="10">
       <c r="A36" s="7" t="n"/>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="n"/>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="7" t="n"/>
@@ -1902,12 +1913,12 @@
       <c r="Z36" s="7" t="n"/>
       <c r="AA36" s="7" t="n"/>
       <c r="AB36" s="7" t="n"/>
+      <c r="AC36" s="7" t="n"/>
     </row>
     <row r="37" ht="16.05" customHeight="1" s="10">
       <c r="A37" s="8" t="n"/>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
@@ -1932,12 +1943,12 @@
       <c r="Z37" s="8" t="n"/>
       <c r="AA37" s="8" t="n"/>
       <c r="AB37" s="8" t="n"/>
+      <c r="AC37" s="8" t="n"/>
     </row>
     <row r="38" ht="16.05" customHeight="1" s="10">
       <c r="A38" s="7" t="n"/>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="7" t="n"/>
@@ -1962,12 +1973,12 @@
       <c r="Z38" s="7" t="n"/>
       <c r="AA38" s="7" t="n"/>
       <c r="AB38" s="7" t="n"/>
+      <c r="AC38" s="7" t="n"/>
     </row>
     <row r="39" ht="16.05" customHeight="1" s="10">
       <c r="A39" s="8" t="n"/>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
@@ -1992,12 +2003,12 @@
       <c r="Z39" s="8" t="n"/>
       <c r="AA39" s="8" t="n"/>
       <c r="AB39" s="8" t="n"/>
+      <c r="AC39" s="8" t="n"/>
     </row>
     <row r="40" ht="16.05" customHeight="1" s="10">
       <c r="A40" s="7" t="n"/>
       <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -2022,12 +2033,12 @@
       <c r="Z40" s="7" t="n"/>
       <c r="AA40" s="7" t="n"/>
       <c r="AB40" s="7" t="n"/>
+      <c r="AC40" s="7" t="n"/>
     </row>
     <row r="41" ht="16.05" customHeight="1" s="10">
       <c r="A41" s="8" t="n"/>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -2052,12 +2063,12 @@
       <c r="Z41" s="8" t="n"/>
       <c r="AA41" s="8" t="n"/>
       <c r="AB41" s="8" t="n"/>
+      <c r="AC41" s="8" t="n"/>
     </row>
     <row r="42" ht="16.05" customHeight="1" s="10">
       <c r="A42" s="7" t="n"/>
       <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
@@ -2082,12 +2093,12 @@
       <c r="Z42" s="7" t="n"/>
       <c r="AA42" s="7" t="n"/>
       <c r="AB42" s="7" t="n"/>
+      <c r="AC42" s="7" t="n"/>
     </row>
     <row r="43" ht="16.05" customHeight="1" s="10">
       <c r="A43" s="8" t="n"/>
       <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
@@ -2112,12 +2123,12 @@
       <c r="Z43" s="8" t="n"/>
       <c r="AA43" s="8" t="n"/>
       <c r="AB43" s="8" t="n"/>
+      <c r="AC43" s="8" t="n"/>
     </row>
     <row r="44" ht="16.05" customHeight="1" s="10">
       <c r="A44" s="7" t="n"/>
       <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
@@ -2142,12 +2153,12 @@
       <c r="Z44" s="7" t="n"/>
       <c r="AA44" s="7" t="n"/>
       <c r="AB44" s="7" t="n"/>
+      <c r="AC44" s="7" t="n"/>
     </row>
     <row r="45" ht="16.05" customHeight="1" s="10">
       <c r="A45" s="8" t="n"/>
       <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -2172,12 +2183,12 @@
       <c r="Z45" s="8" t="n"/>
       <c r="AA45" s="8" t="n"/>
       <c r="AB45" s="8" t="n"/>
+      <c r="AC45" s="8" t="n"/>
     </row>
     <row r="46" ht="16.05" customHeight="1" s="10">
       <c r="A46" s="7" t="n"/>
       <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="n"/>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
@@ -2202,12 +2213,12 @@
       <c r="Z46" s="7" t="n"/>
       <c r="AA46" s="7" t="n"/>
       <c r="AB46" s="7" t="n"/>
+      <c r="AC46" s="7" t="n"/>
     </row>
     <row r="47" ht="16.05" customHeight="1" s="10">
       <c r="A47" s="8" t="n"/>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
@@ -2232,12 +2243,12 @@
       <c r="Z47" s="8" t="n"/>
       <c r="AA47" s="8" t="n"/>
       <c r="AB47" s="8" t="n"/>
+      <c r="AC47" s="8" t="n"/>
     </row>
     <row r="48" ht="16.05" customHeight="1" s="10">
       <c r="A48" s="7" t="n"/>
       <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="n"/>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -2262,12 +2273,12 @@
       <c r="Z48" s="7" t="n"/>
       <c r="AA48" s="7" t="n"/>
       <c r="AB48" s="7" t="n"/>
+      <c r="AC48" s="7" t="n"/>
     </row>
     <row r="49" ht="16.05" customHeight="1" s="10">
       <c r="A49" s="8" t="n"/>
       <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -2292,12 +2303,12 @@
       <c r="Z49" s="8" t="n"/>
       <c r="AA49" s="8" t="n"/>
       <c r="AB49" s="8" t="n"/>
+      <c r="AC49" s="8" t="n"/>
     </row>
     <row r="50" ht="16.05" customHeight="1" s="10">
       <c r="A50" s="7" t="n"/>
       <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
@@ -2322,12 +2333,12 @@
       <c r="Z50" s="7" t="n"/>
       <c r="AA50" s="7" t="n"/>
       <c r="AB50" s="7" t="n"/>
+      <c r="AC50" s="7" t="n"/>
     </row>
     <row r="51" ht="16.05" customHeight="1" s="10">
       <c r="A51" s="8" t="n"/>
       <c r="B51" s="8" t="n"/>
       <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
       <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="n"/>
@@ -2352,12 +2363,12 @@
       <c r="Z51" s="8" t="n"/>
       <c r="AA51" s="8" t="n"/>
       <c r="AB51" s="8" t="n"/>
+      <c r="AC51" s="8" t="n"/>
     </row>
     <row r="52" ht="16.05" customHeight="1" s="10">
       <c r="A52" s="7" t="n"/>
       <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
@@ -2382,12 +2393,12 @@
       <c r="Z52" s="7" t="n"/>
       <c r="AA52" s="7" t="n"/>
       <c r="AB52" s="7" t="n"/>
+      <c r="AC52" s="7" t="n"/>
     </row>
     <row r="53" ht="16.05" customHeight="1" s="10">
       <c r="A53" s="8" t="n"/>
       <c r="B53" s="8" t="n"/>
       <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="n"/>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
@@ -2412,12 +2423,12 @@
       <c r="Z53" s="8" t="n"/>
       <c r="AA53" s="8" t="n"/>
       <c r="AB53" s="8" t="n"/>
+      <c r="AC53" s="8" t="n"/>
     </row>
     <row r="54" ht="16.05" customHeight="1" s="10">
       <c r="A54" s="7" t="n"/>
       <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
@@ -2442,12 +2453,12 @@
       <c r="Z54" s="7" t="n"/>
       <c r="AA54" s="7" t="n"/>
       <c r="AB54" s="7" t="n"/>
+      <c r="AC54" s="7" t="n"/>
     </row>
     <row r="55" ht="16.05" customHeight="1" s="10">
       <c r="A55" s="8" t="n"/>
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
@@ -2472,12 +2483,12 @@
       <c r="Z55" s="8" t="n"/>
       <c r="AA55" s="8" t="n"/>
       <c r="AB55" s="8" t="n"/>
+      <c r="AC55" s="8" t="n"/>
     </row>
     <row r="56" ht="16.05" customHeight="1" s="10">
       <c r="A56" s="7" t="n"/>
       <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
@@ -2502,12 +2513,12 @@
       <c r="Z56" s="7" t="n"/>
       <c r="AA56" s="7" t="n"/>
       <c r="AB56" s="7" t="n"/>
+      <c r="AC56" s="7" t="n"/>
     </row>
     <row r="57" ht="16.05" customHeight="1" s="10">
       <c r="A57" s="8" t="n"/>
       <c r="B57" s="8" t="n"/>
       <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
@@ -2532,12 +2543,12 @@
       <c r="Z57" s="8" t="n"/>
       <c r="AA57" s="8" t="n"/>
       <c r="AB57" s="8" t="n"/>
+      <c r="AC57" s="8" t="n"/>
     </row>
     <row r="58" ht="16.05" customHeight="1" s="10">
       <c r="A58" s="7" t="n"/>
       <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
@@ -2562,12 +2573,12 @@
       <c r="Z58" s="7" t="n"/>
       <c r="AA58" s="7" t="n"/>
       <c r="AB58" s="7" t="n"/>
+      <c r="AC58" s="7" t="n"/>
     </row>
     <row r="59" ht="16.05" customHeight="1" s="10">
       <c r="A59" s="8" t="n"/>
       <c r="B59" s="8" t="n"/>
       <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
@@ -2592,12 +2603,12 @@
       <c r="Z59" s="8" t="n"/>
       <c r="AA59" s="8" t="n"/>
       <c r="AB59" s="8" t="n"/>
+      <c r="AC59" s="8" t="n"/>
     </row>
     <row r="60" ht="16.05" customHeight="1" s="10">
       <c r="A60" s="7" t="n"/>
       <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
@@ -2622,12 +2633,12 @@
       <c r="Z60" s="7" t="n"/>
       <c r="AA60" s="7" t="n"/>
       <c r="AB60" s="7" t="n"/>
+      <c r="AC60" s="7" t="n"/>
     </row>
     <row r="61" ht="16.05" customHeight="1" s="10">
       <c r="A61" s="8" t="n"/>
       <c r="B61" s="8" t="n"/>
       <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
       <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="n"/>
@@ -2652,12 +2663,12 @@
       <c r="Z61" s="8" t="n"/>
       <c r="AA61" s="8" t="n"/>
       <c r="AB61" s="8" t="n"/>
+      <c r="AC61" s="8" t="n"/>
     </row>
     <row r="62" ht="16.05" customHeight="1" s="10">
       <c r="A62" s="7" t="n"/>
       <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="n"/>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
@@ -2682,12 +2693,12 @@
       <c r="Z62" s="7" t="n"/>
       <c r="AA62" s="7" t="n"/>
       <c r="AB62" s="7" t="n"/>
+      <c r="AC62" s="7" t="n"/>
     </row>
     <row r="63" ht="16.05" customHeight="1" s="10">
       <c r="A63" s="8" t="n"/>
       <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
@@ -2712,12 +2723,12 @@
       <c r="Z63" s="8" t="n"/>
       <c r="AA63" s="8" t="n"/>
       <c r="AB63" s="8" t="n"/>
+      <c r="AC63" s="8" t="n"/>
     </row>
     <row r="64" ht="16.05" customHeight="1" s="10">
       <c r="A64" s="7" t="n"/>
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
       <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
@@ -2742,12 +2753,12 @@
       <c r="Z64" s="7" t="n"/>
       <c r="AA64" s="7" t="n"/>
       <c r="AB64" s="7" t="n"/>
+      <c r="AC64" s="7" t="n"/>
     </row>
     <row r="65" ht="16.05" customHeight="1" s="10">
       <c r="A65" s="8" t="n"/>
       <c r="B65" s="8" t="n"/>
       <c r="C65" s="8" t="n"/>
-      <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
       <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
@@ -2772,12 +2783,12 @@
       <c r="Z65" s="8" t="n"/>
       <c r="AA65" s="8" t="n"/>
       <c r="AB65" s="8" t="n"/>
+      <c r="AC65" s="8" t="n"/>
     </row>
     <row r="66" ht="16.05" customHeight="1" s="10">
       <c r="A66" s="7" t="n"/>
       <c r="B66" s="7" t="n"/>
       <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
@@ -2802,12 +2813,12 @@
       <c r="Z66" s="7" t="n"/>
       <c r="AA66" s="7" t="n"/>
       <c r="AB66" s="7" t="n"/>
+      <c r="AC66" s="7" t="n"/>
     </row>
     <row r="67" ht="16.05" customHeight="1" s="10">
       <c r="A67" s="8" t="n"/>
       <c r="B67" s="8" t="n"/>
       <c r="C67" s="8" t="n"/>
-      <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
@@ -2832,12 +2843,12 @@
       <c r="Z67" s="8" t="n"/>
       <c r="AA67" s="8" t="n"/>
       <c r="AB67" s="8" t="n"/>
+      <c r="AC67" s="8" t="n"/>
     </row>
     <row r="68" ht="16.05" customHeight="1" s="10">
       <c r="A68" s="7" t="n"/>
       <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="n"/>
-      <c r="D68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
@@ -2862,12 +2873,12 @@
       <c r="Z68" s="7" t="n"/>
       <c r="AA68" s="7" t="n"/>
       <c r="AB68" s="7" t="n"/>
+      <c r="AC68" s="7" t="n"/>
     </row>
     <row r="69" ht="16.05" customHeight="1" s="10">
       <c r="A69" s="8" t="n"/>
       <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
@@ -2892,12 +2903,12 @@
       <c r="Z69" s="8" t="n"/>
       <c r="AA69" s="8" t="n"/>
       <c r="AB69" s="8" t="n"/>
+      <c r="AC69" s="8" t="n"/>
     </row>
     <row r="70" ht="16.05" customHeight="1" s="10">
       <c r="A70" s="7" t="n"/>
       <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
@@ -2922,12 +2933,12 @@
       <c r="Z70" s="7" t="n"/>
       <c r="AA70" s="7" t="n"/>
       <c r="AB70" s="7" t="n"/>
+      <c r="AC70" s="7" t="n"/>
     </row>
     <row r="71" ht="16.05" customHeight="1" s="10">
       <c r="A71" s="8" t="n"/>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
@@ -2952,12 +2963,12 @@
       <c r="Z71" s="8" t="n"/>
       <c r="AA71" s="8" t="n"/>
       <c r="AB71" s="8" t="n"/>
+      <c r="AC71" s="8" t="n"/>
     </row>
     <row r="72" ht="16.05" customHeight="1" s="10">
       <c r="A72" s="7" t="n"/>
       <c r="B72" s="7" t="n"/>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
@@ -2982,12 +2993,12 @@
       <c r="Z72" s="7" t="n"/>
       <c r="AA72" s="7" t="n"/>
       <c r="AB72" s="7" t="n"/>
+      <c r="AC72" s="7" t="n"/>
     </row>
     <row r="73" ht="16.05" customHeight="1" s="10">
       <c r="A73" s="8" t="n"/>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
       <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
@@ -3012,12 +3023,12 @@
       <c r="Z73" s="8" t="n"/>
       <c r="AA73" s="8" t="n"/>
       <c r="AB73" s="8" t="n"/>
+      <c r="AC73" s="8" t="n"/>
     </row>
     <row r="74" ht="16.05" customHeight="1" s="10">
       <c r="A74" s="7" t="n"/>
       <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
-      <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
@@ -3042,12 +3053,12 @@
       <c r="Z74" s="7" t="n"/>
       <c r="AA74" s="7" t="n"/>
       <c r="AB74" s="7" t="n"/>
+      <c r="AC74" s="7" t="n"/>
     </row>
     <row r="75" ht="16.05" customHeight="1" s="10">
       <c r="A75" s="8" t="n"/>
       <c r="B75" s="8" t="n"/>
       <c r="C75" s="8" t="n"/>
-      <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
@@ -3072,12 +3083,12 @@
       <c r="Z75" s="8" t="n"/>
       <c r="AA75" s="8" t="n"/>
       <c r="AB75" s="8" t="n"/>
+      <c r="AC75" s="8" t="n"/>
     </row>
     <row r="76" ht="16.05" customHeight="1" s="10">
       <c r="A76" s="7" t="n"/>
       <c r="B76" s="7" t="n"/>
       <c r="C76" s="7" t="n"/>
-      <c r="D76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
@@ -3102,12 +3113,12 @@
       <c r="Z76" s="7" t="n"/>
       <c r="AA76" s="7" t="n"/>
       <c r="AB76" s="7" t="n"/>
+      <c r="AC76" s="7" t="n"/>
     </row>
     <row r="77" ht="16.05" customHeight="1" s="10">
       <c r="A77" s="8" t="n"/>
       <c r="B77" s="8" t="n"/>
       <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
       <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="n"/>
@@ -3132,12 +3143,12 @@
       <c r="Z77" s="8" t="n"/>
       <c r="AA77" s="8" t="n"/>
       <c r="AB77" s="8" t="n"/>
+      <c r="AC77" s="8" t="n"/>
     </row>
     <row r="78" ht="16.05" customHeight="1" s="10">
       <c r="A78" s="7" t="n"/>
       <c r="B78" s="7" t="n"/>
       <c r="C78" s="7" t="n"/>
-      <c r="D78" s="7" t="n"/>
       <c r="E78" s="7" t="n"/>
       <c r="F78" s="7" t="n"/>
       <c r="G78" s="7" t="n"/>
@@ -3162,12 +3173,12 @@
       <c r="Z78" s="7" t="n"/>
       <c r="AA78" s="7" t="n"/>
       <c r="AB78" s="7" t="n"/>
+      <c r="AC78" s="7" t="n"/>
     </row>
     <row r="79" ht="16.05" customHeight="1" s="10">
       <c r="A79" s="8" t="n"/>
       <c r="B79" s="8" t="n"/>
       <c r="C79" s="8" t="n"/>
-      <c r="D79" s="8" t="n"/>
       <c r="E79" s="8" t="n"/>
       <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="n"/>
@@ -3192,12 +3203,12 @@
       <c r="Z79" s="8" t="n"/>
       <c r="AA79" s="8" t="n"/>
       <c r="AB79" s="8" t="n"/>
+      <c r="AC79" s="8" t="n"/>
     </row>
     <row r="80" ht="16.05" customHeight="1" s="10">
       <c r="A80" s="7" t="n"/>
       <c r="B80" s="7" t="n"/>
       <c r="C80" s="7" t="n"/>
-      <c r="D80" s="7" t="n"/>
       <c r="E80" s="7" t="n"/>
       <c r="F80" s="7" t="n"/>
       <c r="G80" s="7" t="n"/>
@@ -3222,12 +3233,12 @@
       <c r="Z80" s="7" t="n"/>
       <c r="AA80" s="7" t="n"/>
       <c r="AB80" s="7" t="n"/>
+      <c r="AC80" s="7" t="n"/>
     </row>
     <row r="81" ht="16.05" customHeight="1" s="10">
       <c r="A81" s="8" t="n"/>
       <c r="B81" s="8" t="n"/>
       <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="n"/>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
@@ -3252,12 +3263,12 @@
       <c r="Z81" s="8" t="n"/>
       <c r="AA81" s="8" t="n"/>
       <c r="AB81" s="8" t="n"/>
+      <c r="AC81" s="8" t="n"/>
     </row>
     <row r="82" ht="16.05" customHeight="1" s="10">
       <c r="A82" s="7" t="n"/>
       <c r="B82" s="7" t="n"/>
       <c r="C82" s="7" t="n"/>
-      <c r="D82" s="7" t="n"/>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="7" t="n"/>
       <c r="G82" s="7" t="n"/>
@@ -3282,12 +3293,12 @@
       <c r="Z82" s="7" t="n"/>
       <c r="AA82" s="7" t="n"/>
       <c r="AB82" s="7" t="n"/>
+      <c r="AC82" s="7" t="n"/>
     </row>
     <row r="83" ht="16.05" customHeight="1" s="10">
       <c r="A83" s="8" t="n"/>
       <c r="B83" s="8" t="n"/>
       <c r="C83" s="8" t="n"/>
-      <c r="D83" s="8" t="n"/>
       <c r="E83" s="8" t="n"/>
       <c r="F83" s="8" t="n"/>
       <c r="G83" s="8" t="n"/>
@@ -3312,12 +3323,12 @@
       <c r="Z83" s="8" t="n"/>
       <c r="AA83" s="8" t="n"/>
       <c r="AB83" s="8" t="n"/>
+      <c r="AC83" s="8" t="n"/>
     </row>
     <row r="84" ht="16.05" customHeight="1" s="10">
       <c r="A84" s="7" t="n"/>
       <c r="B84" s="7" t="n"/>
       <c r="C84" s="7" t="n"/>
-      <c r="D84" s="7" t="n"/>
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="7" t="n"/>
       <c r="G84" s="7" t="n"/>
@@ -3342,12 +3353,12 @@
       <c r="Z84" s="7" t="n"/>
       <c r="AA84" s="7" t="n"/>
       <c r="AB84" s="7" t="n"/>
+      <c r="AC84" s="7" t="n"/>
     </row>
     <row r="85" ht="16.05" customHeight="1" s="10">
       <c r="A85" s="8" t="n"/>
       <c r="B85" s="8" t="n"/>
       <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
@@ -3372,12 +3383,12 @@
       <c r="Z85" s="8" t="n"/>
       <c r="AA85" s="8" t="n"/>
       <c r="AB85" s="8" t="n"/>
+      <c r="AC85" s="8" t="n"/>
     </row>
     <row r="86" ht="16.05" customHeight="1" s="10">
       <c r="A86" s="7" t="n"/>
       <c r="B86" s="7" t="n"/>
       <c r="C86" s="7" t="n"/>
-      <c r="D86" s="7" t="n"/>
       <c r="E86" s="7" t="n"/>
       <c r="F86" s="7" t="n"/>
       <c r="G86" s="7" t="n"/>
@@ -3402,12 +3413,12 @@
       <c r="Z86" s="7" t="n"/>
       <c r="AA86" s="7" t="n"/>
       <c r="AB86" s="7" t="n"/>
+      <c r="AC86" s="7" t="n"/>
     </row>
     <row r="87" ht="16.05" customHeight="1" s="10">
       <c r="A87" s="8" t="n"/>
       <c r="B87" s="8" t="n"/>
       <c r="C87" s="8" t="n"/>
-      <c r="D87" s="8" t="n"/>
       <c r="E87" s="8" t="n"/>
       <c r="F87" s="8" t="n"/>
       <c r="G87" s="8" t="n"/>
@@ -3432,12 +3443,12 @@
       <c r="Z87" s="8" t="n"/>
       <c r="AA87" s="8" t="n"/>
       <c r="AB87" s="8" t="n"/>
+      <c r="AC87" s="8" t="n"/>
     </row>
     <row r="88" ht="16.05" customHeight="1" s="10">
       <c r="A88" s="7" t="n"/>
       <c r="B88" s="7" t="n"/>
       <c r="C88" s="7" t="n"/>
-      <c r="D88" s="7" t="n"/>
       <c r="E88" s="7" t="n"/>
       <c r="F88" s="7" t="n"/>
       <c r="G88" s="7" t="n"/>
@@ -3462,12 +3473,12 @@
       <c r="Z88" s="7" t="n"/>
       <c r="AA88" s="7" t="n"/>
       <c r="AB88" s="7" t="n"/>
+      <c r="AC88" s="7" t="n"/>
     </row>
     <row r="89" ht="16.05" customHeight="1" s="10">
       <c r="A89" s="8" t="n"/>
       <c r="B89" s="8" t="n"/>
       <c r="C89" s="8" t="n"/>
-      <c r="D89" s="8" t="n"/>
       <c r="E89" s="8" t="n"/>
       <c r="F89" s="8" t="n"/>
       <c r="G89" s="8" t="n"/>
@@ -3492,12 +3503,12 @@
       <c r="Z89" s="8" t="n"/>
       <c r="AA89" s="8" t="n"/>
       <c r="AB89" s="8" t="n"/>
+      <c r="AC89" s="8" t="n"/>
     </row>
     <row r="90" ht="16.05" customHeight="1" s="10">
       <c r="A90" s="7" t="n"/>
       <c r="B90" s="7" t="n"/>
       <c r="C90" s="7" t="n"/>
-      <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="7" t="n"/>
       <c r="G90" s="7" t="n"/>
@@ -3522,12 +3533,12 @@
       <c r="Z90" s="7" t="n"/>
       <c r="AA90" s="7" t="n"/>
       <c r="AB90" s="7" t="n"/>
+      <c r="AC90" s="7" t="n"/>
     </row>
     <row r="91" ht="16.05" customHeight="1" s="10">
       <c r="A91" s="8" t="n"/>
       <c r="B91" s="8" t="n"/>
       <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="n"/>
       <c r="E91" s="8" t="n"/>
       <c r="F91" s="8" t="n"/>
       <c r="G91" s="8" t="n"/>
@@ -3552,12 +3563,12 @@
       <c r="Z91" s="8" t="n"/>
       <c r="AA91" s="8" t="n"/>
       <c r="AB91" s="8" t="n"/>
+      <c r="AC91" s="8" t="n"/>
     </row>
     <row r="92" ht="16.05" customHeight="1" s="10">
       <c r="A92" s="7" t="n"/>
       <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
-      <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
@@ -3582,12 +3593,12 @@
       <c r="Z92" s="7" t="n"/>
       <c r="AA92" s="7" t="n"/>
       <c r="AB92" s="7" t="n"/>
+      <c r="AC92" s="7" t="n"/>
     </row>
     <row r="93" ht="16.05" customHeight="1" s="10">
       <c r="A93" s="8" t="n"/>
       <c r="B93" s="8" t="n"/>
       <c r="C93" s="8" t="n"/>
-      <c r="D93" s="8" t="n"/>
       <c r="E93" s="8" t="n"/>
       <c r="F93" s="8" t="n"/>
       <c r="G93" s="8" t="n"/>
@@ -3612,12 +3623,12 @@
       <c r="Z93" s="8" t="n"/>
       <c r="AA93" s="8" t="n"/>
       <c r="AB93" s="8" t="n"/>
+      <c r="AC93" s="8" t="n"/>
     </row>
     <row r="94" ht="16.05" customHeight="1" s="10">
       <c r="A94" s="7" t="n"/>
       <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
-      <c r="D94" s="7" t="n"/>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
@@ -3642,12 +3653,12 @@
       <c r="Z94" s="7" t="n"/>
       <c r="AA94" s="7" t="n"/>
       <c r="AB94" s="7" t="n"/>
+      <c r="AC94" s="7" t="n"/>
     </row>
     <row r="95" ht="16.05" customHeight="1" s="10">
       <c r="A95" s="8" t="n"/>
       <c r="B95" s="8" t="n"/>
       <c r="C95" s="8" t="n"/>
-      <c r="D95" s="8" t="n"/>
       <c r="E95" s="8" t="n"/>
       <c r="F95" s="8" t="n"/>
       <c r="G95" s="8" t="n"/>
@@ -3672,12 +3683,12 @@
       <c r="Z95" s="8" t="n"/>
       <c r="AA95" s="8" t="n"/>
       <c r="AB95" s="8" t="n"/>
+      <c r="AC95" s="8" t="n"/>
     </row>
     <row r="96" ht="16.05" customHeight="1" s="10">
       <c r="A96" s="7" t="n"/>
       <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
@@ -3702,12 +3713,12 @@
       <c r="Z96" s="7" t="n"/>
       <c r="AA96" s="7" t="n"/>
       <c r="AB96" s="7" t="n"/>
+      <c r="AC96" s="7" t="n"/>
     </row>
     <row r="97" ht="16.05" customHeight="1" s="10">
       <c r="A97" s="8" t="n"/>
       <c r="B97" s="8" t="n"/>
       <c r="C97" s="8" t="n"/>
-      <c r="D97" s="8" t="n"/>
       <c r="E97" s="8" t="n"/>
       <c r="F97" s="8" t="n"/>
       <c r="G97" s="8" t="n"/>
@@ -3732,12 +3743,12 @@
       <c r="Z97" s="8" t="n"/>
       <c r="AA97" s="8" t="n"/>
       <c r="AB97" s="8" t="n"/>
+      <c r="AC97" s="8" t="n"/>
     </row>
     <row r="98" ht="16.05" customHeight="1" s="10">
       <c r="A98" s="7" t="n"/>
       <c r="B98" s="7" t="n"/>
       <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="n"/>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="7" t="n"/>
       <c r="G98" s="7" t="n"/>
@@ -3762,12 +3773,12 @@
       <c r="Z98" s="7" t="n"/>
       <c r="AA98" s="7" t="n"/>
       <c r="AB98" s="7" t="n"/>
+      <c r="AC98" s="7" t="n"/>
     </row>
     <row r="99" ht="16.05" customHeight="1" s="10">
       <c r="A99" s="8" t="n"/>
       <c r="B99" s="8" t="n"/>
       <c r="C99" s="8" t="n"/>
-      <c r="D99" s="8" t="n"/>
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="8" t="n"/>
@@ -3792,12 +3803,12 @@
       <c r="Z99" s="8" t="n"/>
       <c r="AA99" s="8" t="n"/>
       <c r="AB99" s="8" t="n"/>
+      <c r="AC99" s="8" t="n"/>
     </row>
     <row r="100" ht="16.05" customHeight="1" s="10">
       <c r="A100" s="7" t="n"/>
       <c r="B100" s="7" t="n"/>
       <c r="C100" s="7" t="n"/>
-      <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
@@ -3822,12 +3833,12 @@
       <c r="Z100" s="7" t="n"/>
       <c r="AA100" s="7" t="n"/>
       <c r="AB100" s="7" t="n"/>
+      <c r="AC100" s="7" t="n"/>
     </row>
     <row r="101" ht="16.05" customHeight="1" s="10">
       <c r="A101" s="8" t="n"/>
       <c r="B101" s="8" t="n"/>
       <c r="C101" s="8" t="n"/>
-      <c r="D101" s="8" t="n"/>
       <c r="E101" s="8" t="n"/>
       <c r="F101" s="8" t="n"/>
       <c r="G101" s="8" t="n"/>
@@ -3852,12 +3863,12 @@
       <c r="Z101" s="8" t="n"/>
       <c r="AA101" s="8" t="n"/>
       <c r="AB101" s="8" t="n"/>
+      <c r="AC101" s="8" t="n"/>
     </row>
     <row r="102" ht="16.05" customHeight="1" s="10">
       <c r="A102" s="7" t="n"/>
       <c r="B102" s="7" t="n"/>
       <c r="C102" s="7" t="n"/>
-      <c r="D102" s="7" t="n"/>
       <c r="E102" s="7" t="n"/>
       <c r="F102" s="7" t="n"/>
       <c r="G102" s="7" t="n"/>
@@ -3882,12 +3893,12 @@
       <c r="Z102" s="7" t="n"/>
       <c r="AA102" s="7" t="n"/>
       <c r="AB102" s="7" t="n"/>
+      <c r="AC102" s="7" t="n"/>
     </row>
     <row r="103" ht="16.05" customHeight="1" s="10">
       <c r="A103" s="8" t="n"/>
       <c r="B103" s="8" t="n"/>
       <c r="C103" s="8" t="n"/>
-      <c r="D103" s="8" t="n"/>
       <c r="E103" s="8" t="n"/>
       <c r="F103" s="8" t="n"/>
       <c r="G103" s="8" t="n"/>
@@ -3912,12 +3923,12 @@
       <c r="Z103" s="8" t="n"/>
       <c r="AA103" s="8" t="n"/>
       <c r="AB103" s="8" t="n"/>
+      <c r="AC103" s="8" t="n"/>
     </row>
     <row r="104" ht="16.05" customHeight="1" s="10">
       <c r="A104" s="7" t="n"/>
       <c r="B104" s="7" t="n"/>
       <c r="C104" s="7" t="n"/>
-      <c r="D104" s="7" t="n"/>
       <c r="E104" s="7" t="n"/>
       <c r="F104" s="7" t="n"/>
       <c r="G104" s="7" t="n"/>
@@ -3942,12 +3953,12 @@
       <c r="Z104" s="7" t="n"/>
       <c r="AA104" s="7" t="n"/>
       <c r="AB104" s="7" t="n"/>
+      <c r="AC104" s="7" t="n"/>
     </row>
     <row r="105" ht="16.05" customHeight="1" s="10">
       <c r="A105" s="8" t="n"/>
       <c r="B105" s="8" t="n"/>
       <c r="C105" s="8" t="n"/>
-      <c r="D105" s="8" t="n"/>
       <c r="E105" s="8" t="n"/>
       <c r="F105" s="8" t="n"/>
       <c r="G105" s="8" t="n"/>
@@ -3972,12 +3983,12 @@
       <c r="Z105" s="8" t="n"/>
       <c r="AA105" s="8" t="n"/>
       <c r="AB105" s="8" t="n"/>
+      <c r="AC105" s="8" t="n"/>
     </row>
     <row r="106" ht="16.05" customHeight="1" s="10">
       <c r="A106" s="7" t="n"/>
       <c r="B106" s="7" t="n"/>
       <c r="C106" s="7" t="n"/>
-      <c r="D106" s="7" t="n"/>
       <c r="E106" s="7" t="n"/>
       <c r="F106" s="7" t="n"/>
       <c r="G106" s="7" t="n"/>
@@ -4002,12 +4013,12 @@
       <c r="Z106" s="7" t="n"/>
       <c r="AA106" s="7" t="n"/>
       <c r="AB106" s="7" t="n"/>
+      <c r="AC106" s="7" t="n"/>
     </row>
     <row r="107" ht="16.05" customHeight="1" s="10">
       <c r="A107" s="8" t="n"/>
       <c r="B107" s="8" t="n"/>
       <c r="C107" s="8" t="n"/>
-      <c r="D107" s="8" t="n"/>
       <c r="E107" s="8" t="n"/>
       <c r="F107" s="8" t="n"/>
       <c r="G107" s="8" t="n"/>
@@ -4032,12 +4043,12 @@
       <c r="Z107" s="8" t="n"/>
       <c r="AA107" s="8" t="n"/>
       <c r="AB107" s="8" t="n"/>
+      <c r="AC107" s="8" t="n"/>
     </row>
     <row r="108" ht="16.05" customHeight="1" s="10">
       <c r="A108" s="7" t="n"/>
       <c r="B108" s="7" t="n"/>
       <c r="C108" s="7" t="n"/>
-      <c r="D108" s="7" t="n"/>
       <c r="E108" s="7" t="n"/>
       <c r="F108" s="7" t="n"/>
       <c r="G108" s="7" t="n"/>
@@ -4062,12 +4073,12 @@
       <c r="Z108" s="7" t="n"/>
       <c r="AA108" s="7" t="n"/>
       <c r="AB108" s="7" t="n"/>
+      <c r="AC108" s="7" t="n"/>
     </row>
     <row r="109" ht="16.05" customHeight="1" s="10">
       <c r="A109" s="8" t="n"/>
       <c r="B109" s="8" t="n"/>
       <c r="C109" s="8" t="n"/>
-      <c r="D109" s="8" t="n"/>
       <c r="E109" s="8" t="n"/>
       <c r="F109" s="8" t="n"/>
       <c r="G109" s="8" t="n"/>
@@ -4092,12 +4103,12 @@
       <c r="Z109" s="8" t="n"/>
       <c r="AA109" s="8" t="n"/>
       <c r="AB109" s="8" t="n"/>
+      <c r="AC109" s="8" t="n"/>
     </row>
     <row r="110" ht="16.05" customHeight="1" s="10">
       <c r="A110" s="7" t="n"/>
       <c r="B110" s="7" t="n"/>
       <c r="C110" s="7" t="n"/>
-      <c r="D110" s="7" t="n"/>
       <c r="E110" s="7" t="n"/>
       <c r="F110" s="7" t="n"/>
       <c r="G110" s="7" t="n"/>
@@ -4122,12 +4133,12 @@
       <c r="Z110" s="7" t="n"/>
       <c r="AA110" s="7" t="n"/>
       <c r="AB110" s="7" t="n"/>
+      <c r="AC110" s="7" t="n"/>
     </row>
     <row r="111" ht="16.05" customHeight="1" s="10">
       <c r="A111" s="8" t="n"/>
       <c r="B111" s="8" t="n"/>
       <c r="C111" s="8" t="n"/>
-      <c r="D111" s="8" t="n"/>
       <c r="E111" s="8" t="n"/>
       <c r="F111" s="8" t="n"/>
       <c r="G111" s="8" t="n"/>
@@ -4152,12 +4163,12 @@
       <c r="Z111" s="8" t="n"/>
       <c r="AA111" s="8" t="n"/>
       <c r="AB111" s="8" t="n"/>
+      <c r="AC111" s="8" t="n"/>
     </row>
     <row r="112" ht="16.05" customHeight="1" s="10">
       <c r="A112" s="7" t="n"/>
       <c r="B112" s="7" t="n"/>
       <c r="C112" s="7" t="n"/>
-      <c r="D112" s="7" t="n"/>
       <c r="E112" s="7" t="n"/>
       <c r="F112" s="7" t="n"/>
       <c r="G112" s="7" t="n"/>
@@ -4182,12 +4193,12 @@
       <c r="Z112" s="7" t="n"/>
       <c r="AA112" s="7" t="n"/>
       <c r="AB112" s="7" t="n"/>
+      <c r="AC112" s="7" t="n"/>
     </row>
     <row r="113" ht="16.05" customHeight="1" s="10">
       <c r="A113" s="8" t="n"/>
       <c r="B113" s="8" t="n"/>
       <c r="C113" s="8" t="n"/>
-      <c r="D113" s="8" t="n"/>
       <c r="E113" s="8" t="n"/>
       <c r="F113" s="8" t="n"/>
       <c r="G113" s="8" t="n"/>
@@ -4212,12 +4223,12 @@
       <c r="Z113" s="8" t="n"/>
       <c r="AA113" s="8" t="n"/>
       <c r="AB113" s="8" t="n"/>
+      <c r="AC113" s="8" t="n"/>
     </row>
     <row r="114" ht="16.05" customHeight="1" s="10">
       <c r="A114" s="7" t="n"/>
       <c r="B114" s="7" t="n"/>
       <c r="C114" s="7" t="n"/>
-      <c r="D114" s="7" t="n"/>
       <c r="E114" s="7" t="n"/>
       <c r="F114" s="7" t="n"/>
       <c r="G114" s="7" t="n"/>
@@ -4242,12 +4253,12 @@
       <c r="Z114" s="7" t="n"/>
       <c r="AA114" s="7" t="n"/>
       <c r="AB114" s="7" t="n"/>
+      <c r="AC114" s="7" t="n"/>
     </row>
     <row r="115" ht="16.05" customHeight="1" s="10">
       <c r="A115" s="8" t="n"/>
       <c r="B115" s="8" t="n"/>
       <c r="C115" s="8" t="n"/>
-      <c r="D115" s="8" t="n"/>
       <c r="E115" s="8" t="n"/>
       <c r="F115" s="8" t="n"/>
       <c r="G115" s="8" t="n"/>
@@ -4272,12 +4283,12 @@
       <c r="Z115" s="8" t="n"/>
       <c r="AA115" s="8" t="n"/>
       <c r="AB115" s="8" t="n"/>
+      <c r="AC115" s="8" t="n"/>
     </row>
     <row r="116" ht="16.05" customHeight="1" s="10">
       <c r="A116" s="7" t="n"/>
       <c r="B116" s="7" t="n"/>
       <c r="C116" s="7" t="n"/>
-      <c r="D116" s="7" t="n"/>
       <c r="E116" s="7" t="n"/>
       <c r="F116" s="7" t="n"/>
       <c r="G116" s="7" t="n"/>
@@ -4302,12 +4313,12 @@
       <c r="Z116" s="7" t="n"/>
       <c r="AA116" s="7" t="n"/>
       <c r="AB116" s="7" t="n"/>
+      <c r="AC116" s="7" t="n"/>
     </row>
     <row r="117" ht="16.05" customHeight="1" s="10">
       <c r="A117" s="8" t="n"/>
       <c r="B117" s="8" t="n"/>
       <c r="C117" s="8" t="n"/>
-      <c r="D117" s="8" t="n"/>
       <c r="E117" s="8" t="n"/>
       <c r="F117" s="8" t="n"/>
       <c r="G117" s="8" t="n"/>
@@ -4332,12 +4343,12 @@
       <c r="Z117" s="8" t="n"/>
       <c r="AA117" s="8" t="n"/>
       <c r="AB117" s="8" t="n"/>
+      <c r="AC117" s="8" t="n"/>
     </row>
     <row r="118" ht="16.05" customHeight="1" s="10">
       <c r="A118" s="7" t="n"/>
       <c r="B118" s="7" t="n"/>
       <c r="C118" s="7" t="n"/>
-      <c r="D118" s="7" t="n"/>
       <c r="E118" s="7" t="n"/>
       <c r="F118" s="7" t="n"/>
       <c r="G118" s="7" t="n"/>
@@ -4362,12 +4373,12 @@
       <c r="Z118" s="7" t="n"/>
       <c r="AA118" s="7" t="n"/>
       <c r="AB118" s="7" t="n"/>
+      <c r="AC118" s="7" t="n"/>
     </row>
     <row r="119" ht="16.05" customHeight="1" s="10">
       <c r="A119" s="8" t="n"/>
       <c r="B119" s="8" t="n"/>
       <c r="C119" s="8" t="n"/>
-      <c r="D119" s="8" t="n"/>
       <c r="E119" s="8" t="n"/>
       <c r="F119" s="8" t="n"/>
       <c r="G119" s="8" t="n"/>
@@ -4392,12 +4403,12 @@
       <c r="Z119" s="8" t="n"/>
       <c r="AA119" s="8" t="n"/>
       <c r="AB119" s="8" t="n"/>
+      <c r="AC119" s="8" t="n"/>
     </row>
     <row r="120" ht="16.05" customHeight="1" s="10">
       <c r="A120" s="7" t="n"/>
       <c r="B120" s="7" t="n"/>
       <c r="C120" s="7" t="n"/>
-      <c r="D120" s="7" t="n"/>
       <c r="E120" s="7" t="n"/>
       <c r="F120" s="7" t="n"/>
       <c r="G120" s="7" t="n"/>
@@ -4422,12 +4433,12 @@
       <c r="Z120" s="7" t="n"/>
       <c r="AA120" s="7" t="n"/>
       <c r="AB120" s="7" t="n"/>
+      <c r="AC120" s="7" t="n"/>
     </row>
     <row r="121" ht="16.05" customHeight="1" s="10">
       <c r="A121" s="8" t="n"/>
       <c r="B121" s="8" t="n"/>
       <c r="C121" s="8" t="n"/>
-      <c r="D121" s="8" t="n"/>
       <c r="E121" s="8" t="n"/>
       <c r="F121" s="8" t="n"/>
       <c r="G121" s="8" t="n"/>
@@ -4452,12 +4463,12 @@
       <c r="Z121" s="8" t="n"/>
       <c r="AA121" s="8" t="n"/>
       <c r="AB121" s="8" t="n"/>
+      <c r="AC121" s="8" t="n"/>
     </row>
     <row r="122" ht="16.05" customHeight="1" s="10">
       <c r="A122" s="7" t="n"/>
       <c r="B122" s="7" t="n"/>
       <c r="C122" s="7" t="n"/>
-      <c r="D122" s="7" t="n"/>
       <c r="E122" s="7" t="n"/>
       <c r="F122" s="7" t="n"/>
       <c r="G122" s="7" t="n"/>
@@ -4482,12 +4493,12 @@
       <c r="Z122" s="7" t="n"/>
       <c r="AA122" s="7" t="n"/>
       <c r="AB122" s="7" t="n"/>
+      <c r="AC122" s="7" t="n"/>
     </row>
     <row r="123" ht="16.05" customHeight="1" s="10">
       <c r="A123" s="8" t="n"/>
       <c r="B123" s="8" t="n"/>
       <c r="C123" s="8" t="n"/>
-      <c r="D123" s="8" t="n"/>
       <c r="E123" s="8" t="n"/>
       <c r="F123" s="8" t="n"/>
       <c r="G123" s="8" t="n"/>
@@ -4512,12 +4523,12 @@
       <c r="Z123" s="8" t="n"/>
       <c r="AA123" s="8" t="n"/>
       <c r="AB123" s="8" t="n"/>
+      <c r="AC123" s="8" t="n"/>
     </row>
     <row r="124" ht="16.05" customHeight="1" s="10">
       <c r="A124" s="7" t="n"/>
       <c r="B124" s="7" t="n"/>
       <c r="C124" s="7" t="n"/>
-      <c r="D124" s="7" t="n"/>
       <c r="E124" s="7" t="n"/>
       <c r="F124" s="7" t="n"/>
       <c r="G124" s="7" t="n"/>
@@ -4542,12 +4553,12 @@
       <c r="Z124" s="7" t="n"/>
       <c r="AA124" s="7" t="n"/>
       <c r="AB124" s="7" t="n"/>
+      <c r="AC124" s="7" t="n"/>
     </row>
     <row r="125" ht="16.05" customHeight="1" s="10">
       <c r="A125" s="8" t="n"/>
       <c r="B125" s="8" t="n"/>
       <c r="C125" s="8" t="n"/>
-      <c r="D125" s="8" t="n"/>
       <c r="E125" s="8" t="n"/>
       <c r="F125" s="8" t="n"/>
       <c r="G125" s="8" t="n"/>
@@ -4572,12 +4583,12 @@
       <c r="Z125" s="8" t="n"/>
       <c r="AA125" s="8" t="n"/>
       <c r="AB125" s="8" t="n"/>
+      <c r="AC125" s="8" t="n"/>
     </row>
     <row r="126" ht="16.05" customHeight="1" s="10">
       <c r="A126" s="7" t="n"/>
       <c r="B126" s="7" t="n"/>
       <c r="C126" s="7" t="n"/>
-      <c r="D126" s="7" t="n"/>
       <c r="E126" s="7" t="n"/>
       <c r="F126" s="7" t="n"/>
       <c r="G126" s="7" t="n"/>
@@ -4602,12 +4613,12 @@
       <c r="Z126" s="7" t="n"/>
       <c r="AA126" s="7" t="n"/>
       <c r="AB126" s="7" t="n"/>
+      <c r="AC126" s="7" t="n"/>
     </row>
     <row r="127" ht="16.05" customHeight="1" s="10">
       <c r="A127" s="8" t="n"/>
       <c r="B127" s="8" t="n"/>
       <c r="C127" s="8" t="n"/>
-      <c r="D127" s="8" t="n"/>
       <c r="E127" s="8" t="n"/>
       <c r="F127" s="8" t="n"/>
       <c r="G127" s="8" t="n"/>
@@ -4632,12 +4643,12 @@
       <c r="Z127" s="8" t="n"/>
       <c r="AA127" s="8" t="n"/>
       <c r="AB127" s="8" t="n"/>
+      <c r="AC127" s="8" t="n"/>
     </row>
     <row r="128" ht="16.05" customHeight="1" s="10">
       <c r="A128" s="7" t="n"/>
       <c r="B128" s="7" t="n"/>
       <c r="C128" s="7" t="n"/>
-      <c r="D128" s="7" t="n"/>
       <c r="E128" s="7" t="n"/>
       <c r="F128" s="7" t="n"/>
       <c r="G128" s="7" t="n"/>
@@ -4662,12 +4673,12 @@
       <c r="Z128" s="7" t="n"/>
       <c r="AA128" s="7" t="n"/>
       <c r="AB128" s="7" t="n"/>
+      <c r="AC128" s="7" t="n"/>
     </row>
     <row r="129" ht="16.05" customHeight="1" s="10">
       <c r="A129" s="8" t="n"/>
       <c r="B129" s="8" t="n"/>
       <c r="C129" s="8" t="n"/>
-      <c r="D129" s="8" t="n"/>
       <c r="E129" s="8" t="n"/>
       <c r="F129" s="8" t="n"/>
       <c r="G129" s="8" t="n"/>
@@ -4692,12 +4703,12 @@
       <c r="Z129" s="8" t="n"/>
       <c r="AA129" s="8" t="n"/>
       <c r="AB129" s="8" t="n"/>
+      <c r="AC129" s="8" t="n"/>
     </row>
     <row r="130" ht="16.05" customHeight="1" s="10">
       <c r="A130" s="7" t="n"/>
       <c r="B130" s="7" t="n"/>
       <c r="C130" s="7" t="n"/>
-      <c r="D130" s="7" t="n"/>
       <c r="E130" s="7" t="n"/>
       <c r="F130" s="7" t="n"/>
       <c r="G130" s="7" t="n"/>
@@ -4722,12 +4733,12 @@
       <c r="Z130" s="7" t="n"/>
       <c r="AA130" s="7" t="n"/>
       <c r="AB130" s="7" t="n"/>
+      <c r="AC130" s="7" t="n"/>
     </row>
     <row r="131" ht="16.05" customHeight="1" s="10">
       <c r="A131" s="8" t="n"/>
       <c r="B131" s="8" t="n"/>
       <c r="C131" s="8" t="n"/>
-      <c r="D131" s="8" t="n"/>
       <c r="E131" s="8" t="n"/>
       <c r="F131" s="8" t="n"/>
       <c r="G131" s="8" t="n"/>
@@ -4752,12 +4763,12 @@
       <c r="Z131" s="8" t="n"/>
       <c r="AA131" s="8" t="n"/>
       <c r="AB131" s="8" t="n"/>
+      <c r="AC131" s="8" t="n"/>
     </row>
     <row r="132" ht="16.05" customHeight="1" s="10">
       <c r="A132" s="7" t="n"/>
       <c r="B132" s="7" t="n"/>
       <c r="C132" s="7" t="n"/>
-      <c r="D132" s="7" t="n"/>
       <c r="E132" s="7" t="n"/>
       <c r="F132" s="7" t="n"/>
       <c r="G132" s="7" t="n"/>
@@ -4782,12 +4793,12 @@
       <c r="Z132" s="7" t="n"/>
       <c r="AA132" s="7" t="n"/>
       <c r="AB132" s="7" t="n"/>
+      <c r="AC132" s="7" t="n"/>
     </row>
     <row r="133" ht="16.05" customHeight="1" s="10">
       <c r="A133" s="8" t="n"/>
       <c r="B133" s="8" t="n"/>
       <c r="C133" s="8" t="n"/>
-      <c r="D133" s="8" t="n"/>
       <c r="E133" s="8" t="n"/>
       <c r="F133" s="8" t="n"/>
       <c r="G133" s="8" t="n"/>
@@ -4812,12 +4823,12 @@
       <c r="Z133" s="8" t="n"/>
       <c r="AA133" s="8" t="n"/>
       <c r="AB133" s="8" t="n"/>
+      <c r="AC133" s="8" t="n"/>
     </row>
     <row r="134" ht="16.05" customHeight="1" s="10">
       <c r="A134" s="7" t="n"/>
       <c r="B134" s="7" t="n"/>
       <c r="C134" s="7" t="n"/>
-      <c r="D134" s="7" t="n"/>
       <c r="E134" s="7" t="n"/>
       <c r="F134" s="7" t="n"/>
       <c r="G134" s="7" t="n"/>
@@ -4842,12 +4853,12 @@
       <c r="Z134" s="7" t="n"/>
       <c r="AA134" s="7" t="n"/>
       <c r="AB134" s="7" t="n"/>
+      <c r="AC134" s="7" t="n"/>
     </row>
     <row r="135" ht="16.05" customHeight="1" s="10">
       <c r="A135" s="8" t="n"/>
       <c r="B135" s="8" t="n"/>
       <c r="C135" s="8" t="n"/>
-      <c r="D135" s="8" t="n"/>
       <c r="E135" s="8" t="n"/>
       <c r="F135" s="8" t="n"/>
       <c r="G135" s="8" t="n"/>
@@ -4872,12 +4883,12 @@
       <c r="Z135" s="8" t="n"/>
       <c r="AA135" s="8" t="n"/>
       <c r="AB135" s="8" t="n"/>
+      <c r="AC135" s="8" t="n"/>
     </row>
     <row r="136" ht="16.05" customHeight="1" s="10">
       <c r="A136" s="7" t="n"/>
       <c r="B136" s="7" t="n"/>
       <c r="C136" s="7" t="n"/>
-      <c r="D136" s="7" t="n"/>
       <c r="E136" s="7" t="n"/>
       <c r="F136" s="7" t="n"/>
       <c r="G136" s="7" t="n"/>
@@ -4902,12 +4913,12 @@
       <c r="Z136" s="7" t="n"/>
       <c r="AA136" s="7" t="n"/>
       <c r="AB136" s="7" t="n"/>
+      <c r="AC136" s="7" t="n"/>
     </row>
     <row r="137" ht="16.05" customHeight="1" s="10">
       <c r="A137" s="8" t="n"/>
       <c r="B137" s="8" t="n"/>
       <c r="C137" s="8" t="n"/>
-      <c r="D137" s="8" t="n"/>
       <c r="E137" s="8" t="n"/>
       <c r="F137" s="8" t="n"/>
       <c r="G137" s="8" t="n"/>
@@ -4932,12 +4943,12 @@
       <c r="Z137" s="8" t="n"/>
       <c r="AA137" s="8" t="n"/>
       <c r="AB137" s="8" t="n"/>
+      <c r="AC137" s="8" t="n"/>
     </row>
     <row r="138" ht="16.05" customHeight="1" s="10">
       <c r="A138" s="7" t="n"/>
       <c r="B138" s="7" t="n"/>
       <c r="C138" s="7" t="n"/>
-      <c r="D138" s="7" t="n"/>
       <c r="E138" s="7" t="n"/>
       <c r="F138" s="7" t="n"/>
       <c r="G138" s="7" t="n"/>
@@ -4962,12 +4973,12 @@
       <c r="Z138" s="7" t="n"/>
       <c r="AA138" s="7" t="n"/>
       <c r="AB138" s="7" t="n"/>
+      <c r="AC138" s="7" t="n"/>
     </row>
     <row r="139" ht="16.05" customHeight="1" s="10">
       <c r="A139" s="8" t="n"/>
       <c r="B139" s="8" t="n"/>
       <c r="C139" s="8" t="n"/>
-      <c r="D139" s="8" t="n"/>
       <c r="E139" s="8" t="n"/>
       <c r="F139" s="8" t="n"/>
       <c r="G139" s="8" t="n"/>
@@ -4992,12 +5003,12 @@
       <c r="Z139" s="8" t="n"/>
       <c r="AA139" s="8" t="n"/>
       <c r="AB139" s="8" t="n"/>
+      <c r="AC139" s="8" t="n"/>
     </row>
     <row r="140" ht="16.05" customHeight="1" s="10">
       <c r="A140" s="7" t="n"/>
       <c r="B140" s="7" t="n"/>
       <c r="C140" s="7" t="n"/>
-      <c r="D140" s="7" t="n"/>
       <c r="E140" s="7" t="n"/>
       <c r="F140" s="7" t="n"/>
       <c r="G140" s="7" t="n"/>
@@ -5022,12 +5033,12 @@
       <c r="Z140" s="7" t="n"/>
       <c r="AA140" s="7" t="n"/>
       <c r="AB140" s="7" t="n"/>
+      <c r="AC140" s="7" t="n"/>
     </row>
     <row r="141" ht="16.05" customHeight="1" s="10">
       <c r="A141" s="8" t="n"/>
       <c r="B141" s="8" t="n"/>
       <c r="C141" s="8" t="n"/>
-      <c r="D141" s="8" t="n"/>
       <c r="E141" s="8" t="n"/>
       <c r="F141" s="8" t="n"/>
       <c r="G141" s="8" t="n"/>
@@ -5052,12 +5063,12 @@
       <c r="Z141" s="8" t="n"/>
       <c r="AA141" s="8" t="n"/>
       <c r="AB141" s="8" t="n"/>
+      <c r="AC141" s="8" t="n"/>
     </row>
     <row r="142" ht="16.05" customHeight="1" s="10">
       <c r="A142" s="7" t="n"/>
       <c r="B142" s="7" t="n"/>
       <c r="C142" s="7" t="n"/>
-      <c r="D142" s="7" t="n"/>
       <c r="E142" s="7" t="n"/>
       <c r="F142" s="7" t="n"/>
       <c r="G142" s="7" t="n"/>
@@ -5082,12 +5093,12 @@
       <c r="Z142" s="7" t="n"/>
       <c r="AA142" s="7" t="n"/>
       <c r="AB142" s="7" t="n"/>
+      <c r="AC142" s="7" t="n"/>
     </row>
     <row r="143" ht="16.05" customHeight="1" s="10">
       <c r="A143" s="8" t="n"/>
       <c r="B143" s="8" t="n"/>
       <c r="C143" s="8" t="n"/>
-      <c r="D143" s="8" t="n"/>
       <c r="E143" s="8" t="n"/>
       <c r="F143" s="8" t="n"/>
       <c r="G143" s="8" t="n"/>
@@ -5112,12 +5123,12 @@
       <c r="Z143" s="8" t="n"/>
       <c r="AA143" s="8" t="n"/>
       <c r="AB143" s="8" t="n"/>
+      <c r="AC143" s="8" t="n"/>
     </row>
     <row r="144" ht="16.05" customHeight="1" s="10">
       <c r="A144" s="7" t="n"/>
       <c r="B144" s="7" t="n"/>
       <c r="C144" s="7" t="n"/>
-      <c r="D144" s="7" t="n"/>
       <c r="E144" s="7" t="n"/>
       <c r="F144" s="7" t="n"/>
       <c r="G144" s="7" t="n"/>
@@ -5142,12 +5153,12 @@
       <c r="Z144" s="7" t="n"/>
       <c r="AA144" s="7" t="n"/>
       <c r="AB144" s="7" t="n"/>
+      <c r="AC144" s="7" t="n"/>
     </row>
     <row r="145" ht="16.05" customHeight="1" s="10">
       <c r="A145" s="8" t="n"/>
       <c r="B145" s="8" t="n"/>
       <c r="C145" s="8" t="n"/>
-      <c r="D145" s="8" t="n"/>
       <c r="E145" s="8" t="n"/>
       <c r="F145" s="8" t="n"/>
       <c r="G145" s="8" t="n"/>
@@ -5172,12 +5183,12 @@
       <c r="Z145" s="8" t="n"/>
       <c r="AA145" s="8" t="n"/>
       <c r="AB145" s="8" t="n"/>
+      <c r="AC145" s="8" t="n"/>
     </row>
     <row r="146" ht="16.05" customHeight="1" s="10">
       <c r="A146" s="7" t="n"/>
       <c r="B146" s="7" t="n"/>
       <c r="C146" s="7" t="n"/>
-      <c r="D146" s="7" t="n"/>
       <c r="E146" s="7" t="n"/>
       <c r="F146" s="7" t="n"/>
       <c r="G146" s="7" t="n"/>
@@ -5202,12 +5213,12 @@
       <c r="Z146" s="7" t="n"/>
       <c r="AA146" s="7" t="n"/>
       <c r="AB146" s="7" t="n"/>
+      <c r="AC146" s="7" t="n"/>
     </row>
     <row r="147" ht="16.05" customHeight="1" s="10">
       <c r="A147" s="8" t="n"/>
       <c r="B147" s="8" t="n"/>
       <c r="C147" s="8" t="n"/>
-      <c r="D147" s="8" t="n"/>
       <c r="E147" s="8" t="n"/>
       <c r="F147" s="8" t="n"/>
       <c r="G147" s="8" t="n"/>
@@ -5232,12 +5243,12 @@
       <c r="Z147" s="8" t="n"/>
       <c r="AA147" s="8" t="n"/>
       <c r="AB147" s="8" t="n"/>
+      <c r="AC147" s="8" t="n"/>
     </row>
     <row r="148" ht="16.05" customHeight="1" s="10">
       <c r="A148" s="7" t="n"/>
       <c r="B148" s="7" t="n"/>
       <c r="C148" s="7" t="n"/>
-      <c r="D148" s="7" t="n"/>
       <c r="E148" s="7" t="n"/>
       <c r="F148" s="7" t="n"/>
       <c r="G148" s="7" t="n"/>
@@ -5262,12 +5273,12 @@
       <c r="Z148" s="7" t="n"/>
       <c r="AA148" s="7" t="n"/>
       <c r="AB148" s="7" t="n"/>
+      <c r="AC148" s="7" t="n"/>
     </row>
     <row r="149" ht="16.05" customHeight="1" s="10">
       <c r="A149" s="8" t="n"/>
       <c r="B149" s="8" t="n"/>
       <c r="C149" s="8" t="n"/>
-      <c r="D149" s="8" t="n"/>
       <c r="E149" s="8" t="n"/>
       <c r="F149" s="8" t="n"/>
       <c r="G149" s="8" t="n"/>
@@ -5292,12 +5303,12 @@
       <c r="Z149" s="8" t="n"/>
       <c r="AA149" s="8" t="n"/>
       <c r="AB149" s="8" t="n"/>
+      <c r="AC149" s="8" t="n"/>
     </row>
     <row r="150" ht="16.05" customHeight="1" s="10">
       <c r="A150" s="7" t="n"/>
       <c r="B150" s="7" t="n"/>
       <c r="C150" s="7" t="n"/>
-      <c r="D150" s="7" t="n"/>
       <c r="E150" s="7" t="n"/>
       <c r="F150" s="7" t="n"/>
       <c r="G150" s="7" t="n"/>
@@ -5322,12 +5333,12 @@
       <c r="Z150" s="7" t="n"/>
       <c r="AA150" s="7" t="n"/>
       <c r="AB150" s="7" t="n"/>
+      <c r="AC150" s="7" t="n"/>
     </row>
     <row r="151" ht="16.05" customHeight="1" s="10">
       <c r="A151" s="8" t="n"/>
       <c r="B151" s="8" t="n"/>
       <c r="C151" s="8" t="n"/>
-      <c r="D151" s="8" t="n"/>
       <c r="E151" s="8" t="n"/>
       <c r="F151" s="8" t="n"/>
       <c r="G151" s="8" t="n"/>
@@ -5352,12 +5363,12 @@
       <c r="Z151" s="8" t="n"/>
       <c r="AA151" s="8" t="n"/>
       <c r="AB151" s="8" t="n"/>
+      <c r="AC151" s="8" t="n"/>
     </row>
     <row r="152" ht="16.05" customHeight="1" s="10">
       <c r="A152" s="7" t="n"/>
       <c r="B152" s="7" t="n"/>
       <c r="C152" s="7" t="n"/>
-      <c r="D152" s="7" t="n"/>
       <c r="E152" s="7" t="n"/>
       <c r="F152" s="7" t="n"/>
       <c r="G152" s="7" t="n"/>
@@ -5382,12 +5393,12 @@
       <c r="Z152" s="7" t="n"/>
       <c r="AA152" s="7" t="n"/>
       <c r="AB152" s="7" t="n"/>
+      <c r="AC152" s="7" t="n"/>
     </row>
     <row r="153" ht="16.05" customHeight="1" s="10">
       <c r="A153" s="8" t="n"/>
       <c r="B153" s="8" t="n"/>
       <c r="C153" s="8" t="n"/>
-      <c r="D153" s="8" t="n"/>
       <c r="E153" s="8" t="n"/>
       <c r="F153" s="8" t="n"/>
       <c r="G153" s="8" t="n"/>
@@ -5412,12 +5423,12 @@
       <c r="Z153" s="8" t="n"/>
       <c r="AA153" s="8" t="n"/>
       <c r="AB153" s="8" t="n"/>
+      <c r="AC153" s="8" t="n"/>
     </row>
     <row r="154" ht="16.05" customHeight="1" s="10">
       <c r="A154" s="7" t="n"/>
       <c r="B154" s="7" t="n"/>
       <c r="C154" s="7" t="n"/>
-      <c r="D154" s="7" t="n"/>
       <c r="E154" s="7" t="n"/>
       <c r="F154" s="7" t="n"/>
       <c r="G154" s="7" t="n"/>
@@ -5442,12 +5453,12 @@
       <c r="Z154" s="7" t="n"/>
       <c r="AA154" s="7" t="n"/>
       <c r="AB154" s="7" t="n"/>
+      <c r="AC154" s="7" t="n"/>
     </row>
     <row r="155" ht="16.05" customHeight="1" s="10">
       <c r="A155" s="8" t="n"/>
       <c r="B155" s="8" t="n"/>
       <c r="C155" s="8" t="n"/>
-      <c r="D155" s="8" t="n"/>
       <c r="E155" s="8" t="n"/>
       <c r="F155" s="8" t="n"/>
       <c r="G155" s="8" t="n"/>
@@ -5472,12 +5483,12 @@
       <c r="Z155" s="8" t="n"/>
       <c r="AA155" s="8" t="n"/>
       <c r="AB155" s="8" t="n"/>
+      <c r="AC155" s="8" t="n"/>
     </row>
     <row r="156" ht="16.05" customHeight="1" s="10">
       <c r="A156" s="7" t="n"/>
       <c r="B156" s="7" t="n"/>
       <c r="C156" s="7" t="n"/>
-      <c r="D156" s="7" t="n"/>
       <c r="E156" s="7" t="n"/>
       <c r="F156" s="7" t="n"/>
       <c r="G156" s="7" t="n"/>
@@ -5502,12 +5513,12 @@
       <c r="Z156" s="7" t="n"/>
       <c r="AA156" s="7" t="n"/>
       <c r="AB156" s="7" t="n"/>
+      <c r="AC156" s="7" t="n"/>
     </row>
     <row r="157" ht="16.05" customHeight="1" s="10">
       <c r="A157" s="8" t="n"/>
       <c r="B157" s="8" t="n"/>
       <c r="C157" s="8" t="n"/>
-      <c r="D157" s="8" t="n"/>
       <c r="E157" s="8" t="n"/>
       <c r="F157" s="8" t="n"/>
       <c r="G157" s="8" t="n"/>
@@ -5532,12 +5543,12 @@
       <c r="Z157" s="8" t="n"/>
       <c r="AA157" s="8" t="n"/>
       <c r="AB157" s="8" t="n"/>
+      <c r="AC157" s="8" t="n"/>
     </row>
     <row r="158" ht="16.05" customHeight="1" s="10">
       <c r="A158" s="7" t="n"/>
       <c r="B158" s="7" t="n"/>
       <c r="C158" s="7" t="n"/>
-      <c r="D158" s="7" t="n"/>
       <c r="E158" s="7" t="n"/>
       <c r="F158" s="7" t="n"/>
       <c r="G158" s="7" t="n"/>
@@ -5562,12 +5573,12 @@
       <c r="Z158" s="7" t="n"/>
       <c r="AA158" s="7" t="n"/>
       <c r="AB158" s="7" t="n"/>
+      <c r="AC158" s="7" t="n"/>
     </row>
     <row r="159" ht="16.05" customHeight="1" s="10">
       <c r="A159" s="8" t="n"/>
       <c r="B159" s="8" t="n"/>
       <c r="C159" s="8" t="n"/>
-      <c r="D159" s="8" t="n"/>
       <c r="E159" s="8" t="n"/>
       <c r="F159" s="8" t="n"/>
       <c r="G159" s="8" t="n"/>
@@ -5592,12 +5603,12 @@
       <c r="Z159" s="8" t="n"/>
       <c r="AA159" s="8" t="n"/>
       <c r="AB159" s="8" t="n"/>
+      <c r="AC159" s="8" t="n"/>
     </row>
     <row r="160" ht="16.05" customHeight="1" s="10">
       <c r="A160" s="7" t="n"/>
       <c r="B160" s="7" t="n"/>
       <c r="C160" s="7" t="n"/>
-      <c r="D160" s="7" t="n"/>
       <c r="E160" s="7" t="n"/>
       <c r="F160" s="7" t="n"/>
       <c r="G160" s="7" t="n"/>
@@ -5622,12 +5633,12 @@
       <c r="Z160" s="7" t="n"/>
       <c r="AA160" s="7" t="n"/>
       <c r="AB160" s="7" t="n"/>
+      <c r="AC160" s="7" t="n"/>
     </row>
     <row r="161" ht="16.05" customHeight="1" s="10">
       <c r="A161" s="8" t="n"/>
       <c r="B161" s="8" t="n"/>
       <c r="C161" s="8" t="n"/>
-      <c r="D161" s="8" t="n"/>
       <c r="E161" s="8" t="n"/>
       <c r="F161" s="8" t="n"/>
       <c r="G161" s="8" t="n"/>
@@ -5652,12 +5663,12 @@
       <c r="Z161" s="8" t="n"/>
       <c r="AA161" s="8" t="n"/>
       <c r="AB161" s="8" t="n"/>
+      <c r="AC161" s="8" t="n"/>
     </row>
     <row r="162" ht="16.05" customHeight="1" s="10">
       <c r="A162" s="7" t="n"/>
       <c r="B162" s="7" t="n"/>
       <c r="C162" s="7" t="n"/>
-      <c r="D162" s="7" t="n"/>
       <c r="E162" s="7" t="n"/>
       <c r="F162" s="7" t="n"/>
       <c r="G162" s="7" t="n"/>
@@ -5682,12 +5693,12 @@
       <c r="Z162" s="7" t="n"/>
       <c r="AA162" s="7" t="n"/>
       <c r="AB162" s="7" t="n"/>
+      <c r="AC162" s="7" t="n"/>
     </row>
     <row r="163" ht="16.05" customHeight="1" s="10">
       <c r="A163" s="8" t="n"/>
       <c r="B163" s="8" t="n"/>
       <c r="C163" s="8" t="n"/>
-      <c r="D163" s="8" t="n"/>
       <c r="E163" s="8" t="n"/>
       <c r="F163" s="8" t="n"/>
       <c r="G163" s="8" t="n"/>
@@ -5712,12 +5723,12 @@
       <c r="Z163" s="8" t="n"/>
       <c r="AA163" s="8" t="n"/>
       <c r="AB163" s="8" t="n"/>
+      <c r="AC163" s="8" t="n"/>
     </row>
     <row r="164" ht="16.05" customHeight="1" s="10">
       <c r="A164" s="7" t="n"/>
       <c r="B164" s="7" t="n"/>
       <c r="C164" s="7" t="n"/>
-      <c r="D164" s="7" t="n"/>
       <c r="E164" s="7" t="n"/>
       <c r="F164" s="7" t="n"/>
       <c r="G164" s="7" t="n"/>
@@ -5742,12 +5753,12 @@
       <c r="Z164" s="7" t="n"/>
       <c r="AA164" s="7" t="n"/>
       <c r="AB164" s="7" t="n"/>
+      <c r="AC164" s="7" t="n"/>
     </row>
     <row r="165" ht="16.05" customHeight="1" s="10">
       <c r="A165" s="8" t="n"/>
       <c r="B165" s="8" t="n"/>
       <c r="C165" s="8" t="n"/>
-      <c r="D165" s="8" t="n"/>
       <c r="E165" s="8" t="n"/>
       <c r="F165" s="8" t="n"/>
       <c r="G165" s="8" t="n"/>
@@ -5772,12 +5783,12 @@
       <c r="Z165" s="8" t="n"/>
       <c r="AA165" s="8" t="n"/>
       <c r="AB165" s="8" t="n"/>
+      <c r="AC165" s="8" t="n"/>
     </row>
     <row r="166" ht="16.05" customHeight="1" s="10">
       <c r="A166" s="7" t="n"/>
       <c r="B166" s="7" t="n"/>
       <c r="C166" s="7" t="n"/>
-      <c r="D166" s="7" t="n"/>
       <c r="E166" s="7" t="n"/>
       <c r="F166" s="7" t="n"/>
       <c r="G166" s="7" t="n"/>
@@ -5802,12 +5813,12 @@
       <c r="Z166" s="7" t="n"/>
       <c r="AA166" s="7" t="n"/>
       <c r="AB166" s="7" t="n"/>
+      <c r="AC166" s="7" t="n"/>
     </row>
     <row r="167" ht="16.05" customHeight="1" s="10">
       <c r="A167" s="8" t="n"/>
       <c r="B167" s="8" t="n"/>
       <c r="C167" s="8" t="n"/>
-      <c r="D167" s="8" t="n"/>
       <c r="E167" s="8" t="n"/>
       <c r="F167" s="8" t="n"/>
       <c r="G167" s="8" t="n"/>
@@ -5832,12 +5843,12 @@
       <c r="Z167" s="8" t="n"/>
       <c r="AA167" s="8" t="n"/>
       <c r="AB167" s="8" t="n"/>
+      <c r="AC167" s="8" t="n"/>
     </row>
     <row r="168" ht="16.05" customHeight="1" s="10">
       <c r="A168" s="7" t="n"/>
       <c r="B168" s="7" t="n"/>
       <c r="C168" s="7" t="n"/>
-      <c r="D168" s="7" t="n"/>
       <c r="E168" s="7" t="n"/>
       <c r="F168" s="7" t="n"/>
       <c r="G168" s="7" t="n"/>
@@ -5862,12 +5873,12 @@
       <c r="Z168" s="7" t="n"/>
       <c r="AA168" s="7" t="n"/>
       <c r="AB168" s="7" t="n"/>
+      <c r="AC168" s="7" t="n"/>
     </row>
     <row r="169" ht="16.05" customHeight="1" s="10">
       <c r="A169" s="8" t="n"/>
       <c r="B169" s="8" t="n"/>
       <c r="C169" s="8" t="n"/>
-      <c r="D169" s="8" t="n"/>
       <c r="E169" s="8" t="n"/>
       <c r="F169" s="8" t="n"/>
       <c r="G169" s="8" t="n"/>
@@ -5892,12 +5903,12 @@
       <c r="Z169" s="8" t="n"/>
       <c r="AA169" s="8" t="n"/>
       <c r="AB169" s="8" t="n"/>
+      <c r="AC169" s="8" t="n"/>
     </row>
     <row r="170" ht="16.05" customHeight="1" s="10">
       <c r="A170" s="7" t="n"/>
       <c r="B170" s="7" t="n"/>
       <c r="C170" s="7" t="n"/>
-      <c r="D170" s="7" t="n"/>
       <c r="E170" s="7" t="n"/>
       <c r="F170" s="7" t="n"/>
       <c r="G170" s="7" t="n"/>
@@ -5922,12 +5933,12 @@
       <c r="Z170" s="7" t="n"/>
       <c r="AA170" s="7" t="n"/>
       <c r="AB170" s="7" t="n"/>
+      <c r="AC170" s="7" t="n"/>
     </row>
     <row r="171" ht="16.05" customHeight="1" s="10">
       <c r="A171" s="8" t="n"/>
       <c r="B171" s="8" t="n"/>
       <c r="C171" s="8" t="n"/>
-      <c r="D171" s="8" t="n"/>
       <c r="E171" s="8" t="n"/>
       <c r="F171" s="8" t="n"/>
       <c r="G171" s="8" t="n"/>
@@ -5952,12 +5963,12 @@
       <c r="Z171" s="8" t="n"/>
       <c r="AA171" s="8" t="n"/>
       <c r="AB171" s="8" t="n"/>
+      <c r="AC171" s="8" t="n"/>
     </row>
     <row r="172" ht="16.05" customHeight="1" s="10">
       <c r="A172" s="7" t="n"/>
       <c r="B172" s="7" t="n"/>
       <c r="C172" s="7" t="n"/>
-      <c r="D172" s="7" t="n"/>
       <c r="E172" s="7" t="n"/>
       <c r="F172" s="7" t="n"/>
       <c r="G172" s="7" t="n"/>
@@ -5982,12 +5993,12 @@
       <c r="Z172" s="7" t="n"/>
       <c r="AA172" s="7" t="n"/>
       <c r="AB172" s="7" t="n"/>
+      <c r="AC172" s="7" t="n"/>
     </row>
     <row r="173" ht="16.05" customHeight="1" s="10">
       <c r="A173" s="8" t="n"/>
       <c r="B173" s="8" t="n"/>
       <c r="C173" s="8" t="n"/>
-      <c r="D173" s="8" t="n"/>
       <c r="E173" s="8" t="n"/>
       <c r="F173" s="8" t="n"/>
       <c r="G173" s="8" t="n"/>
@@ -6012,12 +6023,12 @@
       <c r="Z173" s="8" t="n"/>
       <c r="AA173" s="8" t="n"/>
       <c r="AB173" s="8" t="n"/>
+      <c r="AC173" s="8" t="n"/>
     </row>
     <row r="174" ht="16.05" customHeight="1" s="10">
       <c r="A174" s="7" t="n"/>
       <c r="B174" s="7" t="n"/>
       <c r="C174" s="7" t="n"/>
-      <c r="D174" s="7" t="n"/>
       <c r="E174" s="7" t="n"/>
       <c r="F174" s="7" t="n"/>
       <c r="G174" s="7" t="n"/>
@@ -6042,12 +6053,12 @@
       <c r="Z174" s="7" t="n"/>
       <c r="AA174" s="7" t="n"/>
       <c r="AB174" s="7" t="n"/>
+      <c r="AC174" s="7" t="n"/>
     </row>
     <row r="175" ht="16.05" customHeight="1" s="10">
       <c r="A175" s="8" t="n"/>
       <c r="B175" s="8" t="n"/>
       <c r="C175" s="8" t="n"/>
-      <c r="D175" s="8" t="n"/>
       <c r="E175" s="8" t="n"/>
       <c r="F175" s="8" t="n"/>
       <c r="G175" s="8" t="n"/>
@@ -6072,12 +6083,12 @@
       <c r="Z175" s="8" t="n"/>
       <c r="AA175" s="8" t="n"/>
       <c r="AB175" s="8" t="n"/>
+      <c r="AC175" s="8" t="n"/>
     </row>
     <row r="176" ht="16.05" customHeight="1" s="10">
       <c r="A176" s="7" t="n"/>
       <c r="B176" s="7" t="n"/>
       <c r="C176" s="7" t="n"/>
-      <c r="D176" s="7" t="n"/>
       <c r="E176" s="7" t="n"/>
       <c r="F176" s="7" t="n"/>
       <c r="G176" s="7" t="n"/>
@@ -6102,12 +6113,12 @@
       <c r="Z176" s="7" t="n"/>
       <c r="AA176" s="7" t="n"/>
       <c r="AB176" s="7" t="n"/>
+      <c r="AC176" s="7" t="n"/>
     </row>
     <row r="177" ht="16.05" customHeight="1" s="10">
       <c r="A177" s="8" t="n"/>
       <c r="B177" s="8" t="n"/>
       <c r="C177" s="8" t="n"/>
-      <c r="D177" s="8" t="n"/>
       <c r="E177" s="8" t="n"/>
       <c r="F177" s="8" t="n"/>
       <c r="G177" s="8" t="n"/>
@@ -6132,12 +6143,12 @@
       <c r="Z177" s="8" t="n"/>
       <c r="AA177" s="8" t="n"/>
       <c r="AB177" s="8" t="n"/>
+      <c r="AC177" s="8" t="n"/>
     </row>
     <row r="178" ht="16.05" customHeight="1" s="10">
       <c r="A178" s="7" t="n"/>
       <c r="B178" s="7" t="n"/>
       <c r="C178" s="7" t="n"/>
-      <c r="D178" s="7" t="n"/>
       <c r="E178" s="7" t="n"/>
       <c r="F178" s="7" t="n"/>
       <c r="G178" s="7" t="n"/>
@@ -6162,12 +6173,12 @@
       <c r="Z178" s="7" t="n"/>
       <c r="AA178" s="7" t="n"/>
       <c r="AB178" s="7" t="n"/>
+      <c r="AC178" s="7" t="n"/>
     </row>
     <row r="179" ht="16.05" customHeight="1" s="10">
       <c r="A179" s="8" t="n"/>
       <c r="B179" s="8" t="n"/>
       <c r="C179" s="8" t="n"/>
-      <c r="D179" s="8" t="n"/>
       <c r="E179" s="8" t="n"/>
       <c r="F179" s="8" t="n"/>
       <c r="G179" s="8" t="n"/>
@@ -6192,12 +6203,12 @@
       <c r="Z179" s="8" t="n"/>
       <c r="AA179" s="8" t="n"/>
       <c r="AB179" s="8" t="n"/>
+      <c r="AC179" s="8" t="n"/>
     </row>
     <row r="180" ht="16.05" customHeight="1" s="10">
       <c r="A180" s="7" t="n"/>
       <c r="B180" s="7" t="n"/>
       <c r="C180" s="7" t="n"/>
-      <c r="D180" s="7" t="n"/>
       <c r="E180" s="7" t="n"/>
       <c r="F180" s="7" t="n"/>
       <c r="G180" s="7" t="n"/>
@@ -6222,12 +6233,12 @@
       <c r="Z180" s="7" t="n"/>
       <c r="AA180" s="7" t="n"/>
       <c r="AB180" s="7" t="n"/>
+      <c r="AC180" s="7" t="n"/>
     </row>
     <row r="181" ht="16.05" customHeight="1" s="10">
       <c r="A181" s="8" t="n"/>
       <c r="B181" s="8" t="n"/>
       <c r="C181" s="8" t="n"/>
-      <c r="D181" s="8" t="n"/>
       <c r="E181" s="8" t="n"/>
       <c r="F181" s="8" t="n"/>
       <c r="G181" s="8" t="n"/>
@@ -6252,12 +6263,12 @@
       <c r="Z181" s="8" t="n"/>
       <c r="AA181" s="8" t="n"/>
       <c r="AB181" s="8" t="n"/>
+      <c r="AC181" s="8" t="n"/>
     </row>
     <row r="182" ht="16.05" customHeight="1" s="10">
       <c r="A182" s="7" t="n"/>
       <c r="B182" s="7" t="n"/>
       <c r="C182" s="7" t="n"/>
-      <c r="D182" s="7" t="n"/>
       <c r="E182" s="7" t="n"/>
       <c r="F182" s="7" t="n"/>
       <c r="G182" s="7" t="n"/>
@@ -6282,12 +6293,12 @@
       <c r="Z182" s="7" t="n"/>
       <c r="AA182" s="7" t="n"/>
       <c r="AB182" s="7" t="n"/>
+      <c r="AC182" s="7" t="n"/>
     </row>
     <row r="183" ht="16.05" customHeight="1" s="10">
       <c r="A183" s="8" t="n"/>
       <c r="B183" s="8" t="n"/>
       <c r="C183" s="8" t="n"/>
-      <c r="D183" s="8" t="n"/>
       <c r="E183" s="8" t="n"/>
       <c r="F183" s="8" t="n"/>
       <c r="G183" s="8" t="n"/>
@@ -6312,12 +6323,12 @@
       <c r="Z183" s="8" t="n"/>
       <c r="AA183" s="8" t="n"/>
       <c r="AB183" s="8" t="n"/>
+      <c r="AC183" s="8" t="n"/>
     </row>
     <row r="184" ht="16.05" customHeight="1" s="10">
       <c r="A184" s="7" t="n"/>
       <c r="B184" s="7" t="n"/>
       <c r="C184" s="7" t="n"/>
-      <c r="D184" s="7" t="n"/>
       <c r="E184" s="7" t="n"/>
       <c r="F184" s="7" t="n"/>
       <c r="G184" s="7" t="n"/>
@@ -6342,12 +6353,12 @@
       <c r="Z184" s="7" t="n"/>
       <c r="AA184" s="7" t="n"/>
       <c r="AB184" s="7" t="n"/>
+      <c r="AC184" s="7" t="n"/>
     </row>
     <row r="185" ht="16.05" customHeight="1" s="10">
       <c r="A185" s="8" t="n"/>
       <c r="B185" s="8" t="n"/>
       <c r="C185" s="8" t="n"/>
-      <c r="D185" s="8" t="n"/>
       <c r="E185" s="8" t="n"/>
       <c r="F185" s="8" t="n"/>
       <c r="G185" s="8" t="n"/>
@@ -6372,12 +6383,12 @@
       <c r="Z185" s="8" t="n"/>
       <c r="AA185" s="8" t="n"/>
       <c r="AB185" s="8" t="n"/>
+      <c r="AC185" s="8" t="n"/>
     </row>
     <row r="186" ht="16.05" customHeight="1" s="10">
       <c r="A186" s="7" t="n"/>
       <c r="B186" s="7" t="n"/>
       <c r="C186" s="7" t="n"/>
-      <c r="D186" s="7" t="n"/>
       <c r="E186" s="7" t="n"/>
       <c r="F186" s="7" t="n"/>
       <c r="G186" s="7" t="n"/>
@@ -6402,12 +6413,12 @@
       <c r="Z186" s="7" t="n"/>
       <c r="AA186" s="7" t="n"/>
       <c r="AB186" s="7" t="n"/>
+      <c r="AC186" s="7" t="n"/>
     </row>
     <row r="187" ht="16.05" customHeight="1" s="10">
       <c r="A187" s="8" t="n"/>
       <c r="B187" s="8" t="n"/>
       <c r="C187" s="8" t="n"/>
-      <c r="D187" s="8" t="n"/>
       <c r="E187" s="8" t="n"/>
       <c r="F187" s="8" t="n"/>
       <c r="G187" s="8" t="n"/>
@@ -6432,12 +6443,12 @@
       <c r="Z187" s="8" t="n"/>
       <c r="AA187" s="8" t="n"/>
       <c r="AB187" s="8" t="n"/>
+      <c r="AC187" s="8" t="n"/>
     </row>
     <row r="188" ht="16.05" customHeight="1" s="10">
       <c r="A188" s="7" t="n"/>
       <c r="B188" s="7" t="n"/>
       <c r="C188" s="7" t="n"/>
-      <c r="D188" s="7" t="n"/>
       <c r="E188" s="7" t="n"/>
       <c r="F188" s="7" t="n"/>
       <c r="G188" s="7" t="n"/>
@@ -6462,12 +6473,12 @@
       <c r="Z188" s="7" t="n"/>
       <c r="AA188" s="7" t="n"/>
       <c r="AB188" s="7" t="n"/>
+      <c r="AC188" s="7" t="n"/>
     </row>
     <row r="189" ht="16.05" customHeight="1" s="10">
       <c r="A189" s="8" t="n"/>
       <c r="B189" s="8" t="n"/>
       <c r="C189" s="8" t="n"/>
-      <c r="D189" s="8" t="n"/>
       <c r="E189" s="8" t="n"/>
       <c r="F189" s="8" t="n"/>
       <c r="G189" s="8" t="n"/>
@@ -6492,12 +6503,12 @@
       <c r="Z189" s="8" t="n"/>
       <c r="AA189" s="8" t="n"/>
       <c r="AB189" s="8" t="n"/>
+      <c r="AC189" s="8" t="n"/>
     </row>
     <row r="190" ht="16.05" customHeight="1" s="10">
       <c r="A190" s="7" t="n"/>
       <c r="B190" s="7" t="n"/>
       <c r="C190" s="7" t="n"/>
-      <c r="D190" s="7" t="n"/>
       <c r="E190" s="7" t="n"/>
       <c r="F190" s="7" t="n"/>
       <c r="G190" s="7" t="n"/>
@@ -6522,12 +6533,12 @@
       <c r="Z190" s="7" t="n"/>
       <c r="AA190" s="7" t="n"/>
       <c r="AB190" s="7" t="n"/>
+      <c r="AC190" s="7" t="n"/>
     </row>
     <row r="191" ht="16.05" customHeight="1" s="10">
       <c r="A191" s="8" t="n"/>
       <c r="B191" s="8" t="n"/>
       <c r="C191" s="8" t="n"/>
-      <c r="D191" s="8" t="n"/>
       <c r="E191" s="8" t="n"/>
       <c r="F191" s="8" t="n"/>
       <c r="G191" s="8" t="n"/>
@@ -6552,12 +6563,12 @@
       <c r="Z191" s="8" t="n"/>
       <c r="AA191" s="8" t="n"/>
       <c r="AB191" s="8" t="n"/>
+      <c r="AC191" s="8" t="n"/>
     </row>
     <row r="192" ht="16.05" customHeight="1" s="10">
       <c r="A192" s="7" t="n"/>
       <c r="B192" s="7" t="n"/>
       <c r="C192" s="7" t="n"/>
-      <c r="D192" s="7" t="n"/>
       <c r="E192" s="7" t="n"/>
       <c r="F192" s="7" t="n"/>
       <c r="G192" s="7" t="n"/>
@@ -6582,12 +6593,12 @@
       <c r="Z192" s="7" t="n"/>
       <c r="AA192" s="7" t="n"/>
       <c r="AB192" s="7" t="n"/>
+      <c r="AC192" s="7" t="n"/>
     </row>
     <row r="193" ht="16.05" customHeight="1" s="10">
       <c r="A193" s="8" t="n"/>
       <c r="B193" s="8" t="n"/>
       <c r="C193" s="8" t="n"/>
-      <c r="D193" s="8" t="n"/>
       <c r="E193" s="8" t="n"/>
       <c r="F193" s="8" t="n"/>
       <c r="G193" s="8" t="n"/>
@@ -6612,12 +6623,12 @@
       <c r="Z193" s="8" t="n"/>
       <c r="AA193" s="8" t="n"/>
       <c r="AB193" s="8" t="n"/>
+      <c r="AC193" s="8" t="n"/>
     </row>
     <row r="194" ht="16.05" customHeight="1" s="10">
       <c r="A194" s="7" t="n"/>
       <c r="B194" s="7" t="n"/>
       <c r="C194" s="7" t="n"/>
-      <c r="D194" s="7" t="n"/>
       <c r="E194" s="7" t="n"/>
       <c r="F194" s="7" t="n"/>
       <c r="G194" s="7" t="n"/>
@@ -6642,12 +6653,12 @@
       <c r="Z194" s="7" t="n"/>
       <c r="AA194" s="7" t="n"/>
       <c r="AB194" s="7" t="n"/>
+      <c r="AC194" s="7" t="n"/>
     </row>
     <row r="195" ht="16.05" customHeight="1" s="10">
       <c r="A195" s="8" t="n"/>
       <c r="B195" s="8" t="n"/>
       <c r="C195" s="8" t="n"/>
-      <c r="D195" s="8" t="n"/>
       <c r="E195" s="8" t="n"/>
       <c r="F195" s="8" t="n"/>
       <c r="G195" s="8" t="n"/>
@@ -6672,12 +6683,12 @@
       <c r="Z195" s="8" t="n"/>
       <c r="AA195" s="8" t="n"/>
       <c r="AB195" s="8" t="n"/>
+      <c r="AC195" s="8" t="n"/>
     </row>
     <row r="196" ht="16.05" customHeight="1" s="10">
       <c r="A196" s="7" t="n"/>
       <c r="B196" s="7" t="n"/>
       <c r="C196" s="7" t="n"/>
-      <c r="D196" s="7" t="n"/>
       <c r="E196" s="7" t="n"/>
       <c r="F196" s="7" t="n"/>
       <c r="G196" s="7" t="n"/>
@@ -6702,12 +6713,12 @@
       <c r="Z196" s="7" t="n"/>
       <c r="AA196" s="7" t="n"/>
       <c r="AB196" s="7" t="n"/>
+      <c r="AC196" s="7" t="n"/>
     </row>
     <row r="197" ht="16.05" customHeight="1" s="10">
       <c r="A197" s="8" t="n"/>
       <c r="B197" s="8" t="n"/>
       <c r="C197" s="8" t="n"/>
-      <c r="D197" s="8" t="n"/>
       <c r="E197" s="8" t="n"/>
       <c r="F197" s="8" t="n"/>
       <c r="G197" s="8" t="n"/>
@@ -6732,12 +6743,12 @@
       <c r="Z197" s="8" t="n"/>
       <c r="AA197" s="8" t="n"/>
       <c r="AB197" s="8" t="n"/>
+      <c r="AC197" s="8" t="n"/>
     </row>
     <row r="198" ht="16.05" customHeight="1" s="10">
       <c r="A198" s="7" t="n"/>
       <c r="B198" s="7" t="n"/>
       <c r="C198" s="7" t="n"/>
-      <c r="D198" s="7" t="n"/>
       <c r="E198" s="7" t="n"/>
       <c r="F198" s="7" t="n"/>
       <c r="G198" s="7" t="n"/>
@@ -6762,12 +6773,12 @@
       <c r="Z198" s="7" t="n"/>
       <c r="AA198" s="7" t="n"/>
       <c r="AB198" s="7" t="n"/>
+      <c r="AC198" s="7" t="n"/>
     </row>
     <row r="199" ht="16.05" customHeight="1" s="10">
       <c r="A199" s="8" t="n"/>
       <c r="B199" s="8" t="n"/>
       <c r="C199" s="8" t="n"/>
-      <c r="D199" s="8" t="n"/>
       <c r="E199" s="8" t="n"/>
       <c r="F199" s="8" t="n"/>
       <c r="G199" s="8" t="n"/>
@@ -6792,12 +6803,12 @@
       <c r="Z199" s="8" t="n"/>
       <c r="AA199" s="8" t="n"/>
       <c r="AB199" s="8" t="n"/>
+      <c r="AC199" s="8" t="n"/>
     </row>
     <row r="200" ht="16.05" customHeight="1" s="10">
       <c r="A200" s="7" t="n"/>
       <c r="B200" s="7" t="n"/>
       <c r="C200" s="7" t="n"/>
-      <c r="D200" s="7" t="n"/>
       <c r="E200" s="7" t="n"/>
       <c r="F200" s="7" t="n"/>
       <c r="G200" s="7" t="n"/>
@@ -6822,12 +6833,12 @@
       <c r="Z200" s="7" t="n"/>
       <c r="AA200" s="7" t="n"/>
       <c r="AB200" s="7" t="n"/>
+      <c r="AC200" s="7" t="n"/>
     </row>
     <row r="201" ht="16.05" customHeight="1" s="10">
       <c r="A201" s="8" t="n"/>
       <c r="B201" s="8" t="n"/>
       <c r="C201" s="8" t="n"/>
-      <c r="D201" s="8" t="n"/>
       <c r="E201" s="8" t="n"/>
       <c r="F201" s="8" t="n"/>
       <c r="G201" s="8" t="n"/>
@@ -6852,12 +6863,12 @@
       <c r="Z201" s="8" t="n"/>
       <c r="AA201" s="8" t="n"/>
       <c r="AB201" s="8" t="n"/>
+      <c r="AC201" s="8" t="n"/>
     </row>
     <row r="202" ht="16.05" customHeight="1" s="10">
       <c r="A202" s="7" t="n"/>
       <c r="B202" s="7" t="n"/>
       <c r="C202" s="7" t="n"/>
-      <c r="D202" s="7" t="n"/>
       <c r="E202" s="7" t="n"/>
       <c r="F202" s="7" t="n"/>
       <c r="G202" s="7" t="n"/>
@@ -6882,12 +6893,12 @@
       <c r="Z202" s="7" t="n"/>
       <c r="AA202" s="7" t="n"/>
       <c r="AB202" s="7" t="n"/>
+      <c r="AC202" s="7" t="n"/>
     </row>
     <row r="203" ht="16.05" customHeight="1" s="10">
       <c r="A203" s="8" t="n"/>
       <c r="B203" s="8" t="n"/>
       <c r="C203" s="8" t="n"/>
-      <c r="D203" s="8" t="n"/>
       <c r="E203" s="8" t="n"/>
       <c r="F203" s="8" t="n"/>
       <c r="G203" s="8" t="n"/>
@@ -6912,10 +6923,11 @@
       <c r="Z203" s="8" t="n"/>
       <c r="AA203" s="8" t="n"/>
       <c r="AB203" s="8" t="n"/>
+      <c r="AC203" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="A1:AC1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -6950,7 +6962,7 @@
     <row r="1" ht="19.95" customHeight="1" s="10">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>MAX_IMPORTA  |  Clientes / Fornecedores  (INSERT = sem cliId / UPDATE = cliId obrigatorio  |  cliId minimo: 11)</t>
+          <t>MAX_IMPORTA  |  Clientes / Fornecedores    INSERT = sem cliId (cliId minimo: 11)  |  UPDATE = so o cliId (ou o cliCpfCgc) e obrigatorio; celula VAZIA mantem o valor do banco</t>
         </is>
       </c>
     </row>
@@ -10992,7 +11004,7 @@
     <row r="1" ht="19.95" customHeight="1" s="10">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>MAX_IMPORTA  |  Financeiro vendaPgto  (somente INSERT  |  cliCpfCgc deve existir na tabela cliente)</t>
+          <t>MAX_IMPORTA  |  Financeiro vendaPgto    somente INSERT  |  cliCpfCgc deve existir na tabela cliente  |  pgtPago: S = Concluido / N = Aberto</t>
         </is>
       </c>
     </row>

--- a/MaxImporta_Modelos_Importacao.xlsx
+++ b/MaxImporta_Modelos_Importacao.xlsx
@@ -567,21 +567,22 @@
     <col width="22" customWidth="1" style="10" min="2" max="2"/>
     <col width="14" customWidth="1" style="10" min="3" max="3"/>
     <col width="16" customWidth="1" style="10" min="4" max="4"/>
-    <col width="14" customWidth="1" style="10" min="5" max="11"/>
-    <col width="18" customWidth="1" style="10" min="12" max="12"/>
-    <col width="14" customWidth="1" style="10" min="13" max="13"/>
-    <col width="15" customWidth="1" style="10" min="14" max="14"/>
-    <col width="14" customWidth="1" style="10" min="15" max="16"/>
-    <col width="17" customWidth="1" style="10" min="17" max="18"/>
-    <col width="16" customWidth="1" style="10" min="19" max="20"/>
-    <col width="15" customWidth="1" style="10" min="21" max="21"/>
-    <col width="16" customWidth="1" style="10" min="22" max="22"/>
-    <col width="19" customWidth="1" style="10" min="23" max="23"/>
-    <col width="14" customWidth="1" style="10" min="24" max="24"/>
-    <col width="20" customWidth="1" style="10" min="25" max="25"/>
-    <col width="18" customWidth="1" style="10" min="26" max="26"/>
-    <col width="21" customWidth="1" style="10" min="27" max="27"/>
-    <col width="14" customWidth="1" style="10" min="28" max="28"/>
+    <col width="14" customWidth="1" style="10" min="5" max="5"/>
+    <col width="14" customWidth="1" style="10" min="7" max="7"/>
+    <col width="18" customWidth="1" style="10" min="13" max="13"/>
+    <col width="14" customWidth="1" style="10" min="14" max="14"/>
+    <col width="15" customWidth="1" style="10" min="15" max="15"/>
+    <col width="14" customWidth="1" style="10" min="16" max="16"/>
+    <col width="17" customWidth="1" style="10" min="18" max="18"/>
+    <col width="16" customWidth="1" style="10" min="20" max="20"/>
+    <col width="15" customWidth="1" style="10" min="22" max="22"/>
+    <col width="16" customWidth="1" style="10" min="23" max="23"/>
+    <col width="19" customWidth="1" style="10" min="24" max="24"/>
+    <col width="14" customWidth="1" style="10" min="25" max="25"/>
+    <col width="20" customWidth="1" style="10" min="26" max="26"/>
+    <col width="18" customWidth="1" style="10" min="27" max="27"/>
+    <col width="21" customWidth="1" style="10" min="28" max="28"/>
+    <col width="14" customWidth="1" style="10" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1" ht="19.95" customHeight="1" s="10">
@@ -611,31 +612,31 @@
 (máx. 2 caracteres)</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Cód. CST1 — origem
-(um dígito de 0 a 9)
-0 = Nacional</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Código Interno
 do Produto
 (máx. 50 caracteres)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Unidade
 (ex: PC, KG, CX)
 (máx. 10 caracteres)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Código NCM
 (máx. 10 caracteres)</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Cód. CST1
+(origem: 0 a 9)
+(0 = Nacional)</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -794,24 +795,24 @@
           <t>proCodCst2</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>proCodCst1</t>
+          <t>proCodigo</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>proCodigo</t>
+          <t>proUn</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>proUn</t>
+          <t>ncmCodigoNCM</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>ncmCodigoNCM</t>
+          <t>proCodCst1</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
@@ -929,9 +930,9 @@
       <c r="A4" s="7" t="n"/>
       <c r="B4" s="7" t="n"/>
       <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
       <c r="E4" s="7" t="n"/>
       <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
       <c r="J4" s="7" t="n"/>
@@ -959,9 +960,9 @@
       <c r="A5" s="8" t="n"/>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
       <c r="E5" s="8" t="n"/>
       <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
       <c r="H5" s="8" t="n"/>
       <c r="I5" s="8" t="n"/>
       <c r="J5" s="8" t="n"/>
@@ -989,9 +990,9 @@
       <c r="A6" s="7" t="n"/>
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
       <c r="J6" s="7" t="n"/>
@@ -1019,9 +1020,9 @@
       <c r="A7" s="8" t="n"/>
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
-      <c r="G7" s="8" t="n"/>
       <c r="H7" s="8" t="n"/>
       <c r="I7" s="8" t="n"/>
       <c r="J7" s="8" t="n"/>
@@ -1049,9 +1050,9 @@
       <c r="A8" s="7" t="n"/>
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="7" t="n"/>
       <c r="J8" s="7" t="n"/>
@@ -1079,9 +1080,9 @@
       <c r="A9" s="8" t="n"/>
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
       <c r="H9" s="8" t="n"/>
       <c r="I9" s="8" t="n"/>
       <c r="J9" s="8" t="n"/>
@@ -1109,9 +1110,9 @@
       <c r="A10" s="7" t="n"/>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="7" t="n"/>
       <c r="J10" s="7" t="n"/>
@@ -1139,9 +1140,9 @@
       <c r="A11" s="8" t="n"/>
       <c r="B11" s="8" t="n"/>
       <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
       <c r="H11" s="8" t="n"/>
       <c r="I11" s="8" t="n"/>
       <c r="J11" s="8" t="n"/>
@@ -1169,9 +1170,9 @@
       <c r="A12" s="7" t="n"/>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
       <c r="H12" s="7" t="n"/>
       <c r="I12" s="7" t="n"/>
       <c r="J12" s="7" t="n"/>
@@ -1199,9 +1200,9 @@
       <c r="A13" s="8" t="n"/>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="n"/>
       <c r="H13" s="8" t="n"/>
       <c r="I13" s="8" t="n"/>
       <c r="J13" s="8" t="n"/>
@@ -1229,9 +1230,9 @@
       <c r="A14" s="7" t="n"/>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
       <c r="H14" s="7" t="n"/>
       <c r="I14" s="7" t="n"/>
       <c r="J14" s="7" t="n"/>
@@ -1259,9 +1260,9 @@
       <c r="A15" s="8" t="n"/>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
       <c r="H15" s="8" t="n"/>
       <c r="I15" s="8" t="n"/>
       <c r="J15" s="8" t="n"/>
@@ -1289,9 +1290,9 @@
       <c r="A16" s="7" t="n"/>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
       <c r="H16" s="7" t="n"/>
       <c r="I16" s="7" t="n"/>
       <c r="J16" s="7" t="n"/>
@@ -1319,9 +1320,9 @@
       <c r="A17" s="8" t="n"/>
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
       <c r="H17" s="8" t="n"/>
       <c r="I17" s="8" t="n"/>
       <c r="J17" s="8" t="n"/>
@@ -1349,9 +1350,9 @@
       <c r="A18" s="7" t="n"/>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
       <c r="H18" s="7" t="n"/>
       <c r="I18" s="7" t="n"/>
       <c r="J18" s="7" t="n"/>
@@ -1379,9 +1380,9 @@
       <c r="A19" s="8" t="n"/>
       <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
       <c r="H19" s="8" t="n"/>
       <c r="I19" s="8" t="n"/>
       <c r="J19" s="8" t="n"/>
@@ -1409,9 +1410,9 @@
       <c r="A20" s="7" t="n"/>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
       <c r="H20" s="7" t="n"/>
       <c r="I20" s="7" t="n"/>
       <c r="J20" s="7" t="n"/>
@@ -1439,9 +1440,9 @@
       <c r="A21" s="8" t="n"/>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
       <c r="I21" s="8" t="n"/>
       <c r="J21" s="8" t="n"/>
@@ -1469,9 +1470,9 @@
       <c r="A22" s="7" t="n"/>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
       <c r="I22" s="7" t="n"/>
       <c r="J22" s="7" t="n"/>
@@ -1499,9 +1500,9 @@
       <c r="A23" s="8" t="n"/>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
       <c r="H23" s="8" t="n"/>
       <c r="I23" s="8" t="n"/>
       <c r="J23" s="8" t="n"/>
@@ -1529,9 +1530,9 @@
       <c r="A24" s="7" t="n"/>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
       <c r="I24" s="7" t="n"/>
       <c r="J24" s="7" t="n"/>
@@ -1559,9 +1560,9 @@
       <c r="A25" s="8" t="n"/>
       <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
       <c r="I25" s="8" t="n"/>
       <c r="J25" s="8" t="n"/>
@@ -1589,9 +1590,9 @@
       <c r="A26" s="7" t="n"/>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
-      <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
       <c r="I26" s="7" t="n"/>
       <c r="J26" s="7" t="n"/>
@@ -1619,9 +1620,9 @@
       <c r="A27" s="8" t="n"/>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
-      <c r="G27" s="8" t="n"/>
       <c r="H27" s="8" t="n"/>
       <c r="I27" s="8" t="n"/>
       <c r="J27" s="8" t="n"/>
@@ -1649,9 +1650,9 @@
       <c r="A28" s="7" t="n"/>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
-      <c r="G28" s="7" t="n"/>
       <c r="H28" s="7" t="n"/>
       <c r="I28" s="7" t="n"/>
       <c r="J28" s="7" t="n"/>
@@ -1679,9 +1680,9 @@
       <c r="A29" s="8" t="n"/>
       <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
-      <c r="G29" s="8" t="n"/>
       <c r="H29" s="8" t="n"/>
       <c r="I29" s="8" t="n"/>
       <c r="J29" s="8" t="n"/>
@@ -1709,9 +1710,9 @@
       <c r="A30" s="7" t="n"/>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="7" t="n"/>
-      <c r="G30" s="7" t="n"/>
       <c r="H30" s="7" t="n"/>
       <c r="I30" s="7" t="n"/>
       <c r="J30" s="7" t="n"/>
@@ -1739,9 +1740,9 @@
       <c r="A31" s="8" t="n"/>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
-      <c r="G31" s="8" t="n"/>
       <c r="H31" s="8" t="n"/>
       <c r="I31" s="8" t="n"/>
       <c r="J31" s="8" t="n"/>
@@ -1769,9 +1770,9 @@
       <c r="A32" s="7" t="n"/>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
-      <c r="G32" s="7" t="n"/>
       <c r="H32" s="7" t="n"/>
       <c r="I32" s="7" t="n"/>
       <c r="J32" s="7" t="n"/>
@@ -1799,9 +1800,9 @@
       <c r="A33" s="8" t="n"/>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
-      <c r="G33" s="8" t="n"/>
       <c r="H33" s="8" t="n"/>
       <c r="I33" s="8" t="n"/>
       <c r="J33" s="8" t="n"/>
@@ -1829,9 +1830,9 @@
       <c r="A34" s="7" t="n"/>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
-      <c r="G34" s="7" t="n"/>
       <c r="H34" s="7" t="n"/>
       <c r="I34" s="7" t="n"/>
       <c r="J34" s="7" t="n"/>
@@ -1859,9 +1860,9 @@
       <c r="A35" s="8" t="n"/>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
-      <c r="G35" s="8" t="n"/>
       <c r="H35" s="8" t="n"/>
       <c r="I35" s="8" t="n"/>
       <c r="J35" s="8" t="n"/>
@@ -1889,9 +1890,9 @@
       <c r="A36" s="7" t="n"/>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
-      <c r="G36" s="7" t="n"/>
       <c r="H36" s="7" t="n"/>
       <c r="I36" s="7" t="n"/>
       <c r="J36" s="7" t="n"/>
@@ -1919,9 +1920,9 @@
       <c r="A37" s="8" t="n"/>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
-      <c r="G37" s="8" t="n"/>
       <c r="H37" s="8" t="n"/>
       <c r="I37" s="8" t="n"/>
       <c r="J37" s="8" t="n"/>
@@ -1949,9 +1950,9 @@
       <c r="A38" s="7" t="n"/>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
-      <c r="G38" s="7" t="n"/>
       <c r="H38" s="7" t="n"/>
       <c r="I38" s="7" t="n"/>
       <c r="J38" s="7" t="n"/>
@@ -1979,9 +1980,9 @@
       <c r="A39" s="8" t="n"/>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
-      <c r="G39" s="8" t="n"/>
       <c r="H39" s="8" t="n"/>
       <c r="I39" s="8" t="n"/>
       <c r="J39" s="8" t="n"/>
@@ -2009,9 +2010,9 @@
       <c r="A40" s="7" t="n"/>
       <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
-      <c r="G40" s="7" t="n"/>
       <c r="H40" s="7" t="n"/>
       <c r="I40" s="7" t="n"/>
       <c r="J40" s="7" t="n"/>
@@ -2039,9 +2040,9 @@
       <c r="A41" s="8" t="n"/>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="8" t="n"/>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
-      <c r="G41" s="8" t="n"/>
       <c r="H41" s="8" t="n"/>
       <c r="I41" s="8" t="n"/>
       <c r="J41" s="8" t="n"/>
@@ -2069,9 +2070,9 @@
       <c r="A42" s="7" t="n"/>
       <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
-      <c r="G42" s="7" t="n"/>
       <c r="H42" s="7" t="n"/>
       <c r="I42" s="7" t="n"/>
       <c r="J42" s="7" t="n"/>
@@ -2099,9 +2100,9 @@
       <c r="A43" s="8" t="n"/>
       <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
-      <c r="G43" s="8" t="n"/>
       <c r="H43" s="8" t="n"/>
       <c r="I43" s="8" t="n"/>
       <c r="J43" s="8" t="n"/>
@@ -2129,9 +2130,9 @@
       <c r="A44" s="7" t="n"/>
       <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
+      <c r="D44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
-      <c r="G44" s="7" t="n"/>
       <c r="H44" s="7" t="n"/>
       <c r="I44" s="7" t="n"/>
       <c r="J44" s="7" t="n"/>
@@ -2159,9 +2160,9 @@
       <c r="A45" s="8" t="n"/>
       <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
+      <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
-      <c r="G45" s="8" t="n"/>
       <c r="H45" s="8" t="n"/>
       <c r="I45" s="8" t="n"/>
       <c r="J45" s="8" t="n"/>
@@ -2189,9 +2190,9 @@
       <c r="A46" s="7" t="n"/>
       <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
+      <c r="D46" s="7" t="n"/>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
-      <c r="G46" s="7" t="n"/>
       <c r="H46" s="7" t="n"/>
       <c r="I46" s="7" t="n"/>
       <c r="J46" s="7" t="n"/>
@@ -2219,9 +2220,9 @@
       <c r="A47" s="8" t="n"/>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="8" t="n"/>
+      <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
-      <c r="G47" s="8" t="n"/>
       <c r="H47" s="8" t="n"/>
       <c r="I47" s="8" t="n"/>
       <c r="J47" s="8" t="n"/>
@@ -2249,9 +2250,9 @@
       <c r="A48" s="7" t="n"/>
       <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
+      <c r="D48" s="7" t="n"/>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
-      <c r="G48" s="7" t="n"/>
       <c r="H48" s="7" t="n"/>
       <c r="I48" s="7" t="n"/>
       <c r="J48" s="7" t="n"/>
@@ -2279,9 +2280,9 @@
       <c r="A49" s="8" t="n"/>
       <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
+      <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
-      <c r="G49" s="8" t="n"/>
       <c r="H49" s="8" t="n"/>
       <c r="I49" s="8" t="n"/>
       <c r="J49" s="8" t="n"/>
@@ -2309,9 +2310,9 @@
       <c r="A50" s="7" t="n"/>
       <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
+      <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="n"/>
-      <c r="G50" s="7" t="n"/>
       <c r="H50" s="7" t="n"/>
       <c r="I50" s="7" t="n"/>
       <c r="J50" s="7" t="n"/>
@@ -2339,9 +2340,9 @@
       <c r="A51" s="8" t="n"/>
       <c r="B51" s="8" t="n"/>
       <c r="C51" s="8" t="n"/>
+      <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
       <c r="F51" s="8" t="n"/>
-      <c r="G51" s="8" t="n"/>
       <c r="H51" s="8" t="n"/>
       <c r="I51" s="8" t="n"/>
       <c r="J51" s="8" t="n"/>
@@ -2369,9 +2370,9 @@
       <c r="A52" s="7" t="n"/>
       <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
+      <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
-      <c r="G52" s="7" t="n"/>
       <c r="H52" s="7" t="n"/>
       <c r="I52" s="7" t="n"/>
       <c r="J52" s="7" t="n"/>
@@ -2399,9 +2400,9 @@
       <c r="A53" s="8" t="n"/>
       <c r="B53" s="8" t="n"/>
       <c r="C53" s="8" t="n"/>
+      <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="n"/>
       <c r="F53" s="8" t="n"/>
-      <c r="G53" s="8" t="n"/>
       <c r="H53" s="8" t="n"/>
       <c r="I53" s="8" t="n"/>
       <c r="J53" s="8" t="n"/>
@@ -2429,9 +2430,9 @@
       <c r="A54" s="7" t="n"/>
       <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
+      <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="7" t="n"/>
-      <c r="G54" s="7" t="n"/>
       <c r="H54" s="7" t="n"/>
       <c r="I54" s="7" t="n"/>
       <c r="J54" s="7" t="n"/>
@@ -2459,9 +2460,9 @@
       <c r="A55" s="8" t="n"/>
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="8" t="n"/>
+      <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
-      <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
       <c r="I55" s="8" t="n"/>
       <c r="J55" s="8" t="n"/>
@@ -2489,9 +2490,9 @@
       <c r="A56" s="7" t="n"/>
       <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
+      <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
-      <c r="G56" s="7" t="n"/>
       <c r="H56" s="7" t="n"/>
       <c r="I56" s="7" t="n"/>
       <c r="J56" s="7" t="n"/>
@@ -2519,9 +2520,9 @@
       <c r="A57" s="8" t="n"/>
       <c r="B57" s="8" t="n"/>
       <c r="C57" s="8" t="n"/>
+      <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
-      <c r="G57" s="8" t="n"/>
       <c r="H57" s="8" t="n"/>
       <c r="I57" s="8" t="n"/>
       <c r="J57" s="8" t="n"/>
@@ -2549,9 +2550,9 @@
       <c r="A58" s="7" t="n"/>
       <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
+      <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
       <c r="F58" s="7" t="n"/>
-      <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
       <c r="I58" s="7" t="n"/>
       <c r="J58" s="7" t="n"/>
@@ -2579,9 +2580,9 @@
       <c r="A59" s="8" t="n"/>
       <c r="B59" s="8" t="n"/>
       <c r="C59" s="8" t="n"/>
+      <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
-      <c r="G59" s="8" t="n"/>
       <c r="H59" s="8" t="n"/>
       <c r="I59" s="8" t="n"/>
       <c r="J59" s="8" t="n"/>
@@ -2609,9 +2610,9 @@
       <c r="A60" s="7" t="n"/>
       <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
+      <c r="D60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="7" t="n"/>
-      <c r="G60" s="7" t="n"/>
       <c r="H60" s="7" t="n"/>
       <c r="I60" s="7" t="n"/>
       <c r="J60" s="7" t="n"/>
@@ -2639,9 +2640,9 @@
       <c r="A61" s="8" t="n"/>
       <c r="B61" s="8" t="n"/>
       <c r="C61" s="8" t="n"/>
+      <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
       <c r="F61" s="8" t="n"/>
-      <c r="G61" s="8" t="n"/>
       <c r="H61" s="8" t="n"/>
       <c r="I61" s="8" t="n"/>
       <c r="J61" s="8" t="n"/>
@@ -2669,9 +2670,9 @@
       <c r="A62" s="7" t="n"/>
       <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
+      <c r="D62" s="7" t="n"/>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
-      <c r="G62" s="7" t="n"/>
       <c r="H62" s="7" t="n"/>
       <c r="I62" s="7" t="n"/>
       <c r="J62" s="7" t="n"/>
@@ -2699,9 +2700,9 @@
       <c r="A63" s="8" t="n"/>
       <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
+      <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
-      <c r="G63" s="8" t="n"/>
       <c r="H63" s="8" t="n"/>
       <c r="I63" s="8" t="n"/>
       <c r="J63" s="8" t="n"/>
@@ -2729,9 +2730,9 @@
       <c r="A64" s="7" t="n"/>
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
+      <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
       <c r="F64" s="7" t="n"/>
-      <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
       <c r="I64" s="7" t="n"/>
       <c r="J64" s="7" t="n"/>
@@ -2759,9 +2760,9 @@
       <c r="A65" s="8" t="n"/>
       <c r="B65" s="8" t="n"/>
       <c r="C65" s="8" t="n"/>
+      <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
       <c r="F65" s="8" t="n"/>
-      <c r="G65" s="8" t="n"/>
       <c r="H65" s="8" t="n"/>
       <c r="I65" s="8" t="n"/>
       <c r="J65" s="8" t="n"/>
@@ -2789,9 +2790,9 @@
       <c r="A66" s="7" t="n"/>
       <c r="B66" s="7" t="n"/>
       <c r="C66" s="7" t="n"/>
+      <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="n"/>
-      <c r="G66" s="7" t="n"/>
       <c r="H66" s="7" t="n"/>
       <c r="I66" s="7" t="n"/>
       <c r="J66" s="7" t="n"/>
@@ -2819,9 +2820,9 @@
       <c r="A67" s="8" t="n"/>
       <c r="B67" s="8" t="n"/>
       <c r="C67" s="8" t="n"/>
+      <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
-      <c r="G67" s="8" t="n"/>
       <c r="H67" s="8" t="n"/>
       <c r="I67" s="8" t="n"/>
       <c r="J67" s="8" t="n"/>
@@ -2849,9 +2850,9 @@
       <c r="A68" s="7" t="n"/>
       <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="n"/>
+      <c r="D68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="n"/>
-      <c r="G68" s="7" t="n"/>
       <c r="H68" s="7" t="n"/>
       <c r="I68" s="7" t="n"/>
       <c r="J68" s="7" t="n"/>
@@ -2879,9 +2880,9 @@
       <c r="A69" s="8" t="n"/>
       <c r="B69" s="8" t="n"/>
       <c r="C69" s="8" t="n"/>
+      <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
-      <c r="G69" s="8" t="n"/>
       <c r="H69" s="8" t="n"/>
       <c r="I69" s="8" t="n"/>
       <c r="J69" s="8" t="n"/>
@@ -2909,9 +2910,9 @@
       <c r="A70" s="7" t="n"/>
       <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
+      <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
-      <c r="G70" s="7" t="n"/>
       <c r="H70" s="7" t="n"/>
       <c r="I70" s="7" t="n"/>
       <c r="J70" s="7" t="n"/>
@@ -2939,9 +2940,9 @@
       <c r="A71" s="8" t="n"/>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
+      <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
-      <c r="G71" s="8" t="n"/>
       <c r="H71" s="8" t="n"/>
       <c r="I71" s="8" t="n"/>
       <c r="J71" s="8" t="n"/>
@@ -2969,9 +2970,9 @@
       <c r="A72" s="7" t="n"/>
       <c r="B72" s="7" t="n"/>
       <c r="C72" s="7" t="n"/>
+      <c r="D72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
-      <c r="G72" s="7" t="n"/>
       <c r="H72" s="7" t="n"/>
       <c r="I72" s="7" t="n"/>
       <c r="J72" s="7" t="n"/>
@@ -2999,9 +3000,9 @@
       <c r="A73" s="8" t="n"/>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
+      <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
       <c r="F73" s="8" t="n"/>
-      <c r="G73" s="8" t="n"/>
       <c r="H73" s="8" t="n"/>
       <c r="I73" s="8" t="n"/>
       <c r="J73" s="8" t="n"/>
@@ -3029,9 +3030,9 @@
       <c r="A74" s="7" t="n"/>
       <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
+      <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="n"/>
-      <c r="G74" s="7" t="n"/>
       <c r="H74" s="7" t="n"/>
       <c r="I74" s="7" t="n"/>
       <c r="J74" s="7" t="n"/>
@@ -3059,9 +3060,9 @@
       <c r="A75" s="8" t="n"/>
       <c r="B75" s="8" t="n"/>
       <c r="C75" s="8" t="n"/>
+      <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="8" t="n"/>
-      <c r="G75" s="8" t="n"/>
       <c r="H75" s="8" t="n"/>
       <c r="I75" s="8" t="n"/>
       <c r="J75" s="8" t="n"/>
@@ -3089,9 +3090,9 @@
       <c r="A76" s="7" t="n"/>
       <c r="B76" s="7" t="n"/>
       <c r="C76" s="7" t="n"/>
+      <c r="D76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="7" t="n"/>
-      <c r="G76" s="7" t="n"/>
       <c r="H76" s="7" t="n"/>
       <c r="I76" s="7" t="n"/>
       <c r="J76" s="7" t="n"/>
@@ -3119,9 +3120,9 @@
       <c r="A77" s="8" t="n"/>
       <c r="B77" s="8" t="n"/>
       <c r="C77" s="8" t="n"/>
+      <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
       <c r="F77" s="8" t="n"/>
-      <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="n"/>
       <c r="I77" s="8" t="n"/>
       <c r="J77" s="8" t="n"/>
@@ -3149,9 +3150,9 @@
       <c r="A78" s="7" t="n"/>
       <c r="B78" s="7" t="n"/>
       <c r="C78" s="7" t="n"/>
+      <c r="D78" s="7" t="n"/>
       <c r="E78" s="7" t="n"/>
       <c r="F78" s="7" t="n"/>
-      <c r="G78" s="7" t="n"/>
       <c r="H78" s="7" t="n"/>
       <c r="I78" s="7" t="n"/>
       <c r="J78" s="7" t="n"/>
@@ -3179,9 +3180,9 @@
       <c r="A79" s="8" t="n"/>
       <c r="B79" s="8" t="n"/>
       <c r="C79" s="8" t="n"/>
+      <c r="D79" s="8" t="n"/>
       <c r="E79" s="8" t="n"/>
       <c r="F79" s="8" t="n"/>
-      <c r="G79" s="8" t="n"/>
       <c r="H79" s="8" t="n"/>
       <c r="I79" s="8" t="n"/>
       <c r="J79" s="8" t="n"/>
@@ -3209,9 +3210,9 @@
       <c r="A80" s="7" t="n"/>
       <c r="B80" s="7" t="n"/>
       <c r="C80" s="7" t="n"/>
+      <c r="D80" s="7" t="n"/>
       <c r="E80" s="7" t="n"/>
       <c r="F80" s="7" t="n"/>
-      <c r="G80" s="7" t="n"/>
       <c r="H80" s="7" t="n"/>
       <c r="I80" s="7" t="n"/>
       <c r="J80" s="7" t="n"/>
@@ -3239,9 +3240,9 @@
       <c r="A81" s="8" t="n"/>
       <c r="B81" s="8" t="n"/>
       <c r="C81" s="8" t="n"/>
+      <c r="D81" s="8" t="n"/>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
-      <c r="G81" s="8" t="n"/>
       <c r="H81" s="8" t="n"/>
       <c r="I81" s="8" t="n"/>
       <c r="J81" s="8" t="n"/>
@@ -3269,9 +3270,9 @@
       <c r="A82" s="7" t="n"/>
       <c r="B82" s="7" t="n"/>
       <c r="C82" s="7" t="n"/>
+      <c r="D82" s="7" t="n"/>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="7" t="n"/>
-      <c r="G82" s="7" t="n"/>
       <c r="H82" s="7" t="n"/>
       <c r="I82" s="7" t="n"/>
       <c r="J82" s="7" t="n"/>
@@ -3299,9 +3300,9 @@
       <c r="A83" s="8" t="n"/>
       <c r="B83" s="8" t="n"/>
       <c r="C83" s="8" t="n"/>
+      <c r="D83" s="8" t="n"/>
       <c r="E83" s="8" t="n"/>
       <c r="F83" s="8" t="n"/>
-      <c r="G83" s="8" t="n"/>
       <c r="H83" s="8" t="n"/>
       <c r="I83" s="8" t="n"/>
       <c r="J83" s="8" t="n"/>
@@ -3329,9 +3330,9 @@
       <c r="A84" s="7" t="n"/>
       <c r="B84" s="7" t="n"/>
       <c r="C84" s="7" t="n"/>
+      <c r="D84" s="7" t="n"/>
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="7" t="n"/>
-      <c r="G84" s="7" t="n"/>
       <c r="H84" s="7" t="n"/>
       <c r="I84" s="7" t="n"/>
       <c r="J84" s="7" t="n"/>
@@ -3359,9 +3360,9 @@
       <c r="A85" s="8" t="n"/>
       <c r="B85" s="8" t="n"/>
       <c r="C85" s="8" t="n"/>
+      <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="n"/>
-      <c r="G85" s="8" t="n"/>
       <c r="H85" s="8" t="n"/>
       <c r="I85" s="8" t="n"/>
       <c r="J85" s="8" t="n"/>
@@ -3389,9 +3390,9 @@
       <c r="A86" s="7" t="n"/>
       <c r="B86" s="7" t="n"/>
       <c r="C86" s="7" t="n"/>
+      <c r="D86" s="7" t="n"/>
       <c r="E86" s="7" t="n"/>
       <c r="F86" s="7" t="n"/>
-      <c r="G86" s="7" t="n"/>
       <c r="H86" s="7" t="n"/>
       <c r="I86" s="7" t="n"/>
       <c r="J86" s="7" t="n"/>
@@ -3419,9 +3420,9 @@
       <c r="A87" s="8" t="n"/>
       <c r="B87" s="8" t="n"/>
       <c r="C87" s="8" t="n"/>
+      <c r="D87" s="8" t="n"/>
       <c r="E87" s="8" t="n"/>
       <c r="F87" s="8" t="n"/>
-      <c r="G87" s="8" t="n"/>
       <c r="H87" s="8" t="n"/>
       <c r="I87" s="8" t="n"/>
       <c r="J87" s="8" t="n"/>
@@ -3449,9 +3450,9 @@
       <c r="A88" s="7" t="n"/>
       <c r="B88" s="7" t="n"/>
       <c r="C88" s="7" t="n"/>
+      <c r="D88" s="7" t="n"/>
       <c r="E88" s="7" t="n"/>
       <c r="F88" s="7" t="n"/>
-      <c r="G88" s="7" t="n"/>
       <c r="H88" s="7" t="n"/>
       <c r="I88" s="7" t="n"/>
       <c r="J88" s="7" t="n"/>
@@ -3479,9 +3480,9 @@
       <c r="A89" s="8" t="n"/>
       <c r="B89" s="8" t="n"/>
       <c r="C89" s="8" t="n"/>
+      <c r="D89" s="8" t="n"/>
       <c r="E89" s="8" t="n"/>
       <c r="F89" s="8" t="n"/>
-      <c r="G89" s="8" t="n"/>
       <c r="H89" s="8" t="n"/>
       <c r="I89" s="8" t="n"/>
       <c r="J89" s="8" t="n"/>
@@ -3509,9 +3510,9 @@
       <c r="A90" s="7" t="n"/>
       <c r="B90" s="7" t="n"/>
       <c r="C90" s="7" t="n"/>
+      <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="7" t="n"/>
-      <c r="G90" s="7" t="n"/>
       <c r="H90" s="7" t="n"/>
       <c r="I90" s="7" t="n"/>
       <c r="J90" s="7" t="n"/>
@@ -3539,9 +3540,9 @@
       <c r="A91" s="8" t="n"/>
       <c r="B91" s="8" t="n"/>
       <c r="C91" s="8" t="n"/>
+      <c r="D91" s="8" t="n"/>
       <c r="E91" s="8" t="n"/>
       <c r="F91" s="8" t="n"/>
-      <c r="G91" s="8" t="n"/>
       <c r="H91" s="8" t="n"/>
       <c r="I91" s="8" t="n"/>
       <c r="J91" s="8" t="n"/>
@@ -3569,9 +3570,9 @@
       <c r="A92" s="7" t="n"/>
       <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
+      <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="7" t="n"/>
-      <c r="G92" s="7" t="n"/>
       <c r="H92" s="7" t="n"/>
       <c r="I92" s="7" t="n"/>
       <c r="J92" s="7" t="n"/>
@@ -3599,9 +3600,9 @@
       <c r="A93" s="8" t="n"/>
       <c r="B93" s="8" t="n"/>
       <c r="C93" s="8" t="n"/>
+      <c r="D93" s="8" t="n"/>
       <c r="E93" s="8" t="n"/>
       <c r="F93" s="8" t="n"/>
-      <c r="G93" s="8" t="n"/>
       <c r="H93" s="8" t="n"/>
       <c r="I93" s="8" t="n"/>
       <c r="J93" s="8" t="n"/>
@@ -3629,9 +3630,9 @@
       <c r="A94" s="7" t="n"/>
       <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
+      <c r="D94" s="7" t="n"/>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
-      <c r="G94" s="7" t="n"/>
       <c r="H94" s="7" t="n"/>
       <c r="I94" s="7" t="n"/>
       <c r="J94" s="7" t="n"/>
@@ -3659,9 +3660,9 @@
       <c r="A95" s="8" t="n"/>
       <c r="B95" s="8" t="n"/>
       <c r="C95" s="8" t="n"/>
+      <c r="D95" s="8" t="n"/>
       <c r="E95" s="8" t="n"/>
       <c r="F95" s="8" t="n"/>
-      <c r="G95" s="8" t="n"/>
       <c r="H95" s="8" t="n"/>
       <c r="I95" s="8" t="n"/>
       <c r="J95" s="8" t="n"/>
@@ -3689,9 +3690,9 @@
       <c r="A96" s="7" t="n"/>
       <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
+      <c r="D96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="7" t="n"/>
-      <c r="G96" s="7" t="n"/>
       <c r="H96" s="7" t="n"/>
       <c r="I96" s="7" t="n"/>
       <c r="J96" s="7" t="n"/>
@@ -3719,9 +3720,9 @@
       <c r="A97" s="8" t="n"/>
       <c r="B97" s="8" t="n"/>
       <c r="C97" s="8" t="n"/>
+      <c r="D97" s="8" t="n"/>
       <c r="E97" s="8" t="n"/>
       <c r="F97" s="8" t="n"/>
-      <c r="G97" s="8" t="n"/>
       <c r="H97" s="8" t="n"/>
       <c r="I97" s="8" t="n"/>
       <c r="J97" s="8" t="n"/>
@@ -3749,9 +3750,9 @@
       <c r="A98" s="7" t="n"/>
       <c r="B98" s="7" t="n"/>
       <c r="C98" s="7" t="n"/>
+      <c r="D98" s="7" t="n"/>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="7" t="n"/>
-      <c r="G98" s="7" t="n"/>
       <c r="H98" s="7" t="n"/>
       <c r="I98" s="7" t="n"/>
       <c r="J98" s="7" t="n"/>
@@ -3779,9 +3780,9 @@
       <c r="A99" s="8" t="n"/>
       <c r="B99" s="8" t="n"/>
       <c r="C99" s="8" t="n"/>
+      <c r="D99" s="8" t="n"/>
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
-      <c r="G99" s="8" t="n"/>
       <c r="H99" s="8" t="n"/>
       <c r="I99" s="8" t="n"/>
       <c r="J99" s="8" t="n"/>
@@ -3809,9 +3810,9 @@
       <c r="A100" s="7" t="n"/>
       <c r="B100" s="7" t="n"/>
       <c r="C100" s="7" t="n"/>
+      <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
-      <c r="G100" s="7" t="n"/>
       <c r="H100" s="7" t="n"/>
       <c r="I100" s="7" t="n"/>
       <c r="J100" s="7" t="n"/>
@@ -3839,9 +3840,9 @@
       <c r="A101" s="8" t="n"/>
       <c r="B101" s="8" t="n"/>
       <c r="C101" s="8" t="n"/>
+      <c r="D101" s="8" t="n"/>
       <c r="E101" s="8" t="n"/>
       <c r="F101" s="8" t="n"/>
-      <c r="G101" s="8" t="n"/>
       <c r="H101" s="8" t="n"/>
       <c r="I101" s="8" t="n"/>
       <c r="J101" s="8" t="n"/>
@@ -3869,9 +3870,9 @@
       <c r="A102" s="7" t="n"/>
       <c r="B102" s="7" t="n"/>
       <c r="C102" s="7" t="n"/>
+      <c r="D102" s="7" t="n"/>
       <c r="E102" s="7" t="n"/>
       <c r="F102" s="7" t="n"/>
-      <c r="G102" s="7" t="n"/>
       <c r="H102" s="7" t="n"/>
       <c r="I102" s="7" t="n"/>
       <c r="J102" s="7" t="n"/>
@@ -3899,9 +3900,9 @@
       <c r="A103" s="8" t="n"/>
       <c r="B103" s="8" t="n"/>
       <c r="C103" s="8" t="n"/>
+      <c r="D103" s="8" t="n"/>
       <c r="E103" s="8" t="n"/>
       <c r="F103" s="8" t="n"/>
-      <c r="G103" s="8" t="n"/>
       <c r="H103" s="8" t="n"/>
       <c r="I103" s="8" t="n"/>
       <c r="J103" s="8" t="n"/>
@@ -3929,9 +3930,9 @@
       <c r="A104" s="7" t="n"/>
       <c r="B104" s="7" t="n"/>
       <c r="C104" s="7" t="n"/>
+      <c r="D104" s="7" t="n"/>
       <c r="E104" s="7" t="n"/>
       <c r="F104" s="7" t="n"/>
-      <c r="G104" s="7" t="n"/>
       <c r="H104" s="7" t="n"/>
       <c r="I104" s="7" t="n"/>
       <c r="J104" s="7" t="n"/>
@@ -3959,9 +3960,9 @@
       <c r="A105" s="8" t="n"/>
       <c r="B105" s="8" t="n"/>
       <c r="C105" s="8" t="n"/>
+      <c r="D105" s="8" t="n"/>
       <c r="E105" s="8" t="n"/>
       <c r="F105" s="8" t="n"/>
-      <c r="G105" s="8" t="n"/>
       <c r="H105" s="8" t="n"/>
       <c r="I105" s="8" t="n"/>
       <c r="J105" s="8" t="n"/>
@@ -3989,9 +3990,9 @@
       <c r="A106" s="7" t="n"/>
       <c r="B106" s="7" t="n"/>
       <c r="C106" s="7" t="n"/>
+      <c r="D106" s="7" t="n"/>
       <c r="E106" s="7" t="n"/>
       <c r="F106" s="7" t="n"/>
-      <c r="G106" s="7" t="n"/>
       <c r="H106" s="7" t="n"/>
       <c r="I106" s="7" t="n"/>
       <c r="J106" s="7" t="n"/>
@@ -4019,9 +4020,9 @@
       <c r="A107" s="8" t="n"/>
       <c r="B107" s="8" t="n"/>
       <c r="C107" s="8" t="n"/>
+      <c r="D107" s="8" t="n"/>
       <c r="E107" s="8" t="n"/>
       <c r="F107" s="8" t="n"/>
-      <c r="G107" s="8" t="n"/>
       <c r="H107" s="8" t="n"/>
       <c r="I107" s="8" t="n"/>
       <c r="J107" s="8" t="n"/>
@@ -4049,9 +4050,9 @@
       <c r="A108" s="7" t="n"/>
       <c r="B108" s="7" t="n"/>
       <c r="C108" s="7" t="n"/>
+      <c r="D108" s="7" t="n"/>
       <c r="E108" s="7" t="n"/>
       <c r="F108" s="7" t="n"/>
-      <c r="G108" s="7" t="n"/>
       <c r="H108" s="7" t="n"/>
       <c r="I108" s="7" t="n"/>
       <c r="J108" s="7" t="n"/>
@@ -4079,9 +4080,9 @@
       <c r="A109" s="8" t="n"/>
       <c r="B109" s="8" t="n"/>
       <c r="C109" s="8" t="n"/>
+      <c r="D109" s="8" t="n"/>
       <c r="E109" s="8" t="n"/>
       <c r="F109" s="8" t="n"/>
-      <c r="G109" s="8" t="n"/>
       <c r="H109" s="8" t="n"/>
       <c r="I109" s="8" t="n"/>
       <c r="J109" s="8" t="n"/>
@@ -4109,9 +4110,9 @@
       <c r="A110" s="7" t="n"/>
       <c r="B110" s="7" t="n"/>
       <c r="C110" s="7" t="n"/>
+      <c r="D110" s="7" t="n"/>
       <c r="E110" s="7" t="n"/>
       <c r="F110" s="7" t="n"/>
-      <c r="G110" s="7" t="n"/>
       <c r="H110" s="7" t="n"/>
       <c r="I110" s="7" t="n"/>
       <c r="J110" s="7" t="n"/>
@@ -4139,9 +4140,9 @@
       <c r="A111" s="8" t="n"/>
       <c r="B111" s="8" t="n"/>
       <c r="C111" s="8" t="n"/>
+      <c r="D111" s="8" t="n"/>
       <c r="E111" s="8" t="n"/>
       <c r="F111" s="8" t="n"/>
-      <c r="G111" s="8" t="n"/>
       <c r="H111" s="8" t="n"/>
       <c r="I111" s="8" t="n"/>
       <c r="J111" s="8" t="n"/>
@@ -4169,9 +4170,9 @@
       <c r="A112" s="7" t="n"/>
       <c r="B112" s="7" t="n"/>
       <c r="C112" s="7" t="n"/>
+      <c r="D112" s="7" t="n"/>
       <c r="E112" s="7" t="n"/>
       <c r="F112" s="7" t="n"/>
-      <c r="G112" s="7" t="n"/>
       <c r="H112" s="7" t="n"/>
       <c r="I112" s="7" t="n"/>
       <c r="J112" s="7" t="n"/>
@@ -4199,9 +4200,9 @@
       <c r="A113" s="8" t="n"/>
       <c r="B113" s="8" t="n"/>
       <c r="C113" s="8" t="n"/>
+      <c r="D113" s="8" t="n"/>
       <c r="E113" s="8" t="n"/>
       <c r="F113" s="8" t="n"/>
-      <c r="G113" s="8" t="n"/>
       <c r="H113" s="8" t="n"/>
       <c r="I113" s="8" t="n"/>
       <c r="J113" s="8" t="n"/>
@@ -4229,9 +4230,9 @@
       <c r="A114" s="7" t="n"/>
       <c r="B114" s="7" t="n"/>
       <c r="C114" s="7" t="n"/>
+      <c r="D114" s="7" t="n"/>
       <c r="E114" s="7" t="n"/>
       <c r="F114" s="7" t="n"/>
-      <c r="G114" s="7" t="n"/>
       <c r="H114" s="7" t="n"/>
       <c r="I114" s="7" t="n"/>
       <c r="J114" s="7" t="n"/>
@@ -4259,9 +4260,9 @@
       <c r="A115" s="8" t="n"/>
       <c r="B115" s="8" t="n"/>
       <c r="C115" s="8" t="n"/>
+      <c r="D115" s="8" t="n"/>
       <c r="E115" s="8" t="n"/>
       <c r="F115" s="8" t="n"/>
-      <c r="G115" s="8" t="n"/>
       <c r="H115" s="8" t="n"/>
       <c r="I115" s="8" t="n"/>
       <c r="J115" s="8" t="n"/>
@@ -4289,9 +4290,9 @@
       <c r="A116" s="7" t="n"/>
       <c r="B116" s="7" t="n"/>
       <c r="C116" s="7" t="n"/>
+      <c r="D116" s="7" t="n"/>
       <c r="E116" s="7" t="n"/>
       <c r="F116" s="7" t="n"/>
-      <c r="G116" s="7" t="n"/>
       <c r="H116" s="7" t="n"/>
       <c r="I116" s="7" t="n"/>
       <c r="J116" s="7" t="n"/>
@@ -4319,9 +4320,9 @@
       <c r="A117" s="8" t="n"/>
       <c r="B117" s="8" t="n"/>
       <c r="C117" s="8" t="n"/>
+      <c r="D117" s="8" t="n"/>
       <c r="E117" s="8" t="n"/>
       <c r="F117" s="8" t="n"/>
-      <c r="G117" s="8" t="n"/>
       <c r="H117" s="8" t="n"/>
       <c r="I117" s="8" t="n"/>
       <c r="J117" s="8" t="n"/>
@@ -4349,9 +4350,9 @@
       <c r="A118" s="7" t="n"/>
       <c r="B118" s="7" t="n"/>
       <c r="C118" s="7" t="n"/>
+      <c r="D118" s="7" t="n"/>
       <c r="E118" s="7" t="n"/>
       <c r="F118" s="7" t="n"/>
-      <c r="G118" s="7" t="n"/>
       <c r="H118" s="7" t="n"/>
       <c r="I118" s="7" t="n"/>
       <c r="J118" s="7" t="n"/>
@@ -4379,9 +4380,9 @@
       <c r="A119" s="8" t="n"/>
       <c r="B119" s="8" t="n"/>
       <c r="C119" s="8" t="n"/>
+      <c r="D119" s="8" t="n"/>
       <c r="E119" s="8" t="n"/>
       <c r="F119" s="8" t="n"/>
-      <c r="G119" s="8" t="n"/>
       <c r="H119" s="8" t="n"/>
       <c r="I119" s="8" t="n"/>
       <c r="J119" s="8" t="n"/>
@@ -4409,9 +4410,9 @@
       <c r="A120" s="7" t="n"/>
       <c r="B120" s="7" t="n"/>
       <c r="C120" s="7" t="n"/>
+      <c r="D120" s="7" t="n"/>
       <c r="E120" s="7" t="n"/>
       <c r="F120" s="7" t="n"/>
-      <c r="G120" s="7" t="n"/>
       <c r="H120" s="7" t="n"/>
       <c r="I120" s="7" t="n"/>
       <c r="J120" s="7" t="n"/>
@@ -4439,9 +4440,9 @@
       <c r="A121" s="8" t="n"/>
       <c r="B121" s="8" t="n"/>
       <c r="C121" s="8" t="n"/>
+      <c r="D121" s="8" t="n"/>
       <c r="E121" s="8" t="n"/>
       <c r="F121" s="8" t="n"/>
-      <c r="G121" s="8" t="n"/>
       <c r="H121" s="8" t="n"/>
       <c r="I121" s="8" t="n"/>
       <c r="J121" s="8" t="n"/>
@@ -4469,9 +4470,9 @@
       <c r="A122" s="7" t="n"/>
       <c r="B122" s="7" t="n"/>
       <c r="C122" s="7" t="n"/>
+      <c r="D122" s="7" t="n"/>
       <c r="E122" s="7" t="n"/>
       <c r="F122" s="7" t="n"/>
-      <c r="G122" s="7" t="n"/>
       <c r="H122" s="7" t="n"/>
       <c r="I122" s="7" t="n"/>
       <c r="J122" s="7" t="n"/>
@@ -4499,9 +4500,9 @@
       <c r="A123" s="8" t="n"/>
       <c r="B123" s="8" t="n"/>
       <c r="C123" s="8" t="n"/>
+      <c r="D123" s="8" t="n"/>
       <c r="E123" s="8" t="n"/>
       <c r="F123" s="8" t="n"/>
-      <c r="G123" s="8" t="n"/>
       <c r="H123" s="8" t="n"/>
       <c r="I123" s="8" t="n"/>
       <c r="J123" s="8" t="n"/>
@@ -4529,9 +4530,9 @@
       <c r="A124" s="7" t="n"/>
       <c r="B124" s="7" t="n"/>
       <c r="C124" s="7" t="n"/>
+      <c r="D124" s="7" t="n"/>
       <c r="E124" s="7" t="n"/>
       <c r="F124" s="7" t="n"/>
-      <c r="G124" s="7" t="n"/>
       <c r="H124" s="7" t="n"/>
       <c r="I124" s="7" t="n"/>
       <c r="J124" s="7" t="n"/>
@@ -4559,9 +4560,9 @@
       <c r="A125" s="8" t="n"/>
       <c r="B125" s="8" t="n"/>
       <c r="C125" s="8" t="n"/>
+      <c r="D125" s="8" t="n"/>
       <c r="E125" s="8" t="n"/>
       <c r="F125" s="8" t="n"/>
-      <c r="G125" s="8" t="n"/>
       <c r="H125" s="8" t="n"/>
       <c r="I125" s="8" t="n"/>
       <c r="J125" s="8" t="n"/>
@@ -4589,9 +4590,9 @@
       <c r="A126" s="7" t="n"/>
       <c r="B126" s="7" t="n"/>
       <c r="C126" s="7" t="n"/>
+      <c r="D126" s="7" t="n"/>
       <c r="E126" s="7" t="n"/>
       <c r="F126" s="7" t="n"/>
-      <c r="G126" s="7" t="n"/>
       <c r="H126" s="7" t="n"/>
       <c r="I126" s="7" t="n"/>
       <c r="J126" s="7" t="n"/>
@@ -4619,9 +4620,9 @@
       <c r="A127" s="8" t="n"/>
       <c r="B127" s="8" t="n"/>
       <c r="C127" s="8" t="n"/>
+      <c r="D127" s="8" t="n"/>
       <c r="E127" s="8" t="n"/>
       <c r="F127" s="8" t="n"/>
-      <c r="G127" s="8" t="n"/>
       <c r="H127" s="8" t="n"/>
       <c r="I127" s="8" t="n"/>
       <c r="J127" s="8" t="n"/>
@@ -4649,9 +4650,9 @@
       <c r="A128" s="7" t="n"/>
       <c r="B128" s="7" t="n"/>
       <c r="C128" s="7" t="n"/>
+      <c r="D128" s="7" t="n"/>
       <c r="E128" s="7" t="n"/>
       <c r="F128" s="7" t="n"/>
-      <c r="G128" s="7" t="n"/>
       <c r="H128" s="7" t="n"/>
       <c r="I128" s="7" t="n"/>
       <c r="J128" s="7" t="n"/>
@@ -4679,9 +4680,9 @@
       <c r="A129" s="8" t="n"/>
       <c r="B129" s="8" t="n"/>
       <c r="C129" s="8" t="n"/>
+      <c r="D129" s="8" t="n"/>
       <c r="E129" s="8" t="n"/>
       <c r="F129" s="8" t="n"/>
-      <c r="G129" s="8" t="n"/>
       <c r="H129" s="8" t="n"/>
       <c r="I129" s="8" t="n"/>
       <c r="J129" s="8" t="n"/>
@@ -4709,9 +4710,9 @@
       <c r="A130" s="7" t="n"/>
       <c r="B130" s="7" t="n"/>
       <c r="C130" s="7" t="n"/>
+      <c r="D130" s="7" t="n"/>
       <c r="E130" s="7" t="n"/>
       <c r="F130" s="7" t="n"/>
-      <c r="G130" s="7" t="n"/>
       <c r="H130" s="7" t="n"/>
       <c r="I130" s="7" t="n"/>
       <c r="J130" s="7" t="n"/>
@@ -4739,9 +4740,9 @@
       <c r="A131" s="8" t="n"/>
       <c r="B131" s="8" t="n"/>
       <c r="C131" s="8" t="n"/>
+      <c r="D131" s="8" t="n"/>
       <c r="E131" s="8" t="n"/>
       <c r="F131" s="8" t="n"/>
-      <c r="G131" s="8" t="n"/>
       <c r="H131" s="8" t="n"/>
       <c r="I131" s="8" t="n"/>
       <c r="J131" s="8" t="n"/>
@@ -4769,9 +4770,9 @@
       <c r="A132" s="7" t="n"/>
       <c r="B132" s="7" t="n"/>
       <c r="C132" s="7" t="n"/>
+      <c r="D132" s="7" t="n"/>
       <c r="E132" s="7" t="n"/>
       <c r="F132" s="7" t="n"/>
-      <c r="G132" s="7" t="n"/>
       <c r="H132" s="7" t="n"/>
       <c r="I132" s="7" t="n"/>
       <c r="J132" s="7" t="n"/>
@@ -4799,9 +4800,9 @@
       <c r="A133" s="8" t="n"/>
       <c r="B133" s="8" t="n"/>
       <c r="C133" s="8" t="n"/>
+      <c r="D133" s="8" t="n"/>
       <c r="E133" s="8" t="n"/>
       <c r="F133" s="8" t="n"/>
-      <c r="G133" s="8" t="n"/>
       <c r="H133" s="8" t="n"/>
       <c r="I133" s="8" t="n"/>
       <c r="J133" s="8" t="n"/>
@@ -4829,9 +4830,9 @@
       <c r="A134" s="7" t="n"/>
       <c r="B134" s="7" t="n"/>
       <c r="C134" s="7" t="n"/>
+      <c r="D134" s="7" t="n"/>
       <c r="E134" s="7" t="n"/>
       <c r="F134" s="7" t="n"/>
-      <c r="G134" s="7" t="n"/>
       <c r="H134" s="7" t="n"/>
       <c r="I134" s="7" t="n"/>
       <c r="J134" s="7" t="n"/>
@@ -4859,9 +4860,9 @@
       <c r="A135" s="8" t="n"/>
       <c r="B135" s="8" t="n"/>
       <c r="C135" s="8" t="n"/>
+      <c r="D135" s="8" t="n"/>
       <c r="E135" s="8" t="n"/>
       <c r="F135" s="8" t="n"/>
-      <c r="G135" s="8" t="n"/>
       <c r="H135" s="8" t="n"/>
       <c r="I135" s="8" t="n"/>
       <c r="J135" s="8" t="n"/>
@@ -4889,9 +4890,9 @@
       <c r="A136" s="7" t="n"/>
       <c r="B136" s="7" t="n"/>
       <c r="C136" s="7" t="n"/>
+      <c r="D136" s="7" t="n"/>
       <c r="E136" s="7" t="n"/>
       <c r="F136" s="7" t="n"/>
-      <c r="G136" s="7" t="n"/>
       <c r="H136" s="7" t="n"/>
       <c r="I136" s="7" t="n"/>
       <c r="J136" s="7" t="n"/>
@@ -4919,9 +4920,9 @@
       <c r="A137" s="8" t="n"/>
       <c r="B137" s="8" t="n"/>
       <c r="C137" s="8" t="n"/>
+      <c r="D137" s="8" t="n"/>
       <c r="E137" s="8" t="n"/>
       <c r="F137" s="8" t="n"/>
-      <c r="G137" s="8" t="n"/>
       <c r="H137" s="8" t="n"/>
       <c r="I137" s="8" t="n"/>
       <c r="J137" s="8" t="n"/>
@@ -4949,9 +4950,9 @@
       <c r="A138" s="7" t="n"/>
       <c r="B138" s="7" t="n"/>
       <c r="C138" s="7" t="n"/>
+      <c r="D138" s="7" t="n"/>
       <c r="E138" s="7" t="n"/>
       <c r="F138" s="7" t="n"/>
-      <c r="G138" s="7" t="n"/>
       <c r="H138" s="7" t="n"/>
       <c r="I138" s="7" t="n"/>
       <c r="J138" s="7" t="n"/>
@@ -4979,9 +4980,9 @@
       <c r="A139" s="8" t="n"/>
       <c r="B139" s="8" t="n"/>
       <c r="C139" s="8" t="n"/>
+      <c r="D139" s="8" t="n"/>
       <c r="E139" s="8" t="n"/>
       <c r="F139" s="8" t="n"/>
-      <c r="G139" s="8" t="n"/>
       <c r="H139" s="8" t="n"/>
       <c r="I139" s="8" t="n"/>
       <c r="J139" s="8" t="n"/>
@@ -5009,9 +5010,9 @@
       <c r="A140" s="7" t="n"/>
       <c r="B140" s="7" t="n"/>
       <c r="C140" s="7" t="n"/>
+      <c r="D140" s="7" t="n"/>
       <c r="E140" s="7" t="n"/>
       <c r="F140" s="7" t="n"/>
-      <c r="G140" s="7" t="n"/>
       <c r="H140" s="7" t="n"/>
       <c r="I140" s="7" t="n"/>
       <c r="J140" s="7" t="n"/>
@@ -5039,9 +5040,9 @@
       <c r="A141" s="8" t="n"/>
       <c r="B141" s="8" t="n"/>
       <c r="C141" s="8" t="n"/>
+      <c r="D141" s="8" t="n"/>
       <c r="E141" s="8" t="n"/>
       <c r="F141" s="8" t="n"/>
-      <c r="G141" s="8" t="n"/>
       <c r="H141" s="8" t="n"/>
       <c r="I141" s="8" t="n"/>
       <c r="J141" s="8" t="n"/>
@@ -5069,9 +5070,9 @@
       <c r="A142" s="7" t="n"/>
       <c r="B142" s="7" t="n"/>
       <c r="C142" s="7" t="n"/>
+      <c r="D142" s="7" t="n"/>
       <c r="E142" s="7" t="n"/>
       <c r="F142" s="7" t="n"/>
-      <c r="G142" s="7" t="n"/>
       <c r="H142" s="7" t="n"/>
       <c r="I142" s="7" t="n"/>
       <c r="J142" s="7" t="n"/>
@@ -5099,9 +5100,9 @@
       <c r="A143" s="8" t="n"/>
       <c r="B143" s="8" t="n"/>
       <c r="C143" s="8" t="n"/>
+      <c r="D143" s="8" t="n"/>
       <c r="E143" s="8" t="n"/>
       <c r="F143" s="8" t="n"/>
-      <c r="G143" s="8" t="n"/>
       <c r="H143" s="8" t="n"/>
       <c r="I143" s="8" t="n"/>
       <c r="J143" s="8" t="n"/>
@@ -5129,9 +5130,9 @@
       <c r="A144" s="7" t="n"/>
       <c r="B144" s="7" t="n"/>
       <c r="C144" s="7" t="n"/>
+      <c r="D144" s="7" t="n"/>
       <c r="E144" s="7" t="n"/>
       <c r="F144" s="7" t="n"/>
-      <c r="G144" s="7" t="n"/>
       <c r="H144" s="7" t="n"/>
       <c r="I144" s="7" t="n"/>
       <c r="J144" s="7" t="n"/>
@@ -5159,9 +5160,9 @@
       <c r="A145" s="8" t="n"/>
       <c r="B145" s="8" t="n"/>
       <c r="C145" s="8" t="n"/>
+      <c r="D145" s="8" t="n"/>
       <c r="E145" s="8" t="n"/>
       <c r="F145" s="8" t="n"/>
-      <c r="G145" s="8" t="n"/>
       <c r="H145" s="8" t="n"/>
       <c r="I145" s="8" t="n"/>
       <c r="J145" s="8" t="n"/>
@@ -5189,9 +5190,9 @@
       <c r="A146" s="7" t="n"/>
       <c r="B146" s="7" t="n"/>
       <c r="C146" s="7" t="n"/>
+      <c r="D146" s="7" t="n"/>
       <c r="E146" s="7" t="n"/>
       <c r="F146" s="7" t="n"/>
-      <c r="G146" s="7" t="n"/>
       <c r="H146" s="7" t="n"/>
       <c r="I146" s="7" t="n"/>
       <c r="J146" s="7" t="n"/>
@@ -5219,9 +5220,9 @@
       <c r="A147" s="8" t="n"/>
       <c r="B147" s="8" t="n"/>
       <c r="C147" s="8" t="n"/>
+      <c r="D147" s="8" t="n"/>
       <c r="E147" s="8" t="n"/>
       <c r="F147" s="8" t="n"/>
-      <c r="G147" s="8" t="n"/>
       <c r="H147" s="8" t="n"/>
       <c r="I147" s="8" t="n"/>
       <c r="J147" s="8" t="n"/>
@@ -5249,9 +5250,9 @@
       <c r="A148" s="7" t="n"/>
       <c r="B148" s="7" t="n"/>
       <c r="C148" s="7" t="n"/>
+      <c r="D148" s="7" t="n"/>
       <c r="E148" s="7" t="n"/>
       <c r="F148" s="7" t="n"/>
-      <c r="G148" s="7" t="n"/>
       <c r="H148" s="7" t="n"/>
       <c r="I148" s="7" t="n"/>
       <c r="J148" s="7" t="n"/>
@@ -5279,9 +5280,9 @@
       <c r="A149" s="8" t="n"/>
       <c r="B149" s="8" t="n"/>
       <c r="C149" s="8" t="n"/>
+      <c r="D149" s="8" t="n"/>
       <c r="E149" s="8" t="n"/>
       <c r="F149" s="8" t="n"/>
-      <c r="G149" s="8" t="n"/>
       <c r="H149" s="8" t="n"/>
       <c r="I149" s="8" t="n"/>
       <c r="J149" s="8" t="n"/>
@@ -5309,9 +5310,9 @@
       <c r="A150" s="7" t="n"/>
       <c r="B150" s="7" t="n"/>
       <c r="C150" s="7" t="n"/>
+      <c r="D150" s="7" t="n"/>
       <c r="E150" s="7" t="n"/>
       <c r="F150" s="7" t="n"/>
-      <c r="G150" s="7" t="n"/>
       <c r="H150" s="7" t="n"/>
       <c r="I150" s="7" t="n"/>
       <c r="J150" s="7" t="n"/>
@@ -5339,9 +5340,9 @@
       <c r="A151" s="8" t="n"/>
       <c r="B151" s="8" t="n"/>
       <c r="C151" s="8" t="n"/>
+      <c r="D151" s="8" t="n"/>
       <c r="E151" s="8" t="n"/>
       <c r="F151" s="8" t="n"/>
-      <c r="G151" s="8" t="n"/>
       <c r="H151" s="8" t="n"/>
       <c r="I151" s="8" t="n"/>
       <c r="J151" s="8" t="n"/>
@@ -5369,9 +5370,9 @@
       <c r="A152" s="7" t="n"/>
       <c r="B152" s="7" t="n"/>
       <c r="C152" s="7" t="n"/>
+      <c r="D152" s="7" t="n"/>
       <c r="E152" s="7" t="n"/>
       <c r="F152" s="7" t="n"/>
-      <c r="G152" s="7" t="n"/>
       <c r="H152" s="7" t="n"/>
       <c r="I152" s="7" t="n"/>
       <c r="J152" s="7" t="n"/>
@@ -5399,9 +5400,9 @@
       <c r="A153" s="8" t="n"/>
       <c r="B153" s="8" t="n"/>
       <c r="C153" s="8" t="n"/>
+      <c r="D153" s="8" t="n"/>
       <c r="E153" s="8" t="n"/>
       <c r="F153" s="8" t="n"/>
-      <c r="G153" s="8" t="n"/>
       <c r="H153" s="8" t="n"/>
       <c r="I153" s="8" t="n"/>
       <c r="J153" s="8" t="n"/>
@@ -5429,9 +5430,9 @@
       <c r="A154" s="7" t="n"/>
       <c r="B154" s="7" t="n"/>
       <c r="C154" s="7" t="n"/>
+      <c r="D154" s="7" t="n"/>
       <c r="E154" s="7" t="n"/>
       <c r="F154" s="7" t="n"/>
-      <c r="G154" s="7" t="n"/>
       <c r="H154" s="7" t="n"/>
       <c r="I154" s="7" t="n"/>
       <c r="J154" s="7" t="n"/>
@@ -5459,9 +5460,9 @@
       <c r="A155" s="8" t="n"/>
       <c r="B155" s="8" t="n"/>
       <c r="C155" s="8" t="n"/>
+      <c r="D155" s="8" t="n"/>
       <c r="E155" s="8" t="n"/>
       <c r="F155" s="8" t="n"/>
-      <c r="G155" s="8" t="n"/>
       <c r="H155" s="8" t="n"/>
       <c r="I155" s="8" t="n"/>
       <c r="J155" s="8" t="n"/>
@@ -5489,9 +5490,9 @@
       <c r="A156" s="7" t="n"/>
       <c r="B156" s="7" t="n"/>
       <c r="C156" s="7" t="n"/>
+      <c r="D156" s="7" t="n"/>
       <c r="E156" s="7" t="n"/>
       <c r="F156" s="7" t="n"/>
-      <c r="G156" s="7" t="n"/>
       <c r="H156" s="7" t="n"/>
       <c r="I156" s="7" t="n"/>
       <c r="J156" s="7" t="n"/>
@@ -5519,9 +5520,9 @@
       <c r="A157" s="8" t="n"/>
       <c r="B157" s="8" t="n"/>
       <c r="C157" s="8" t="n"/>
+      <c r="D157" s="8" t="n"/>
       <c r="E157" s="8" t="n"/>
       <c r="F157" s="8" t="n"/>
-      <c r="G157" s="8" t="n"/>
       <c r="H157" s="8" t="n"/>
       <c r="I157" s="8" t="n"/>
       <c r="J157" s="8" t="n"/>
@@ -5549,9 +5550,9 @@
       <c r="A158" s="7" t="n"/>
       <c r="B158" s="7" t="n"/>
       <c r="C158" s="7" t="n"/>
+      <c r="D158" s="7" t="n"/>
       <c r="E158" s="7" t="n"/>
       <c r="F158" s="7" t="n"/>
-      <c r="G158" s="7" t="n"/>
       <c r="H158" s="7" t="n"/>
       <c r="I158" s="7" t="n"/>
       <c r="J158" s="7" t="n"/>
@@ -5579,9 +5580,9 @@
       <c r="A159" s="8" t="n"/>
       <c r="B159" s="8" t="n"/>
       <c r="C159" s="8" t="n"/>
+      <c r="D159" s="8" t="n"/>
       <c r="E159" s="8" t="n"/>
       <c r="F159" s="8" t="n"/>
-      <c r="G159" s="8" t="n"/>
       <c r="H159" s="8" t="n"/>
       <c r="I159" s="8" t="n"/>
       <c r="J159" s="8" t="n"/>
@@ -5609,9 +5610,9 @@
       <c r="A160" s="7" t="n"/>
       <c r="B160" s="7" t="n"/>
       <c r="C160" s="7" t="n"/>
+      <c r="D160" s="7" t="n"/>
       <c r="E160" s="7" t="n"/>
       <c r="F160" s="7" t="n"/>
-      <c r="G160" s="7" t="n"/>
       <c r="H160" s="7" t="n"/>
       <c r="I160" s="7" t="n"/>
       <c r="J160" s="7" t="n"/>
@@ -5639,9 +5640,9 @@
       <c r="A161" s="8" t="n"/>
       <c r="B161" s="8" t="n"/>
       <c r="C161" s="8" t="n"/>
+      <c r="D161" s="8" t="n"/>
       <c r="E161" s="8" t="n"/>
       <c r="F161" s="8" t="n"/>
-      <c r="G161" s="8" t="n"/>
       <c r="H161" s="8" t="n"/>
       <c r="I161" s="8" t="n"/>
       <c r="J161" s="8" t="n"/>
@@ -5669,9 +5670,9 @@
       <c r="A162" s="7" t="n"/>
       <c r="B162" s="7" t="n"/>
       <c r="C162" s="7" t="n"/>
+      <c r="D162" s="7" t="n"/>
       <c r="E162" s="7" t="n"/>
       <c r="F162" s="7" t="n"/>
-      <c r="G162" s="7" t="n"/>
       <c r="H162" s="7" t="n"/>
       <c r="I162" s="7" t="n"/>
       <c r="J162" s="7" t="n"/>
@@ -5699,9 +5700,9 @@
       <c r="A163" s="8" t="n"/>
       <c r="B163" s="8" t="n"/>
       <c r="C163" s="8" t="n"/>
+      <c r="D163" s="8" t="n"/>
       <c r="E163" s="8" t="n"/>
       <c r="F163" s="8" t="n"/>
-      <c r="G163" s="8" t="n"/>
       <c r="H163" s="8" t="n"/>
       <c r="I163" s="8" t="n"/>
       <c r="J163" s="8" t="n"/>
@@ -5729,9 +5730,9 @@
       <c r="A164" s="7" t="n"/>
       <c r="B164" s="7" t="n"/>
       <c r="C164" s="7" t="n"/>
+      <c r="D164" s="7" t="n"/>
       <c r="E164" s="7" t="n"/>
       <c r="F164" s="7" t="n"/>
-      <c r="G164" s="7" t="n"/>
       <c r="H164" s="7" t="n"/>
       <c r="I164" s="7" t="n"/>
       <c r="J164" s="7" t="n"/>
@@ -5759,9 +5760,9 @@
       <c r="A165" s="8" t="n"/>
       <c r="B165" s="8" t="n"/>
       <c r="C165" s="8" t="n"/>
+      <c r="D165" s="8" t="n"/>
       <c r="E165" s="8" t="n"/>
       <c r="F165" s="8" t="n"/>
-      <c r="G165" s="8" t="n"/>
       <c r="H165" s="8" t="n"/>
       <c r="I165" s="8" t="n"/>
       <c r="J165" s="8" t="n"/>
@@ -5789,9 +5790,9 @@
       <c r="A166" s="7" t="n"/>
       <c r="B166" s="7" t="n"/>
       <c r="C166" s="7" t="n"/>
+      <c r="D166" s="7" t="n"/>
       <c r="E166" s="7" t="n"/>
       <c r="F166" s="7" t="n"/>
-      <c r="G166" s="7" t="n"/>
       <c r="H166" s="7" t="n"/>
       <c r="I166" s="7" t="n"/>
       <c r="J166" s="7" t="n"/>
@@ -5819,9 +5820,9 @@
       <c r="A167" s="8" t="n"/>
       <c r="B167" s="8" t="n"/>
       <c r="C167" s="8" t="n"/>
+      <c r="D167" s="8" t="n"/>
       <c r="E167" s="8" t="n"/>
       <c r="F167" s="8" t="n"/>
-      <c r="G167" s="8" t="n"/>
       <c r="H167" s="8" t="n"/>
       <c r="I167" s="8" t="n"/>
       <c r="J167" s="8" t="n"/>
@@ -5849,9 +5850,9 @@
       <c r="A168" s="7" t="n"/>
       <c r="B168" s="7" t="n"/>
       <c r="C168" s="7" t="n"/>
+      <c r="D168" s="7" t="n"/>
       <c r="E168" s="7" t="n"/>
       <c r="F168" s="7" t="n"/>
-      <c r="G168" s="7" t="n"/>
       <c r="H168" s="7" t="n"/>
       <c r="I168" s="7" t="n"/>
       <c r="J168" s="7" t="n"/>
@@ -5879,9 +5880,9 @@
       <c r="A169" s="8" t="n"/>
       <c r="B169" s="8" t="n"/>
       <c r="C169" s="8" t="n"/>
+      <c r="D169" s="8" t="n"/>
       <c r="E169" s="8" t="n"/>
       <c r="F169" s="8" t="n"/>
-      <c r="G169" s="8" t="n"/>
       <c r="H169" s="8" t="n"/>
       <c r="I169" s="8" t="n"/>
       <c r="J169" s="8" t="n"/>
@@ -5909,9 +5910,9 @@
       <c r="A170" s="7" t="n"/>
       <c r="B170" s="7" t="n"/>
       <c r="C170" s="7" t="n"/>
+      <c r="D170" s="7" t="n"/>
       <c r="E170" s="7" t="n"/>
       <c r="F170" s="7" t="n"/>
-      <c r="G170" s="7" t="n"/>
       <c r="H170" s="7" t="n"/>
       <c r="I170" s="7" t="n"/>
       <c r="J170" s="7" t="n"/>
@@ -5939,9 +5940,9 @@
       <c r="A171" s="8" t="n"/>
       <c r="B171" s="8" t="n"/>
       <c r="C171" s="8" t="n"/>
+      <c r="D171" s="8" t="n"/>
       <c r="E171" s="8" t="n"/>
       <c r="F171" s="8" t="n"/>
-      <c r="G171" s="8" t="n"/>
       <c r="H171" s="8" t="n"/>
       <c r="I171" s="8" t="n"/>
       <c r="J171" s="8" t="n"/>
@@ -5969,9 +5970,9 @@
       <c r="A172" s="7" t="n"/>
       <c r="B172" s="7" t="n"/>
       <c r="C172" s="7" t="n"/>
+      <c r="D172" s="7" t="n"/>
       <c r="E172" s="7" t="n"/>
       <c r="F172" s="7" t="n"/>
-      <c r="G172" s="7" t="n"/>
       <c r="H172" s="7" t="n"/>
       <c r="I172" s="7" t="n"/>
       <c r="J172" s="7" t="n"/>
@@ -5999,9 +6000,9 @@
       <c r="A173" s="8" t="n"/>
       <c r="B173" s="8" t="n"/>
       <c r="C173" s="8" t="n"/>
+      <c r="D173" s="8" t="n"/>
       <c r="E173" s="8" t="n"/>
       <c r="F173" s="8" t="n"/>
-      <c r="G173" s="8" t="n"/>
       <c r="H173" s="8" t="n"/>
       <c r="I173" s="8" t="n"/>
       <c r="J173" s="8" t="n"/>
@@ -6029,9 +6030,9 @@
       <c r="A174" s="7" t="n"/>
       <c r="B174" s="7" t="n"/>
       <c r="C174" s="7" t="n"/>
+      <c r="D174" s="7" t="n"/>
       <c r="E174" s="7" t="n"/>
       <c r="F174" s="7" t="n"/>
-      <c r="G174" s="7" t="n"/>
       <c r="H174" s="7" t="n"/>
       <c r="I174" s="7" t="n"/>
       <c r="J174" s="7" t="n"/>
@@ -6059,9 +6060,9 @@
       <c r="A175" s="8" t="n"/>
       <c r="B175" s="8" t="n"/>
       <c r="C175" s="8" t="n"/>
+      <c r="D175" s="8" t="n"/>
       <c r="E175" s="8" t="n"/>
       <c r="F175" s="8" t="n"/>
-      <c r="G175" s="8" t="n"/>
       <c r="H175" s="8" t="n"/>
       <c r="I175" s="8" t="n"/>
       <c r="J175" s="8" t="n"/>
@@ -6089,9 +6090,9 @@
       <c r="A176" s="7" t="n"/>
       <c r="B176" s="7" t="n"/>
       <c r="C176" s="7" t="n"/>
+      <c r="D176" s="7" t="n"/>
       <c r="E176" s="7" t="n"/>
       <c r="F176" s="7" t="n"/>
-      <c r="G176" s="7" t="n"/>
       <c r="H176" s="7" t="n"/>
       <c r="I176" s="7" t="n"/>
       <c r="J176" s="7" t="n"/>
@@ -6119,9 +6120,9 @@
       <c r="A177" s="8" t="n"/>
       <c r="B177" s="8" t="n"/>
       <c r="C177" s="8" t="n"/>
+      <c r="D177" s="8" t="n"/>
       <c r="E177" s="8" t="n"/>
       <c r="F177" s="8" t="n"/>
-      <c r="G177" s="8" t="n"/>
       <c r="H177" s="8" t="n"/>
       <c r="I177" s="8" t="n"/>
       <c r="J177" s="8" t="n"/>
@@ -6149,9 +6150,9 @@
       <c r="A178" s="7" t="n"/>
       <c r="B178" s="7" t="n"/>
       <c r="C178" s="7" t="n"/>
+      <c r="D178" s="7" t="n"/>
       <c r="E178" s="7" t="n"/>
       <c r="F178" s="7" t="n"/>
-      <c r="G178" s="7" t="n"/>
       <c r="H178" s="7" t="n"/>
       <c r="I178" s="7" t="n"/>
       <c r="J178" s="7" t="n"/>
@@ -6179,9 +6180,9 @@
       <c r="A179" s="8" t="n"/>
       <c r="B179" s="8" t="n"/>
       <c r="C179" s="8" t="n"/>
+      <c r="D179" s="8" t="n"/>
       <c r="E179" s="8" t="n"/>
       <c r="F179" s="8" t="n"/>
-      <c r="G179" s="8" t="n"/>
       <c r="H179" s="8" t="n"/>
       <c r="I179" s="8" t="n"/>
       <c r="J179" s="8" t="n"/>
@@ -6209,9 +6210,9 @@
       <c r="A180" s="7" t="n"/>
       <c r="B180" s="7" t="n"/>
       <c r="C180" s="7" t="n"/>
+      <c r="D180" s="7" t="n"/>
       <c r="E180" s="7" t="n"/>
       <c r="F180" s="7" t="n"/>
-      <c r="G180" s="7" t="n"/>
       <c r="H180" s="7" t="n"/>
       <c r="I180" s="7" t="n"/>
       <c r="J180" s="7" t="n"/>
@@ -6239,9 +6240,9 @@
       <c r="A181" s="8" t="n"/>
       <c r="B181" s="8" t="n"/>
       <c r="C181" s="8" t="n"/>
+      <c r="D181" s="8" t="n"/>
       <c r="E181" s="8" t="n"/>
       <c r="F181" s="8" t="n"/>
-      <c r="G181" s="8" t="n"/>
       <c r="H181" s="8" t="n"/>
       <c r="I181" s="8" t="n"/>
       <c r="J181" s="8" t="n"/>
@@ -6269,9 +6270,9 @@
       <c r="A182" s="7" t="n"/>
       <c r="B182" s="7" t="n"/>
       <c r="C182" s="7" t="n"/>
+      <c r="D182" s="7" t="n"/>
       <c r="E182" s="7" t="n"/>
       <c r="F182" s="7" t="n"/>
-      <c r="G182" s="7" t="n"/>
       <c r="H182" s="7" t="n"/>
       <c r="I182" s="7" t="n"/>
       <c r="J182" s="7" t="n"/>
@@ -6299,9 +6300,9 @@
       <c r="A183" s="8" t="n"/>
       <c r="B183" s="8" t="n"/>
       <c r="C183" s="8" t="n"/>
+      <c r="D183" s="8" t="n"/>
       <c r="E183" s="8" t="n"/>
       <c r="F183" s="8" t="n"/>
-      <c r="G183" s="8" t="n"/>
       <c r="H183" s="8" t="n"/>
       <c r="I183" s="8" t="n"/>
       <c r="J183" s="8" t="n"/>
@@ -6329,9 +6330,9 @@
       <c r="A184" s="7" t="n"/>
       <c r="B184" s="7" t="n"/>
       <c r="C184" s="7" t="n"/>
+      <c r="D184" s="7" t="n"/>
       <c r="E184" s="7" t="n"/>
       <c r="F184" s="7" t="n"/>
-      <c r="G184" s="7" t="n"/>
       <c r="H184" s="7" t="n"/>
       <c r="I184" s="7" t="n"/>
       <c r="J184" s="7" t="n"/>
@@ -6359,9 +6360,9 @@
       <c r="A185" s="8" t="n"/>
       <c r="B185" s="8" t="n"/>
       <c r="C185" s="8" t="n"/>
+      <c r="D185" s="8" t="n"/>
       <c r="E185" s="8" t="n"/>
       <c r="F185" s="8" t="n"/>
-      <c r="G185" s="8" t="n"/>
       <c r="H185" s="8" t="n"/>
       <c r="I185" s="8" t="n"/>
       <c r="J185" s="8" t="n"/>
@@ -6389,9 +6390,9 @@
       <c r="A186" s="7" t="n"/>
       <c r="B186" s="7" t="n"/>
       <c r="C186" s="7" t="n"/>
+      <c r="D186" s="7" t="n"/>
       <c r="E186" s="7" t="n"/>
       <c r="F186" s="7" t="n"/>
-      <c r="G186" s="7" t="n"/>
       <c r="H186" s="7" t="n"/>
       <c r="I186" s="7" t="n"/>
       <c r="J186" s="7" t="n"/>
@@ -6419,9 +6420,9 @@
       <c r="A187" s="8" t="n"/>
       <c r="B187" s="8" t="n"/>
       <c r="C187" s="8" t="n"/>
+      <c r="D187" s="8" t="n"/>
       <c r="E187" s="8" t="n"/>
       <c r="F187" s="8" t="n"/>
-      <c r="G187" s="8" t="n"/>
       <c r="H187" s="8" t="n"/>
       <c r="I187" s="8" t="n"/>
       <c r="J187" s="8" t="n"/>
@@ -6449,9 +6450,9 @@
       <c r="A188" s="7" t="n"/>
       <c r="B188" s="7" t="n"/>
       <c r="C188" s="7" t="n"/>
+      <c r="D188" s="7" t="n"/>
       <c r="E188" s="7" t="n"/>
       <c r="F188" s="7" t="n"/>
-      <c r="G188" s="7" t="n"/>
       <c r="H188" s="7" t="n"/>
       <c r="I188" s="7" t="n"/>
       <c r="J188" s="7" t="n"/>
@@ -6479,9 +6480,9 @@
       <c r="A189" s="8" t="n"/>
       <c r="B189" s="8" t="n"/>
       <c r="C189" s="8" t="n"/>
+      <c r="D189" s="8" t="n"/>
       <c r="E189" s="8" t="n"/>
       <c r="F189" s="8" t="n"/>
-      <c r="G189" s="8" t="n"/>
       <c r="H189" s="8" t="n"/>
       <c r="I189" s="8" t="n"/>
       <c r="J189" s="8" t="n"/>
@@ -6509,9 +6510,9 @@
       <c r="A190" s="7" t="n"/>
       <c r="B190" s="7" t="n"/>
       <c r="C190" s="7" t="n"/>
+      <c r="D190" s="7" t="n"/>
       <c r="E190" s="7" t="n"/>
       <c r="F190" s="7" t="n"/>
-      <c r="G190" s="7" t="n"/>
       <c r="H190" s="7" t="n"/>
       <c r="I190" s="7" t="n"/>
       <c r="J190" s="7" t="n"/>
@@ -6539,9 +6540,9 @@
       <c r="A191" s="8" t="n"/>
       <c r="B191" s="8" t="n"/>
       <c r="C191" s="8" t="n"/>
+      <c r="D191" s="8" t="n"/>
       <c r="E191" s="8" t="n"/>
       <c r="F191" s="8" t="n"/>
-      <c r="G191" s="8" t="n"/>
       <c r="H191" s="8" t="n"/>
       <c r="I191" s="8" t="n"/>
       <c r="J191" s="8" t="n"/>
@@ -6569,9 +6570,9 @@
       <c r="A192" s="7" t="n"/>
       <c r="B192" s="7" t="n"/>
       <c r="C192" s="7" t="n"/>
+      <c r="D192" s="7" t="n"/>
       <c r="E192" s="7" t="n"/>
       <c r="F192" s="7" t="n"/>
-      <c r="G192" s="7" t="n"/>
       <c r="H192" s="7" t="n"/>
       <c r="I192" s="7" t="n"/>
       <c r="J192" s="7" t="n"/>
@@ -6599,9 +6600,9 @@
       <c r="A193" s="8" t="n"/>
       <c r="B193" s="8" t="n"/>
       <c r="C193" s="8" t="n"/>
+      <c r="D193" s="8" t="n"/>
       <c r="E193" s="8" t="n"/>
       <c r="F193" s="8" t="n"/>
-      <c r="G193" s="8" t="n"/>
       <c r="H193" s="8" t="n"/>
       <c r="I193" s="8" t="n"/>
       <c r="J193" s="8" t="n"/>
@@ -6629,9 +6630,9 @@
       <c r="A194" s="7" t="n"/>
       <c r="B194" s="7" t="n"/>
       <c r="C194" s="7" t="n"/>
+      <c r="D194" s="7" t="n"/>
       <c r="E194" s="7" t="n"/>
       <c r="F194" s="7" t="n"/>
-      <c r="G194" s="7" t="n"/>
       <c r="H194" s="7" t="n"/>
       <c r="I194" s="7" t="n"/>
       <c r="J194" s="7" t="n"/>
@@ -6659,9 +6660,9 @@
       <c r="A195" s="8" t="n"/>
       <c r="B195" s="8" t="n"/>
       <c r="C195" s="8" t="n"/>
+      <c r="D195" s="8" t="n"/>
       <c r="E195" s="8" t="n"/>
       <c r="F195" s="8" t="n"/>
-      <c r="G195" s="8" t="n"/>
       <c r="H195" s="8" t="n"/>
       <c r="I195" s="8" t="n"/>
       <c r="J195" s="8" t="n"/>
@@ -6689,9 +6690,9 @@
       <c r="A196" s="7" t="n"/>
       <c r="B196" s="7" t="n"/>
       <c r="C196" s="7" t="n"/>
+      <c r="D196" s="7" t="n"/>
       <c r="E196" s="7" t="n"/>
       <c r="F196" s="7" t="n"/>
-      <c r="G196" s="7" t="n"/>
       <c r="H196" s="7" t="n"/>
       <c r="I196" s="7" t="n"/>
       <c r="J196" s="7" t="n"/>
@@ -6719,9 +6720,9 @@
       <c r="A197" s="8" t="n"/>
       <c r="B197" s="8" t="n"/>
       <c r="C197" s="8" t="n"/>
+      <c r="D197" s="8" t="n"/>
       <c r="E197" s="8" t="n"/>
       <c r="F197" s="8" t="n"/>
-      <c r="G197" s="8" t="n"/>
       <c r="H197" s="8" t="n"/>
       <c r="I197" s="8" t="n"/>
       <c r="J197" s="8" t="n"/>
@@ -6749,9 +6750,9 @@
       <c r="A198" s="7" t="n"/>
       <c r="B198" s="7" t="n"/>
       <c r="C198" s="7" t="n"/>
+      <c r="D198" s="7" t="n"/>
       <c r="E198" s="7" t="n"/>
       <c r="F198" s="7" t="n"/>
-      <c r="G198" s="7" t="n"/>
       <c r="H198" s="7" t="n"/>
       <c r="I198" s="7" t="n"/>
       <c r="J198" s="7" t="n"/>
@@ -6779,9 +6780,9 @@
       <c r="A199" s="8" t="n"/>
       <c r="B199" s="8" t="n"/>
       <c r="C199" s="8" t="n"/>
+      <c r="D199" s="8" t="n"/>
       <c r="E199" s="8" t="n"/>
       <c r="F199" s="8" t="n"/>
-      <c r="G199" s="8" t="n"/>
       <c r="H199" s="8" t="n"/>
       <c r="I199" s="8" t="n"/>
       <c r="J199" s="8" t="n"/>
@@ -6809,9 +6810,9 @@
       <c r="A200" s="7" t="n"/>
       <c r="B200" s="7" t="n"/>
       <c r="C200" s="7" t="n"/>
+      <c r="D200" s="7" t="n"/>
       <c r="E200" s="7" t="n"/>
       <c r="F200" s="7" t="n"/>
-      <c r="G200" s="7" t="n"/>
       <c r="H200" s="7" t="n"/>
       <c r="I200" s="7" t="n"/>
       <c r="J200" s="7" t="n"/>
@@ -6839,9 +6840,9 @@
       <c r="A201" s="8" t="n"/>
       <c r="B201" s="8" t="n"/>
       <c r="C201" s="8" t="n"/>
+      <c r="D201" s="8" t="n"/>
       <c r="E201" s="8" t="n"/>
       <c r="F201" s="8" t="n"/>
-      <c r="G201" s="8" t="n"/>
       <c r="H201" s="8" t="n"/>
       <c r="I201" s="8" t="n"/>
       <c r="J201" s="8" t="n"/>
@@ -6869,9 +6870,9 @@
       <c r="A202" s="7" t="n"/>
       <c r="B202" s="7" t="n"/>
       <c r="C202" s="7" t="n"/>
+      <c r="D202" s="7" t="n"/>
       <c r="E202" s="7" t="n"/>
       <c r="F202" s="7" t="n"/>
-      <c r="G202" s="7" t="n"/>
       <c r="H202" s="7" t="n"/>
       <c r="I202" s="7" t="n"/>
       <c r="J202" s="7" t="n"/>
@@ -6899,9 +6900,9 @@
       <c r="A203" s="8" t="n"/>
       <c r="B203" s="8" t="n"/>
       <c r="C203" s="8" t="n"/>
+      <c r="D203" s="8" t="n"/>
       <c r="E203" s="8" t="n"/>
       <c r="F203" s="8" t="n"/>
-      <c r="G203" s="8" t="n"/>
       <c r="H203" s="8" t="n"/>
       <c r="I203" s="8" t="n"/>
       <c r="J203" s="8" t="n"/>

--- a/MaxImporta_Modelos_Importacao.xlsx
+++ b/MaxImporta_Modelos_Importacao.xlsx
@@ -10990,7 +10990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M203"/>
+  <dimension ref="A1:N203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" style="10" min="1" max="1"/>
@@ -11000,6 +11000,7 @@
     <col width="14" customWidth="1" style="10" min="11" max="11"/>
     <col width="18" customWidth="1" style="10" min="12" max="12"/>
     <col width="16" customWidth="1" style="10" min="13" max="13"/>
+    <col width="14" customWidth="1" style="10" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="19.95" customHeight="1" s="10">
@@ -11092,6 +11093,13 @@
 (máx. 30 caracteres)</t>
         </is>
       </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Empresa (loja)
+(cofId da config)
+vazio = 1</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="18" customHeight="1" s="10">
       <c r="A3" s="5" t="inlineStr">
@@ -11159,6 +11167,11 @@
           <t>pgtNossoNumero</t>
         </is>
       </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>empId</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="16.05" customHeight="1" s="10">
       <c r="A4" s="7" t="n"/>
@@ -14162,7 +14175,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/MaxImporta_Modelos_Importacao.xlsx
+++ b/MaxImporta_Modelos_Importacao.xlsx
@@ -6941,7 +6941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R203"/>
+  <dimension ref="A1:S203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="15" customWidth="1" style="10" min="1" max="1"/>
@@ -6956,7 +6956,7 @@
     <col width="14" customWidth="1" style="10" min="11" max="12"/>
     <col width="18" customWidth="1" style="10" min="13" max="13"/>
     <col width="14" customWidth="1" style="10" min="14" max="16"/>
-    <col width="18" customWidth="1" style="10" min="17" max="17"/>
+    <col width="16" customWidth="1" style="10" min="17" max="17"/>
     <col width="18" customWidth="1" style="10" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -7073,10 +7073,16 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
+          <t>Celular
+(máx. 20 caracteres)</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
           <t>Tipo de Cadastro</t>
         </is>
       </c>
-      <c r="R2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>Tipo
 0=Pessoa Física
@@ -7167,10 +7173,15 @@
       </c>
       <c r="Q3" s="6" t="inlineStr">
         <is>
+          <t>cliCelular</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
           <t>cliTipoCad</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="S3" s="6" t="inlineStr">
         <is>
           <t>cliTipo</t>
         </is>
@@ -7193,7 +7204,7 @@
       <c r="N4" s="7" t="n"/>
       <c r="O4" s="7" t="n"/>
       <c r="P4" s="7" t="n"/>
-      <c r="Q4" s="7" t="n"/>
+      <c r="R4" s="7" t="n"/>
     </row>
     <row r="5" ht="16.05" customHeight="1" s="10">
       <c r="A5" s="8" t="n"/>
@@ -7212,7 +7223,7 @@
       <c r="N5" s="8" t="n"/>
       <c r="O5" s="8" t="n"/>
       <c r="P5" s="8" t="n"/>
-      <c r="Q5" s="8" t="n"/>
+      <c r="R5" s="8" t="n"/>
     </row>
     <row r="6" ht="16.05" customHeight="1" s="10">
       <c r="A6" s="7" t="n"/>
@@ -7231,7 +7242,7 @@
       <c r="N6" s="7" t="n"/>
       <c r="O6" s="7" t="n"/>
       <c r="P6" s="7" t="n"/>
-      <c r="Q6" s="7" t="n"/>
+      <c r="R6" s="7" t="n"/>
     </row>
     <row r="7" ht="16.05" customHeight="1" s="10">
       <c r="A7" s="8" t="n"/>
@@ -7250,7 +7261,7 @@
       <c r="N7" s="8" t="n"/>
       <c r="O7" s="8" t="n"/>
       <c r="P7" s="8" t="n"/>
-      <c r="Q7" s="8" t="n"/>
+      <c r="R7" s="8" t="n"/>
     </row>
     <row r="8" ht="16.05" customHeight="1" s="10">
       <c r="A8" s="7" t="n"/>
@@ -7269,7 +7280,7 @@
       <c r="N8" s="7" t="n"/>
       <c r="O8" s="7" t="n"/>
       <c r="P8" s="7" t="n"/>
-      <c r="Q8" s="7" t="n"/>
+      <c r="R8" s="7" t="n"/>
     </row>
     <row r="9" ht="16.05" customHeight="1" s="10">
       <c r="A9" s="8" t="n"/>
@@ -7288,7 +7299,7 @@
       <c r="N9" s="8" t="n"/>
       <c r="O9" s="8" t="n"/>
       <c r="P9" s="8" t="n"/>
-      <c r="Q9" s="8" t="n"/>
+      <c r="R9" s="8" t="n"/>
     </row>
     <row r="10" ht="16.05" customHeight="1" s="10">
       <c r="A10" s="7" t="n"/>
@@ -7307,7 +7318,7 @@
       <c r="N10" s="7" t="n"/>
       <c r="O10" s="7" t="n"/>
       <c r="P10" s="7" t="n"/>
-      <c r="Q10" s="7" t="n"/>
+      <c r="R10" s="7" t="n"/>
     </row>
     <row r="11" ht="16.05" customHeight="1" s="10">
       <c r="A11" s="8" t="n"/>
@@ -7326,7 +7337,7 @@
       <c r="N11" s="8" t="n"/>
       <c r="O11" s="8" t="n"/>
       <c r="P11" s="8" t="n"/>
-      <c r="Q11" s="8" t="n"/>
+      <c r="R11" s="8" t="n"/>
     </row>
     <row r="12" ht="16.05" customHeight="1" s="10">
       <c r="A12" s="7" t="n"/>
@@ -7345,7 +7356,7 @@
       <c r="N12" s="7" t="n"/>
       <c r="O12" s="7" t="n"/>
       <c r="P12" s="7" t="n"/>
-      <c r="Q12" s="7" t="n"/>
+      <c r="R12" s="7" t="n"/>
     </row>
     <row r="13" ht="16.05" customHeight="1" s="10">
       <c r="A13" s="8" t="n"/>
@@ -7364,7 +7375,7 @@
       <c r="N13" s="8" t="n"/>
       <c r="O13" s="8" t="n"/>
       <c r="P13" s="8" t="n"/>
-      <c r="Q13" s="8" t="n"/>
+      <c r="R13" s="8" t="n"/>
     </row>
     <row r="14" ht="16.05" customHeight="1" s="10">
       <c r="A14" s="7" t="n"/>
@@ -7383,7 +7394,7 @@
       <c r="N14" s="7" t="n"/>
       <c r="O14" s="7" t="n"/>
       <c r="P14" s="7" t="n"/>
-      <c r="Q14" s="7" t="n"/>
+      <c r="R14" s="7" t="n"/>
     </row>
     <row r="15" ht="16.05" customHeight="1" s="10">
       <c r="A15" s="8" t="n"/>
@@ -7402,7 +7413,7 @@
       <c r="N15" s="8" t="n"/>
       <c r="O15" s="8" t="n"/>
       <c r="P15" s="8" t="n"/>
-      <c r="Q15" s="8" t="n"/>
+      <c r="R15" s="8" t="n"/>
     </row>
     <row r="16" ht="16.05" customHeight="1" s="10">
       <c r="A16" s="7" t="n"/>
@@ -7421,7 +7432,7 @@
       <c r="N16" s="7" t="n"/>
       <c r="O16" s="7" t="n"/>
       <c r="P16" s="7" t="n"/>
-      <c r="Q16" s="7" t="n"/>
+      <c r="R16" s="7" t="n"/>
     </row>
     <row r="17" ht="16.05" customHeight="1" s="10">
       <c r="A17" s="8" t="n"/>
@@ -7440,7 +7451,7 @@
       <c r="N17" s="8" t="n"/>
       <c r="O17" s="8" t="n"/>
       <c r="P17" s="8" t="n"/>
-      <c r="Q17" s="8" t="n"/>
+      <c r="R17" s="8" t="n"/>
     </row>
     <row r="18" ht="16.05" customHeight="1" s="10">
       <c r="A18" s="7" t="n"/>
@@ -7459,7 +7470,7 @@
       <c r="N18" s="7" t="n"/>
       <c r="O18" s="7" t="n"/>
       <c r="P18" s="7" t="n"/>
-      <c r="Q18" s="7" t="n"/>
+      <c r="R18" s="7" t="n"/>
     </row>
     <row r="19" ht="16.05" customHeight="1" s="10">
       <c r="A19" s="8" t="n"/>
@@ -7478,7 +7489,7 @@
       <c r="N19" s="8" t="n"/>
       <c r="O19" s="8" t="n"/>
       <c r="P19" s="8" t="n"/>
-      <c r="Q19" s="8" t="n"/>
+      <c r="R19" s="8" t="n"/>
     </row>
     <row r="20" ht="16.05" customHeight="1" s="10">
       <c r="A20" s="7" t="n"/>
@@ -7497,7 +7508,7 @@
       <c r="N20" s="7" t="n"/>
       <c r="O20" s="7" t="n"/>
       <c r="P20" s="7" t="n"/>
-      <c r="Q20" s="7" t="n"/>
+      <c r="R20" s="7" t="n"/>
     </row>
     <row r="21" ht="16.05" customHeight="1" s="10">
       <c r="A21" s="8" t="n"/>
@@ -7516,7 +7527,7 @@
       <c r="N21" s="8" t="n"/>
       <c r="O21" s="8" t="n"/>
       <c r="P21" s="8" t="n"/>
-      <c r="Q21" s="8" t="n"/>
+      <c r="R21" s="8" t="n"/>
     </row>
     <row r="22" ht="16.05" customHeight="1" s="10">
       <c r="A22" s="7" t="n"/>
@@ -7535,7 +7546,7 @@
       <c r="N22" s="7" t="n"/>
       <c r="O22" s="7" t="n"/>
       <c r="P22" s="7" t="n"/>
-      <c r="Q22" s="7" t="n"/>
+      <c r="R22" s="7" t="n"/>
     </row>
     <row r="23" ht="16.05" customHeight="1" s="10">
       <c r="A23" s="8" t="n"/>
@@ -7554,7 +7565,7 @@
       <c r="N23" s="8" t="n"/>
       <c r="O23" s="8" t="n"/>
       <c r="P23" s="8" t="n"/>
-      <c r="Q23" s="8" t="n"/>
+      <c r="R23" s="8" t="n"/>
     </row>
     <row r="24" ht="16.05" customHeight="1" s="10">
       <c r="A24" s="7" t="n"/>
@@ -7573,7 +7584,7 @@
       <c r="N24" s="7" t="n"/>
       <c r="O24" s="7" t="n"/>
       <c r="P24" s="7" t="n"/>
-      <c r="Q24" s="7" t="n"/>
+      <c r="R24" s="7" t="n"/>
     </row>
     <row r="25" ht="16.05" customHeight="1" s="10">
       <c r="A25" s="8" t="n"/>
@@ -7592,7 +7603,7 @@
       <c r="N25" s="8" t="n"/>
       <c r="O25" s="8" t="n"/>
       <c r="P25" s="8" t="n"/>
-      <c r="Q25" s="8" t="n"/>
+      <c r="R25" s="8" t="n"/>
     </row>
     <row r="26" ht="16.05" customHeight="1" s="10">
       <c r="A26" s="7" t="n"/>
@@ -7611,7 +7622,7 @@
       <c r="N26" s="7" t="n"/>
       <c r="O26" s="7" t="n"/>
       <c r="P26" s="7" t="n"/>
-      <c r="Q26" s="7" t="n"/>
+      <c r="R26" s="7" t="n"/>
     </row>
     <row r="27" ht="16.05" customHeight="1" s="10">
       <c r="A27" s="8" t="n"/>
@@ -7630,7 +7641,7 @@
       <c r="N27" s="8" t="n"/>
       <c r="O27" s="8" t="n"/>
       <c r="P27" s="8" t="n"/>
-      <c r="Q27" s="8" t="n"/>
+      <c r="R27" s="8" t="n"/>
     </row>
     <row r="28" ht="16.05" customHeight="1" s="10">
       <c r="A28" s="7" t="n"/>
@@ -7649,7 +7660,7 @@
       <c r="N28" s="7" t="n"/>
       <c r="O28" s="7" t="n"/>
       <c r="P28" s="7" t="n"/>
-      <c r="Q28" s="7" t="n"/>
+      <c r="R28" s="7" t="n"/>
     </row>
     <row r="29" ht="16.05" customHeight="1" s="10">
       <c r="A29" s="8" t="n"/>
@@ -7668,7 +7679,7 @@
       <c r="N29" s="8" t="n"/>
       <c r="O29" s="8" t="n"/>
       <c r="P29" s="8" t="n"/>
-      <c r="Q29" s="8" t="n"/>
+      <c r="R29" s="8" t="n"/>
     </row>
     <row r="30" ht="16.05" customHeight="1" s="10">
       <c r="A30" s="7" t="n"/>
@@ -7687,7 +7698,7 @@
       <c r="N30" s="7" t="n"/>
       <c r="O30" s="7" t="n"/>
       <c r="P30" s="7" t="n"/>
-      <c r="Q30" s="7" t="n"/>
+      <c r="R30" s="7" t="n"/>
     </row>
     <row r="31" ht="16.05" customHeight="1" s="10">
       <c r="A31" s="8" t="n"/>
@@ -7706,7 +7717,7 @@
       <c r="N31" s="8" t="n"/>
       <c r="O31" s="8" t="n"/>
       <c r="P31" s="8" t="n"/>
-      <c r="Q31" s="8" t="n"/>
+      <c r="R31" s="8" t="n"/>
     </row>
     <row r="32" ht="16.05" customHeight="1" s="10">
       <c r="A32" s="7" t="n"/>
@@ -7725,7 +7736,7 @@
       <c r="N32" s="7" t="n"/>
       <c r="O32" s="7" t="n"/>
       <c r="P32" s="7" t="n"/>
-      <c r="Q32" s="7" t="n"/>
+      <c r="R32" s="7" t="n"/>
     </row>
     <row r="33" ht="16.05" customHeight="1" s="10">
       <c r="A33" s="8" t="n"/>
@@ -7744,7 +7755,7 @@
       <c r="N33" s="8" t="n"/>
       <c r="O33" s="8" t="n"/>
       <c r="P33" s="8" t="n"/>
-      <c r="Q33" s="8" t="n"/>
+      <c r="R33" s="8" t="n"/>
     </row>
     <row r="34" ht="16.05" customHeight="1" s="10">
       <c r="A34" s="7" t="n"/>
@@ -7763,7 +7774,7 @@
       <c r="N34" s="7" t="n"/>
       <c r="O34" s="7" t="n"/>
       <c r="P34" s="7" t="n"/>
-      <c r="Q34" s="7" t="n"/>
+      <c r="R34" s="7" t="n"/>
     </row>
     <row r="35" ht="16.05" customHeight="1" s="10">
       <c r="A35" s="8" t="n"/>
@@ -7782,7 +7793,7 @@
       <c r="N35" s="8" t="n"/>
       <c r="O35" s="8" t="n"/>
       <c r="P35" s="8" t="n"/>
-      <c r="Q35" s="8" t="n"/>
+      <c r="R35" s="8" t="n"/>
     </row>
     <row r="36" ht="16.05" customHeight="1" s="10">
       <c r="A36" s="7" t="n"/>
@@ -7801,7 +7812,7 @@
       <c r="N36" s="7" t="n"/>
       <c r="O36" s="7" t="n"/>
       <c r="P36" s="7" t="n"/>
-      <c r="Q36" s="7" t="n"/>
+      <c r="R36" s="7" t="n"/>
     </row>
     <row r="37" ht="16.05" customHeight="1" s="10">
       <c r="A37" s="8" t="n"/>
@@ -7820,7 +7831,7 @@
       <c r="N37" s="8" t="n"/>
       <c r="O37" s="8" t="n"/>
       <c r="P37" s="8" t="n"/>
-      <c r="Q37" s="8" t="n"/>
+      <c r="R37" s="8" t="n"/>
     </row>
     <row r="38" ht="16.05" customHeight="1" s="10">
       <c r="A38" s="7" t="n"/>
@@ -7839,7 +7850,7 @@
       <c r="N38" s="7" t="n"/>
       <c r="O38" s="7" t="n"/>
       <c r="P38" s="7" t="n"/>
-      <c r="Q38" s="7" t="n"/>
+      <c r="R38" s="7" t="n"/>
     </row>
     <row r="39" ht="16.05" customHeight="1" s="10">
       <c r="A39" s="8" t="n"/>
@@ -7858,7 +7869,7 @@
       <c r="N39" s="8" t="n"/>
       <c r="O39" s="8" t="n"/>
       <c r="P39" s="8" t="n"/>
-      <c r="Q39" s="8" t="n"/>
+      <c r="R39" s="8" t="n"/>
     </row>
     <row r="40" ht="16.05" customHeight="1" s="10">
       <c r="A40" s="7" t="n"/>
@@ -7877,7 +7888,7 @@
       <c r="N40" s="7" t="n"/>
       <c r="O40" s="7" t="n"/>
       <c r="P40" s="7" t="n"/>
-      <c r="Q40" s="7" t="n"/>
+      <c r="R40" s="7" t="n"/>
     </row>
     <row r="41" ht="16.05" customHeight="1" s="10">
       <c r="A41" s="8" t="n"/>
@@ -7896,7 +7907,7 @@
       <c r="N41" s="8" t="n"/>
       <c r="O41" s="8" t="n"/>
       <c r="P41" s="8" t="n"/>
-      <c r="Q41" s="8" t="n"/>
+      <c r="R41" s="8" t="n"/>
     </row>
     <row r="42" ht="16.05" customHeight="1" s="10">
       <c r="A42" s="7" t="n"/>
@@ -7915,7 +7926,7 @@
       <c r="N42" s="7" t="n"/>
       <c r="O42" s="7" t="n"/>
       <c r="P42" s="7" t="n"/>
-      <c r="Q42" s="7" t="n"/>
+      <c r="R42" s="7" t="n"/>
     </row>
     <row r="43" ht="16.05" customHeight="1" s="10">
       <c r="A43" s="8" t="n"/>
@@ -7934,7 +7945,7 @@
       <c r="N43" s="8" t="n"/>
       <c r="O43" s="8" t="n"/>
       <c r="P43" s="8" t="n"/>
-      <c r="Q43" s="8" t="n"/>
+      <c r="R43" s="8" t="n"/>
     </row>
     <row r="44" ht="16.05" customHeight="1" s="10">
       <c r="A44" s="7" t="n"/>
@@ -7953,7 +7964,7 @@
       <c r="N44" s="7" t="n"/>
       <c r="O44" s="7" t="n"/>
       <c r="P44" s="7" t="n"/>
-      <c r="Q44" s="7" t="n"/>
+      <c r="R44" s="7" t="n"/>
     </row>
     <row r="45" ht="16.05" customHeight="1" s="10">
       <c r="A45" s="8" t="n"/>
@@ -7972,7 +7983,7 @@
       <c r="N45" s="8" t="n"/>
       <c r="O45" s="8" t="n"/>
       <c r="P45" s="8" t="n"/>
-      <c r="Q45" s="8" t="n"/>
+      <c r="R45" s="8" t="n"/>
     </row>
     <row r="46" ht="16.05" customHeight="1" s="10">
       <c r="A46" s="7" t="n"/>
@@ -7991,7 +8002,7 @@
       <c r="N46" s="7" t="n"/>
       <c r="O46" s="7" t="n"/>
       <c r="P46" s="7" t="n"/>
-      <c r="Q46" s="7" t="n"/>
+      <c r="R46" s="7" t="n"/>
     </row>
     <row r="47" ht="16.05" customHeight="1" s="10">
       <c r="A47" s="8" t="n"/>
@@ -8010,7 +8021,7 @@
       <c r="N47" s="8" t="n"/>
       <c r="O47" s="8" t="n"/>
       <c r="P47" s="8" t="n"/>
-      <c r="Q47" s="8" t="n"/>
+      <c r="R47" s="8" t="n"/>
     </row>
     <row r="48" ht="16.05" customHeight="1" s="10">
       <c r="A48" s="7" t="n"/>
@@ -8029,7 +8040,7 @@
       <c r="N48" s="7" t="n"/>
       <c r="O48" s="7" t="n"/>
       <c r="P48" s="7" t="n"/>
-      <c r="Q48" s="7" t="n"/>
+      <c r="R48" s="7" t="n"/>
     </row>
     <row r="49" ht="16.05" customHeight="1" s="10">
       <c r="A49" s="8" t="n"/>
@@ -8048,7 +8059,7 @@
       <c r="N49" s="8" t="n"/>
       <c r="O49" s="8" t="n"/>
       <c r="P49" s="8" t="n"/>
-      <c r="Q49" s="8" t="n"/>
+      <c r="R49" s="8" t="n"/>
     </row>
     <row r="50" ht="16.05" customHeight="1" s="10">
       <c r="A50" s="7" t="n"/>
@@ -8067,7 +8078,7 @@
       <c r="N50" s="7" t="n"/>
       <c r="O50" s="7" t="n"/>
       <c r="P50" s="7" t="n"/>
-      <c r="Q50" s="7" t="n"/>
+      <c r="R50" s="7" t="n"/>
     </row>
     <row r="51" ht="16.05" customHeight="1" s="10">
       <c r="A51" s="8" t="n"/>
@@ -8086,7 +8097,7 @@
       <c r="N51" s="8" t="n"/>
       <c r="O51" s="8" t="n"/>
       <c r="P51" s="8" t="n"/>
-      <c r="Q51" s="8" t="n"/>
+      <c r="R51" s="8" t="n"/>
     </row>
     <row r="52" ht="16.05" customHeight="1" s="10">
       <c r="A52" s="7" t="n"/>
@@ -8105,7 +8116,7 @@
       <c r="N52" s="7" t="n"/>
       <c r="O52" s="7" t="n"/>
       <c r="P52" s="7" t="n"/>
-      <c r="Q52" s="7" t="n"/>
+      <c r="R52" s="7" t="n"/>
     </row>
     <row r="53" ht="16.05" customHeight="1" s="10">
       <c r="A53" s="8" t="n"/>
@@ -8124,7 +8135,7 @@
       <c r="N53" s="8" t="n"/>
       <c r="O53" s="8" t="n"/>
       <c r="P53" s="8" t="n"/>
-      <c r="Q53" s="8" t="n"/>
+      <c r="R53" s="8" t="n"/>
     </row>
     <row r="54" ht="16.05" customHeight="1" s="10">
       <c r="A54" s="7" t="n"/>
@@ -8143,7 +8154,7 @@
       <c r="N54" s="7" t="n"/>
       <c r="O54" s="7" t="n"/>
       <c r="P54" s="7" t="n"/>
-      <c r="Q54" s="7" t="n"/>
+      <c r="R54" s="7" t="n"/>
     </row>
     <row r="55" ht="16.05" customHeight="1" s="10">
       <c r="A55" s="8" t="n"/>
@@ -8162,7 +8173,7 @@
       <c r="N55" s="8" t="n"/>
       <c r="O55" s="8" t="n"/>
       <c r="P55" s="8" t="n"/>
-      <c r="Q55" s="8" t="n"/>
+      <c r="R55" s="8" t="n"/>
     </row>
     <row r="56" ht="16.05" customHeight="1" s="10">
       <c r="A56" s="7" t="n"/>
@@ -8181,7 +8192,7 @@
       <c r="N56" s="7" t="n"/>
       <c r="O56" s="7" t="n"/>
       <c r="P56" s="7" t="n"/>
-      <c r="Q56" s="7" t="n"/>
+      <c r="R56" s="7" t="n"/>
     </row>
     <row r="57" ht="16.05" customHeight="1" s="10">
       <c r="A57" s="8" t="n"/>
@@ -8200,7 +8211,7 @@
       <c r="N57" s="8" t="n"/>
       <c r="O57" s="8" t="n"/>
       <c r="P57" s="8" t="n"/>
-      <c r="Q57" s="8" t="n"/>
+      <c r="R57" s="8" t="n"/>
     </row>
     <row r="58" ht="16.05" customHeight="1" s="10">
       <c r="A58" s="7" t="n"/>
@@ -8219,7 +8230,7 @@
       <c r="N58" s="7" t="n"/>
       <c r="O58" s="7" t="n"/>
       <c r="P58" s="7" t="n"/>
-      <c r="Q58" s="7" t="n"/>
+      <c r="R58" s="7" t="n"/>
     </row>
     <row r="59" ht="16.05" customHeight="1" s="10">
       <c r="A59" s="8" t="n"/>
@@ -8238,7 +8249,7 @@
       <c r="N59" s="8" t="n"/>
       <c r="O59" s="8" t="n"/>
       <c r="P59" s="8" t="n"/>
-      <c r="Q59" s="8" t="n"/>
+      <c r="R59" s="8" t="n"/>
     </row>
     <row r="60" ht="16.05" customHeight="1" s="10">
       <c r="A60" s="7" t="n"/>
@@ -8257,7 +8268,7 @@
       <c r="N60" s="7" t="n"/>
       <c r="O60" s="7" t="n"/>
       <c r="P60" s="7" t="n"/>
-      <c r="Q60" s="7" t="n"/>
+      <c r="R60" s="7" t="n"/>
     </row>
     <row r="61" ht="16.05" customHeight="1" s="10">
       <c r="A61" s="8" t="n"/>
@@ -8276,7 +8287,7 @@
       <c r="N61" s="8" t="n"/>
       <c r="O61" s="8" t="n"/>
       <c r="P61" s="8" t="n"/>
-      <c r="Q61" s="8" t="n"/>
+      <c r="R61" s="8" t="n"/>
     </row>
     <row r="62" ht="16.05" customHeight="1" s="10">
       <c r="A62" s="7" t="n"/>
@@ -8295,7 +8306,7 @@
       <c r="N62" s="7" t="n"/>
       <c r="O62" s="7" t="n"/>
       <c r="P62" s="7" t="n"/>
-      <c r="Q62" s="7" t="n"/>
+      <c r="R62" s="7" t="n"/>
     </row>
     <row r="63" ht="16.05" customHeight="1" s="10">
       <c r="A63" s="8" t="n"/>
@@ -8314,7 +8325,7 @@
       <c r="N63" s="8" t="n"/>
       <c r="O63" s="8" t="n"/>
       <c r="P63" s="8" t="n"/>
-      <c r="Q63" s="8" t="n"/>
+      <c r="R63" s="8" t="n"/>
     </row>
     <row r="64" ht="16.05" customHeight="1" s="10">
       <c r="A64" s="7" t="n"/>
@@ -8333,7 +8344,7 @@
       <c r="N64" s="7" t="n"/>
       <c r="O64" s="7" t="n"/>
       <c r="P64" s="7" t="n"/>
-      <c r="Q64" s="7" t="n"/>
+      <c r="R64" s="7" t="n"/>
     </row>
     <row r="65" ht="16.05" customHeight="1" s="10">
       <c r="A65" s="8" t="n"/>
@@ -8352,7 +8363,7 @@
       <c r="N65" s="8" t="n"/>
       <c r="O65" s="8" t="n"/>
       <c r="P65" s="8" t="n"/>
-      <c r="Q65" s="8" t="n"/>
+      <c r="R65" s="8" t="n"/>
     </row>
     <row r="66" ht="16.05" customHeight="1" s="10">
       <c r="A66" s="7" t="n"/>
@@ -8371,7 +8382,7 @@
       <c r="N66" s="7" t="n"/>
       <c r="O66" s="7" t="n"/>
       <c r="P66" s="7" t="n"/>
-      <c r="Q66" s="7" t="n"/>
+      <c r="R66" s="7" t="n"/>
     </row>
     <row r="67" ht="16.05" customHeight="1" s="10">
       <c r="A67" s="8" t="n"/>
@@ -8390,7 +8401,7 @@
       <c r="N67" s="8" t="n"/>
       <c r="O67" s="8" t="n"/>
       <c r="P67" s="8" t="n"/>
-      <c r="Q67" s="8" t="n"/>
+      <c r="R67" s="8" t="n"/>
     </row>
     <row r="68" ht="16.05" customHeight="1" s="10">
       <c r="A68" s="7" t="n"/>
@@ -8409,7 +8420,7 @@
       <c r="N68" s="7" t="n"/>
       <c r="O68" s="7" t="n"/>
       <c r="P68" s="7" t="n"/>
-      <c r="Q68" s="7" t="n"/>
+      <c r="R68" s="7" t="n"/>
     </row>
     <row r="69" ht="16.05" customHeight="1" s="10">
       <c r="A69" s="8" t="n"/>
@@ -8428,7 +8439,7 @@
       <c r="N69" s="8" t="n"/>
       <c r="O69" s="8" t="n"/>
       <c r="P69" s="8" t="n"/>
-      <c r="Q69" s="8" t="n"/>
+      <c r="R69" s="8" t="n"/>
     </row>
     <row r="70" ht="16.05" customHeight="1" s="10">
       <c r="A70" s="7" t="n"/>
@@ -8447,7 +8458,7 @@
       <c r="N70" s="7" t="n"/>
       <c r="O70" s="7" t="n"/>
       <c r="P70" s="7" t="n"/>
-      <c r="Q70" s="7" t="n"/>
+      <c r="R70" s="7" t="n"/>
     </row>
     <row r="71" ht="16.05" customHeight="1" s="10">
       <c r="A71" s="8" t="n"/>
@@ -8466,7 +8477,7 @@
       <c r="N71" s="8" t="n"/>
       <c r="O71" s="8" t="n"/>
       <c r="P71" s="8" t="n"/>
-      <c r="Q71" s="8" t="n"/>
+      <c r="R71" s="8" t="n"/>
     </row>
     <row r="72" ht="16.05" customHeight="1" s="10">
       <c r="A72" s="7" t="n"/>
@@ -8485,7 +8496,7 @@
       <c r="N72" s="7" t="n"/>
       <c r="O72" s="7" t="n"/>
       <c r="P72" s="7" t="n"/>
-      <c r="Q72" s="7" t="n"/>
+      <c r="R72" s="7" t="n"/>
     </row>
     <row r="73" ht="16.05" customHeight="1" s="10">
       <c r="A73" s="8" t="n"/>
@@ -8504,7 +8515,7 @@
       <c r="N73" s="8" t="n"/>
       <c r="O73" s="8" t="n"/>
       <c r="P73" s="8" t="n"/>
-      <c r="Q73" s="8" t="n"/>
+      <c r="R73" s="8" t="n"/>
     </row>
     <row r="74" ht="16.05" customHeight="1" s="10">
       <c r="A74" s="7" t="n"/>
@@ -8523,7 +8534,7 @@
       <c r="N74" s="7" t="n"/>
       <c r="O74" s="7" t="n"/>
       <c r="P74" s="7" t="n"/>
-      <c r="Q74" s="7" t="n"/>
+      <c r="R74" s="7" t="n"/>
     </row>
     <row r="75" ht="16.05" customHeight="1" s="10">
       <c r="A75" s="8" t="n"/>
@@ -8542,7 +8553,7 @@
       <c r="N75" s="8" t="n"/>
       <c r="O75" s="8" t="n"/>
       <c r="P75" s="8" t="n"/>
-      <c r="Q75" s="8" t="n"/>
+      <c r="R75" s="8" t="n"/>
     </row>
     <row r="76" ht="16.05" customHeight="1" s="10">
       <c r="A76" s="7" t="n"/>
@@ -8561,7 +8572,7 @@
       <c r="N76" s="7" t="n"/>
       <c r="O76" s="7" t="n"/>
       <c r="P76" s="7" t="n"/>
-      <c r="Q76" s="7" t="n"/>
+      <c r="R76" s="7" t="n"/>
     </row>
     <row r="77" ht="16.05" customHeight="1" s="10">
       <c r="A77" s="8" t="n"/>
@@ -8580,7 +8591,7 @@
       <c r="N77" s="8" t="n"/>
       <c r="O77" s="8" t="n"/>
       <c r="P77" s="8" t="n"/>
-      <c r="Q77" s="8" t="n"/>
+      <c r="R77" s="8" t="n"/>
     </row>
     <row r="78" ht="16.05" customHeight="1" s="10">
       <c r="A78" s="7" t="n"/>
@@ -8599,7 +8610,7 @@
       <c r="N78" s="7" t="n"/>
       <c r="O78" s="7" t="n"/>
       <c r="P78" s="7" t="n"/>
-      <c r="Q78" s="7" t="n"/>
+      <c r="R78" s="7" t="n"/>
     </row>
     <row r="79" ht="16.05" customHeight="1" s="10">
       <c r="A79" s="8" t="n"/>
@@ -8618,7 +8629,7 @@
       <c r="N79" s="8" t="n"/>
       <c r="O79" s="8" t="n"/>
       <c r="P79" s="8" t="n"/>
-      <c r="Q79" s="8" t="n"/>
+      <c r="R79" s="8" t="n"/>
     </row>
     <row r="80" ht="16.05" customHeight="1" s="10">
       <c r="A80" s="7" t="n"/>
@@ -8637,7 +8648,7 @@
       <c r="N80" s="7" t="n"/>
       <c r="O80" s="7" t="n"/>
       <c r="P80" s="7" t="n"/>
-      <c r="Q80" s="7" t="n"/>
+      <c r="R80" s="7" t="n"/>
     </row>
     <row r="81" ht="16.05" customHeight="1" s="10">
       <c r="A81" s="8" t="n"/>
@@ -8656,7 +8667,7 @@
       <c r="N81" s="8" t="n"/>
       <c r="O81" s="8" t="n"/>
       <c r="P81" s="8" t="n"/>
-      <c r="Q81" s="8" t="n"/>
+      <c r="R81" s="8" t="n"/>
     </row>
     <row r="82" ht="16.05" customHeight="1" s="10">
       <c r="A82" s="7" t="n"/>
@@ -8675,7 +8686,7 @@
       <c r="N82" s="7" t="n"/>
       <c r="O82" s="7" t="n"/>
       <c r="P82" s="7" t="n"/>
-      <c r="Q82" s="7" t="n"/>
+      <c r="R82" s="7" t="n"/>
     </row>
     <row r="83" ht="16.05" customHeight="1" s="10">
       <c r="A83" s="8" t="n"/>
@@ -8694,7 +8705,7 @@
       <c r="N83" s="8" t="n"/>
       <c r="O83" s="8" t="n"/>
       <c r="P83" s="8" t="n"/>
-      <c r="Q83" s="8" t="n"/>
+      <c r="R83" s="8" t="n"/>
     </row>
     <row r="84" ht="16.05" customHeight="1" s="10">
       <c r="A84" s="7" t="n"/>
@@ -8713,7 +8724,7 @@
       <c r="N84" s="7" t="n"/>
       <c r="O84" s="7" t="n"/>
       <c r="P84" s="7" t="n"/>
-      <c r="Q84" s="7" t="n"/>
+      <c r="R84" s="7" t="n"/>
     </row>
     <row r="85" ht="16.05" customHeight="1" s="10">
       <c r="A85" s="8" t="n"/>
@@ -8732,7 +8743,7 @@
       <c r="N85" s="8" t="n"/>
       <c r="O85" s="8" t="n"/>
       <c r="P85" s="8" t="n"/>
-      <c r="Q85" s="8" t="n"/>
+      <c r="R85" s="8" t="n"/>
     </row>
     <row r="86" ht="16.05" customHeight="1" s="10">
       <c r="A86" s="7" t="n"/>
@@ -8751,7 +8762,7 @@
       <c r="N86" s="7" t="n"/>
       <c r="O86" s="7" t="n"/>
       <c r="P86" s="7" t="n"/>
-      <c r="Q86" s="7" t="n"/>
+      <c r="R86" s="7" t="n"/>
     </row>
     <row r="87" ht="16.05" customHeight="1" s="10">
       <c r="A87" s="8" t="n"/>
@@ -8770,7 +8781,7 @@
       <c r="N87" s="8" t="n"/>
       <c r="O87" s="8" t="n"/>
       <c r="P87" s="8" t="n"/>
-      <c r="Q87" s="8" t="n"/>
+      <c r="R87" s="8" t="n"/>
     </row>
     <row r="88" ht="16.05" customHeight="1" s="10">
       <c r="A88" s="7" t="n"/>
@@ -8789,7 +8800,7 @@
       <c r="N88" s="7" t="n"/>
       <c r="O88" s="7" t="n"/>
       <c r="P88" s="7" t="n"/>
-      <c r="Q88" s="7" t="n"/>
+      <c r="R88" s="7" t="n"/>
     </row>
     <row r="89" ht="16.05" customHeight="1" s="10">
       <c r="A89" s="8" t="n"/>
@@ -8808,7 +8819,7 @@
       <c r="N89" s="8" t="n"/>
       <c r="O89" s="8" t="n"/>
       <c r="P89" s="8" t="n"/>
-      <c r="Q89" s="8" t="n"/>
+      <c r="R89" s="8" t="n"/>
     </row>
     <row r="90" ht="16.05" customHeight="1" s="10">
       <c r="A90" s="7" t="n"/>
@@ -8827,7 +8838,7 @@
       <c r="N90" s="7" t="n"/>
       <c r="O90" s="7" t="n"/>
       <c r="P90" s="7" t="n"/>
-      <c r="Q90" s="7" t="n"/>
+      <c r="R90" s="7" t="n"/>
     </row>
     <row r="91" ht="16.05" customHeight="1" s="10">
       <c r="A91" s="8" t="n"/>
@@ -8846,7 +8857,7 @@
       <c r="N91" s="8" t="n"/>
       <c r="O91" s="8" t="n"/>
       <c r="P91" s="8" t="n"/>
-      <c r="Q91" s="8" t="n"/>
+      <c r="R91" s="8" t="n"/>
     </row>
     <row r="92" ht="16.05" customHeight="1" s="10">
       <c r="A92" s="7" t="n"/>
@@ -8865,7 +8876,7 @@
       <c r="N92" s="7" t="n"/>
       <c r="O92" s="7" t="n"/>
       <c r="P92" s="7" t="n"/>
-      <c r="Q92" s="7" t="n"/>
+      <c r="R92" s="7" t="n"/>
     </row>
     <row r="93" ht="16.05" customHeight="1" s="10">
       <c r="A93" s="8" t="n"/>
@@ -8884,7 +8895,7 @@
       <c r="N93" s="8" t="n"/>
       <c r="O93" s="8" t="n"/>
       <c r="P93" s="8" t="n"/>
-      <c r="Q93" s="8" t="n"/>
+      <c r="R93" s="8" t="n"/>
     </row>
     <row r="94" ht="16.05" customHeight="1" s="10">
       <c r="A94" s="7" t="n"/>
@@ -8903,7 +8914,7 @@
       <c r="N94" s="7" t="n"/>
       <c r="O94" s="7" t="n"/>
       <c r="P94" s="7" t="n"/>
-      <c r="Q94" s="7" t="n"/>
+      <c r="R94" s="7" t="n"/>
     </row>
     <row r="95" ht="16.05" customHeight="1" s="10">
       <c r="A95" s="8" t="n"/>
@@ -8922,7 +8933,7 @@
       <c r="N95" s="8" t="n"/>
       <c r="O95" s="8" t="n"/>
       <c r="P95" s="8" t="n"/>
-      <c r="Q95" s="8" t="n"/>
+      <c r="R95" s="8" t="n"/>
     </row>
     <row r="96" ht="16.05" customHeight="1" s="10">
       <c r="A96" s="7" t="n"/>
@@ -8941,7 +8952,7 @@
       <c r="N96" s="7" t="n"/>
       <c r="O96" s="7" t="n"/>
       <c r="P96" s="7" t="n"/>
-      <c r="Q96" s="7" t="n"/>
+      <c r="R96" s="7" t="n"/>
     </row>
     <row r="97" ht="16.05" customHeight="1" s="10">
       <c r="A97" s="8" t="n"/>
@@ -8960,7 +8971,7 @@
       <c r="N97" s="8" t="n"/>
       <c r="O97" s="8" t="n"/>
       <c r="P97" s="8" t="n"/>
-      <c r="Q97" s="8" t="n"/>
+      <c r="R97" s="8" t="n"/>
     </row>
     <row r="98" ht="16.05" customHeight="1" s="10">
       <c r="A98" s="7" t="n"/>
@@ -8979,7 +8990,7 @@
       <c r="N98" s="7" t="n"/>
       <c r="O98" s="7" t="n"/>
       <c r="P98" s="7" t="n"/>
-      <c r="Q98" s="7" t="n"/>
+      <c r="R98" s="7" t="n"/>
     </row>
     <row r="99" ht="16.05" customHeight="1" s="10">
       <c r="A99" s="8" t="n"/>
@@ -8998,7 +9009,7 @@
       <c r="N99" s="8" t="n"/>
       <c r="O99" s="8" t="n"/>
       <c r="P99" s="8" t="n"/>
-      <c r="Q99" s="8" t="n"/>
+      <c r="R99" s="8" t="n"/>
     </row>
     <row r="100" ht="16.05" customHeight="1" s="10">
       <c r="A100" s="7" t="n"/>
@@ -9017,7 +9028,7 @@
       <c r="N100" s="7" t="n"/>
       <c r="O100" s="7" t="n"/>
       <c r="P100" s="7" t="n"/>
-      <c r="Q100" s="7" t="n"/>
+      <c r="R100" s="7" t="n"/>
     </row>
     <row r="101" ht="16.05" customHeight="1" s="10">
       <c r="A101" s="8" t="n"/>
@@ -9036,7 +9047,7 @@
       <c r="N101" s="8" t="n"/>
       <c r="O101" s="8" t="n"/>
       <c r="P101" s="8" t="n"/>
-      <c r="Q101" s="8" t="n"/>
+      <c r="R101" s="8" t="n"/>
     </row>
     <row r="102" ht="16.05" customHeight="1" s="10">
       <c r="A102" s="7" t="n"/>
@@ -9055,7 +9066,7 @@
       <c r="N102" s="7" t="n"/>
       <c r="O102" s="7" t="n"/>
       <c r="P102" s="7" t="n"/>
-      <c r="Q102" s="7" t="n"/>
+      <c r="R102" s="7" t="n"/>
     </row>
     <row r="103" ht="16.05" customHeight="1" s="10">
       <c r="A103" s="8" t="n"/>
@@ -9074,7 +9085,7 @@
       <c r="N103" s="8" t="n"/>
       <c r="O103" s="8" t="n"/>
       <c r="P103" s="8" t="n"/>
-      <c r="Q103" s="8" t="n"/>
+      <c r="R103" s="8" t="n"/>
     </row>
     <row r="104" ht="16.05" customHeight="1" s="10">
       <c r="A104" s="7" t="n"/>
@@ -9093,7 +9104,7 @@
       <c r="N104" s="7" t="n"/>
       <c r="O104" s="7" t="n"/>
       <c r="P104" s="7" t="n"/>
-      <c r="Q104" s="7" t="n"/>
+      <c r="R104" s="7" t="n"/>
     </row>
     <row r="105" ht="16.05" customHeight="1" s="10">
       <c r="A105" s="8" t="n"/>
@@ -9112,7 +9123,7 @@
       <c r="N105" s="8" t="n"/>
       <c r="O105" s="8" t="n"/>
       <c r="P105" s="8" t="n"/>
-      <c r="Q105" s="8" t="n"/>
+      <c r="R105" s="8" t="n"/>
     </row>
     <row r="106" ht="16.05" customHeight="1" s="10">
       <c r="A106" s="7" t="n"/>
@@ -9131,7 +9142,7 @@
       <c r="N106" s="7" t="n"/>
       <c r="O106" s="7" t="n"/>
       <c r="P106" s="7" t="n"/>
-      <c r="Q106" s="7" t="n"/>
+      <c r="R106" s="7" t="n"/>
     </row>
     <row r="107" ht="16.05" customHeight="1" s="10">
       <c r="A107" s="8" t="n"/>
@@ -9150,7 +9161,7 @@
       <c r="N107" s="8" t="n"/>
       <c r="O107" s="8" t="n"/>
       <c r="P107" s="8" t="n"/>
-      <c r="Q107" s="8" t="n"/>
+      <c r="R107" s="8" t="n"/>
     </row>
     <row r="108" ht="16.05" customHeight="1" s="10">
       <c r="A108" s="7" t="n"/>
@@ -9169,7 +9180,7 @@
       <c r="N108" s="7" t="n"/>
       <c r="O108" s="7" t="n"/>
       <c r="P108" s="7" t="n"/>
-      <c r="Q108" s="7" t="n"/>
+      <c r="R108" s="7" t="n"/>
     </row>
     <row r="109" ht="16.05" customHeight="1" s="10">
       <c r="A109" s="8" t="n"/>
@@ -9188,7 +9199,7 @@
       <c r="N109" s="8" t="n"/>
       <c r="O109" s="8" t="n"/>
       <c r="P109" s="8" t="n"/>
-      <c r="Q109" s="8" t="n"/>
+      <c r="R109" s="8" t="n"/>
     </row>
     <row r="110" ht="16.05" customHeight="1" s="10">
       <c r="A110" s="7" t="n"/>
@@ -9207,7 +9218,7 @@
       <c r="N110" s="7" t="n"/>
       <c r="O110" s="7" t="n"/>
       <c r="P110" s="7" t="n"/>
-      <c r="Q110" s="7" t="n"/>
+      <c r="R110" s="7" t="n"/>
     </row>
     <row r="111" ht="16.05" customHeight="1" s="10">
       <c r="A111" s="8" t="n"/>
@@ -9226,7 +9237,7 @@
       <c r="N111" s="8" t="n"/>
       <c r="O111" s="8" t="n"/>
       <c r="P111" s="8" t="n"/>
-      <c r="Q111" s="8" t="n"/>
+      <c r="R111" s="8" t="n"/>
     </row>
     <row r="112" ht="16.05" customHeight="1" s="10">
       <c r="A112" s="7" t="n"/>
@@ -9245,7 +9256,7 @@
       <c r="N112" s="7" t="n"/>
       <c r="O112" s="7" t="n"/>
       <c r="P112" s="7" t="n"/>
-      <c r="Q112" s="7" t="n"/>
+      <c r="R112" s="7" t="n"/>
     </row>
     <row r="113" ht="16.05" customHeight="1" s="10">
       <c r="A113" s="8" t="n"/>
@@ -9264,7 +9275,7 @@
       <c r="N113" s="8" t="n"/>
       <c r="O113" s="8" t="n"/>
       <c r="P113" s="8" t="n"/>
-      <c r="Q113" s="8" t="n"/>
+      <c r="R113" s="8" t="n"/>
     </row>
     <row r="114" ht="16.05" customHeight="1" s="10">
       <c r="A114" s="7" t="n"/>
@@ -9283,7 +9294,7 @@
       <c r="N114" s="7" t="n"/>
       <c r="O114" s="7" t="n"/>
       <c r="P114" s="7" t="n"/>
-      <c r="Q114" s="7" t="n"/>
+      <c r="R114" s="7" t="n"/>
     </row>
     <row r="115" ht="16.05" customHeight="1" s="10">
       <c r="A115" s="8" t="n"/>
@@ -9302,7 +9313,7 @@
       <c r="N115" s="8" t="n"/>
       <c r="O115" s="8" t="n"/>
       <c r="P115" s="8" t="n"/>
-      <c r="Q115" s="8" t="n"/>
+      <c r="R115" s="8" t="n"/>
     </row>
     <row r="116" ht="16.05" customHeight="1" s="10">
       <c r="A116" s="7" t="n"/>
@@ -9321,7 +9332,7 @@
       <c r="N116" s="7" t="n"/>
       <c r="O116" s="7" t="n"/>
       <c r="P116" s="7" t="n"/>
-      <c r="Q116" s="7" t="n"/>
+      <c r="R116" s="7" t="n"/>
     </row>
     <row r="117" ht="16.05" customHeight="1" s="10">
       <c r="A117" s="8" t="n"/>
@@ -9340,7 +9351,7 @@
       <c r="N117" s="8" t="n"/>
       <c r="O117" s="8" t="n"/>
       <c r="P117" s="8" t="n"/>
-      <c r="Q117" s="8" t="n"/>
+      <c r="R117" s="8" t="n"/>
     </row>
     <row r="118" ht="16.05" customHeight="1" s="10">
       <c r="A118" s="7" t="n"/>
@@ -9359,7 +9370,7 @@
       <c r="N118" s="7" t="n"/>
       <c r="O118" s="7" t="n"/>
       <c r="P118" s="7" t="n"/>
-      <c r="Q118" s="7" t="n"/>
+      <c r="R118" s="7" t="n"/>
     </row>
     <row r="119" ht="16.05" customHeight="1" s="10">
       <c r="A119" s="8" t="n"/>
@@ -9378,7 +9389,7 @@
       <c r="N119" s="8" t="n"/>
       <c r="O119" s="8" t="n"/>
       <c r="P119" s="8" t="n"/>
-      <c r="Q119" s="8" t="n"/>
+      <c r="R119" s="8" t="n"/>
     </row>
     <row r="120" ht="16.05" customHeight="1" s="10">
       <c r="A120" s="7" t="n"/>
@@ -9397,7 +9408,7 @@
       <c r="N120" s="7" t="n"/>
       <c r="O120" s="7" t="n"/>
       <c r="P120" s="7" t="n"/>
-      <c r="Q120" s="7" t="n"/>
+      <c r="R120" s="7" t="n"/>
     </row>
     <row r="121" ht="16.05" customHeight="1" s="10">
       <c r="A121" s="8" t="n"/>
@@ -9416,7 +9427,7 @@
       <c r="N121" s="8" t="n"/>
       <c r="O121" s="8" t="n"/>
       <c r="P121" s="8" t="n"/>
-      <c r="Q121" s="8" t="n"/>
+      <c r="R121" s="8" t="n"/>
     </row>
     <row r="122" ht="16.05" customHeight="1" s="10">
       <c r="A122" s="7" t="n"/>
@@ -9435,7 +9446,7 @@
       <c r="N122" s="7" t="n"/>
       <c r="O122" s="7" t="n"/>
       <c r="P122" s="7" t="n"/>
-      <c r="Q122" s="7" t="n"/>
+      <c r="R122" s="7" t="n"/>
     </row>
     <row r="123" ht="16.05" customHeight="1" s="10">
       <c r="A123" s="8" t="n"/>
@@ -9454,7 +9465,7 @@
       <c r="N123" s="8" t="n"/>
       <c r="O123" s="8" t="n"/>
       <c r="P123" s="8" t="n"/>
-      <c r="Q123" s="8" t="n"/>
+      <c r="R123" s="8" t="n"/>
     </row>
     <row r="124" ht="16.05" customHeight="1" s="10">
       <c r="A124" s="7" t="n"/>
@@ -9473,7 +9484,7 @@
       <c r="N124" s="7" t="n"/>
       <c r="O124" s="7" t="n"/>
       <c r="P124" s="7" t="n"/>
-      <c r="Q124" s="7" t="n"/>
+      <c r="R124" s="7" t="n"/>
     </row>
     <row r="125" ht="16.05" customHeight="1" s="10">
       <c r="A125" s="8" t="n"/>
@@ -9492,7 +9503,7 @@
       <c r="N125" s="8" t="n"/>
       <c r="O125" s="8" t="n"/>
       <c r="P125" s="8" t="n"/>
-      <c r="Q125" s="8" t="n"/>
+      <c r="R125" s="8" t="n"/>
     </row>
     <row r="126" ht="16.05" customHeight="1" s="10">
       <c r="A126" s="7" t="n"/>
@@ -9511,7 +9522,7 @@
       <c r="N126" s="7" t="n"/>
       <c r="O126" s="7" t="n"/>
       <c r="P126" s="7" t="n"/>
-      <c r="Q126" s="7" t="n"/>
+      <c r="R126" s="7" t="n"/>
     </row>
     <row r="127" ht="16.05" customHeight="1" s="10">
       <c r="A127" s="8" t="n"/>
@@ -9530,7 +9541,7 @@
       <c r="N127" s="8" t="n"/>
       <c r="O127" s="8" t="n"/>
       <c r="P127" s="8" t="n"/>
-      <c r="Q127" s="8" t="n"/>
+      <c r="R127" s="8" t="n"/>
     </row>
     <row r="128" ht="16.05" customHeight="1" s="10">
       <c r="A128" s="7" t="n"/>
@@ -9549,7 +9560,7 @@
       <c r="N128" s="7" t="n"/>
       <c r="O128" s="7" t="n"/>
       <c r="P128" s="7" t="n"/>
-      <c r="Q128" s="7" t="n"/>
+      <c r="R128" s="7" t="n"/>
     </row>
     <row r="129" ht="16.05" customHeight="1" s="10">
       <c r="A129" s="8" t="n"/>
@@ -9568,7 +9579,7 @@
       <c r="N129" s="8" t="n"/>
       <c r="O129" s="8" t="n"/>
       <c r="P129" s="8" t="n"/>
-      <c r="Q129" s="8" t="n"/>
+      <c r="R129" s="8" t="n"/>
     </row>
     <row r="130" ht="16.05" customHeight="1" s="10">
       <c r="A130" s="7" t="n"/>
@@ -9587,7 +9598,7 @@
       <c r="N130" s="7" t="n"/>
       <c r="O130" s="7" t="n"/>
       <c r="P130" s="7" t="n"/>
-      <c r="Q130" s="7" t="n"/>
+      <c r="R130" s="7" t="n"/>
     </row>
     <row r="131" ht="16.05" customHeight="1" s="10">
       <c r="A131" s="8" t="n"/>
@@ -9606,7 +9617,7 @@
       <c r="N131" s="8" t="n"/>
       <c r="O131" s="8" t="n"/>
       <c r="P131" s="8" t="n"/>
-      <c r="Q131" s="8" t="n"/>
+      <c r="R131" s="8" t="n"/>
     </row>
     <row r="132" ht="16.05" customHeight="1" s="10">
       <c r="A132" s="7" t="n"/>
@@ -9625,7 +9636,7 @@
       <c r="N132" s="7" t="n"/>
       <c r="O132" s="7" t="n"/>
       <c r="P132" s="7" t="n"/>
-      <c r="Q132" s="7" t="n"/>
+      <c r="R132" s="7" t="n"/>
     </row>
     <row r="133" ht="16.05" customHeight="1" s="10">
       <c r="A133" s="8" t="n"/>
@@ -9644,7 +9655,7 @@
       <c r="N133" s="8" t="n"/>
       <c r="O133" s="8" t="n"/>
       <c r="P133" s="8" t="n"/>
-      <c r="Q133" s="8" t="n"/>
+      <c r="R133" s="8" t="n"/>
     </row>
     <row r="134" ht="16.05" customHeight="1" s="10">
       <c r="A134" s="7" t="n"/>
@@ -9663,7 +9674,7 @@
       <c r="N134" s="7" t="n"/>
       <c r="O134" s="7" t="n"/>
       <c r="P134" s="7" t="n"/>
-      <c r="Q134" s="7" t="n"/>
+      <c r="R134" s="7" t="n"/>
     </row>
     <row r="135" ht="16.05" customHeight="1" s="10">
       <c r="A135" s="8" t="n"/>
@@ -9682,7 +9693,7 @@
       <c r="N135" s="8" t="n"/>
       <c r="O135" s="8" t="n"/>
       <c r="P135" s="8" t="n"/>
-      <c r="Q135" s="8" t="n"/>
+      <c r="R135" s="8" t="n"/>
     </row>
     <row r="136" ht="16.05" customHeight="1" s="10">
       <c r="A136" s="7" t="n"/>
@@ -9701,7 +9712,7 @@
       <c r="N136" s="7" t="n"/>
       <c r="O136" s="7" t="n"/>
       <c r="P136" s="7" t="n"/>
-      <c r="Q136" s="7" t="n"/>
+      <c r="R136" s="7" t="n"/>
     </row>
     <row r="137" ht="16.05" customHeight="1" s="10">
       <c r="A137" s="8" t="n"/>
@@ -9720,7 +9731,7 @@
       <c r="N137" s="8" t="n"/>
       <c r="O137" s="8" t="n"/>
       <c r="P137" s="8" t="n"/>
-      <c r="Q137" s="8" t="n"/>
+      <c r="R137" s="8" t="n"/>
     </row>
     <row r="138" ht="16.05" customHeight="1" s="10">
       <c r="A138" s="7" t="n"/>
@@ -9739,7 +9750,7 @@
       <c r="N138" s="7" t="n"/>
       <c r="O138" s="7" t="n"/>
       <c r="P138" s="7" t="n"/>
-      <c r="Q138" s="7" t="n"/>
+      <c r="R138" s="7" t="n"/>
     </row>
     <row r="139" ht="16.05" customHeight="1" s="10">
       <c r="A139" s="8" t="n"/>
@@ -9758,7 +9769,7 @@
       <c r="N139" s="8" t="n"/>
       <c r="O139" s="8" t="n"/>
       <c r="P139" s="8" t="n"/>
-      <c r="Q139" s="8" t="n"/>
+      <c r="R139" s="8" t="n"/>
     </row>
     <row r="140" ht="16.05" customHeight="1" s="10">
       <c r="A140" s="7" t="n"/>
@@ -9777,7 +9788,7 @@
       <c r="N140" s="7" t="n"/>
       <c r="O140" s="7" t="n"/>
       <c r="P140" s="7" t="n"/>
-      <c r="Q140" s="7" t="n"/>
+      <c r="R140" s="7" t="n"/>
     </row>
     <row r="141" ht="16.05" customHeight="1" s="10">
       <c r="A141" s="8" t="n"/>
@@ -9796,7 +9807,7 @@
       <c r="N141" s="8" t="n"/>
       <c r="O141" s="8" t="n"/>
       <c r="P141" s="8" t="n"/>
-      <c r="Q141" s="8" t="n"/>
+      <c r="R141" s="8" t="n"/>
     </row>
     <row r="142" ht="16.05" customHeight="1" s="10">
       <c r="A142" s="7" t="n"/>
@@ -9815,7 +9826,7 @@
       <c r="N142" s="7" t="n"/>
       <c r="O142" s="7" t="n"/>
       <c r="P142" s="7" t="n"/>
-      <c r="Q142" s="7" t="n"/>
+      <c r="R142" s="7" t="n"/>
     </row>
     <row r="143" ht="16.05" customHeight="1" s="10">
       <c r="A143" s="8" t="n"/>
@@ -9834,7 +9845,7 @@
       <c r="N143" s="8" t="n"/>
       <c r="O143" s="8" t="n"/>
       <c r="P143" s="8" t="n"/>
-      <c r="Q143" s="8" t="n"/>
+      <c r="R143" s="8" t="n"/>
     </row>
     <row r="144" ht="16.05" customHeight="1" s="10">
       <c r="A144" s="7" t="n"/>
@@ -9853,7 +9864,7 @@
       <c r="N144" s="7" t="n"/>
       <c r="O144" s="7" t="n"/>
       <c r="P144" s="7" t="n"/>
-      <c r="Q144" s="7" t="n"/>
+      <c r="R144" s="7" t="n"/>
     </row>
     <row r="145" ht="16.05" customHeight="1" s="10">
       <c r="A145" s="8" t="n"/>
@@ -9872,7 +9883,7 @@
       <c r="N145" s="8" t="n"/>
       <c r="O145" s="8" t="n"/>
       <c r="P145" s="8" t="n"/>
-      <c r="Q145" s="8" t="n"/>
+      <c r="R145" s="8" t="n"/>
     </row>
     <row r="146" ht="16.05" customHeight="1" s="10">
       <c r="A146" s="7" t="n"/>
@@ -9891,7 +9902,7 @@
       <c r="N146" s="7" t="n"/>
       <c r="O146" s="7" t="n"/>
       <c r="P146" s="7" t="n"/>
-      <c r="Q146" s="7" t="n"/>
+      <c r="R146" s="7" t="n"/>
     </row>
     <row r="147" ht="16.05" customHeight="1" s="10">
       <c r="A147" s="8" t="n"/>
@@ -9910,7 +9921,7 @@
       <c r="N147" s="8" t="n"/>
       <c r="O147" s="8" t="n"/>
       <c r="P147" s="8" t="n"/>
-      <c r="Q147" s="8" t="n"/>
+      <c r="R147" s="8" t="n"/>
     </row>
     <row r="148" ht="16.05" customHeight="1" s="10">
       <c r="A148" s="7" t="n"/>
@@ -9929,7 +9940,7 @@
       <c r="N148" s="7" t="n"/>
       <c r="O148" s="7" t="n"/>
       <c r="P148" s="7" t="n"/>
-      <c r="Q148" s="7" t="n"/>
+      <c r="R148" s="7" t="n"/>
     </row>
     <row r="149" ht="16.05" customHeight="1" s="10">
       <c r="A149" s="8" t="n"/>
@@ -9948,7 +9959,7 @@
       <c r="N149" s="8" t="n"/>
       <c r="O149" s="8" t="n"/>
       <c r="P149" s="8" t="n"/>
-      <c r="Q149" s="8" t="n"/>
+      <c r="R149" s="8" t="n"/>
     </row>
     <row r="150" ht="16.05" customHeight="1" s="10">
       <c r="A150" s="7" t="n"/>
@@ -9967,7 +9978,7 @@
       <c r="N150" s="7" t="n"/>
       <c r="O150" s="7" t="n"/>
       <c r="P150" s="7" t="n"/>
-      <c r="Q150" s="7" t="n"/>
+      <c r="R150" s="7" t="n"/>
     </row>
     <row r="151" ht="16.05" customHeight="1" s="10">
       <c r="A151" s="8" t="n"/>
@@ -9986,7 +9997,7 @@
       <c r="N151" s="8" t="n"/>
       <c r="O151" s="8" t="n"/>
       <c r="P151" s="8" t="n"/>
-      <c r="Q151" s="8" t="n"/>
+      <c r="R151" s="8" t="n"/>
     </row>
     <row r="152" ht="16.05" customHeight="1" s="10">
       <c r="A152" s="7" t="n"/>
@@ -10005,7 +10016,7 @@
       <c r="N152" s="7" t="n"/>
       <c r="O152" s="7" t="n"/>
       <c r="P152" s="7" t="n"/>
-      <c r="Q152" s="7" t="n"/>
+      <c r="R152" s="7" t="n"/>
     </row>
     <row r="153" ht="16.05" customHeight="1" s="10">
       <c r="A153" s="8" t="n"/>
@@ -10024,7 +10035,7 @@
       <c r="N153" s="8" t="n"/>
       <c r="O153" s="8" t="n"/>
       <c r="P153" s="8" t="n"/>
-      <c r="Q153" s="8" t="n"/>
+      <c r="R153" s="8" t="n"/>
     </row>
     <row r="154" ht="16.05" customHeight="1" s="10">
       <c r="A154" s="7" t="n"/>
@@ -10043,7 +10054,7 @@
       <c r="N154" s="7" t="n"/>
       <c r="O154" s="7" t="n"/>
       <c r="P154" s="7" t="n"/>
-      <c r="Q154" s="7" t="n"/>
+      <c r="R154" s="7" t="n"/>
     </row>
     <row r="155" ht="16.05" customHeight="1" s="10">
       <c r="A155" s="8" t="n"/>
@@ -10062,7 +10073,7 @@
       <c r="N155" s="8" t="n"/>
       <c r="O155" s="8" t="n"/>
       <c r="P155" s="8" t="n"/>
-      <c r="Q155" s="8" t="n"/>
+      <c r="R155" s="8" t="n"/>
     </row>
     <row r="156" ht="16.05" customHeight="1" s="10">
       <c r="A156" s="7" t="n"/>
@@ -10081,7 +10092,7 @@
       <c r="N156" s="7" t="n"/>
       <c r="O156" s="7" t="n"/>
       <c r="P156" s="7" t="n"/>
-      <c r="Q156" s="7" t="n"/>
+      <c r="R156" s="7" t="n"/>
     </row>
     <row r="157" ht="16.05" customHeight="1" s="10">
       <c r="A157" s="8" t="n"/>
@@ -10100,7 +10111,7 @@
       <c r="N157" s="8" t="n"/>
       <c r="O157" s="8" t="n"/>
       <c r="P157" s="8" t="n"/>
-      <c r="Q157" s="8" t="n"/>
+      <c r="R157" s="8" t="n"/>
     </row>
     <row r="158" ht="16.05" customHeight="1" s="10">
       <c r="A158" s="7" t="n"/>
@@ -10119,7 +10130,7 @@
       <c r="N158" s="7" t="n"/>
       <c r="O158" s="7" t="n"/>
       <c r="P158" s="7" t="n"/>
-      <c r="Q158" s="7" t="n"/>
+      <c r="R158" s="7" t="n"/>
     </row>
     <row r="159" ht="16.05" customHeight="1" s="10">
       <c r="A159" s="8" t="n"/>
@@ -10138,7 +10149,7 @@
       <c r="N159" s="8" t="n"/>
       <c r="O159" s="8" t="n"/>
       <c r="P159" s="8" t="n"/>
-      <c r="Q159" s="8" t="n"/>
+      <c r="R159" s="8" t="n"/>
     </row>
     <row r="160" ht="16.05" customHeight="1" s="10">
       <c r="A160" s="7" t="n"/>
@@ -10157,7 +10168,7 @@
       <c r="N160" s="7" t="n"/>
       <c r="O160" s="7" t="n"/>
       <c r="P160" s="7" t="n"/>
-      <c r="Q160" s="7" t="n"/>
+      <c r="R160" s="7" t="n"/>
     </row>
     <row r="161" ht="16.05" customHeight="1" s="10">
       <c r="A161" s="8" t="n"/>
@@ -10176,7 +10187,7 @@
       <c r="N161" s="8" t="n"/>
       <c r="O161" s="8" t="n"/>
       <c r="P161" s="8" t="n"/>
-      <c r="Q161" s="8" t="n"/>
+      <c r="R161" s="8" t="n"/>
     </row>
     <row r="162" ht="16.05" customHeight="1" s="10">
       <c r="A162" s="7" t="n"/>
@@ -10195,7 +10206,7 @@
       <c r="N162" s="7" t="n"/>
       <c r="O162" s="7" t="n"/>
       <c r="P162" s="7" t="n"/>
-      <c r="Q162" s="7" t="n"/>
+      <c r="R162" s="7" t="n"/>
     </row>
     <row r="163" ht="16.05" customHeight="1" s="10">
       <c r="A163" s="8" t="n"/>
@@ -10214,7 +10225,7 @@
       <c r="N163" s="8" t="n"/>
       <c r="O163" s="8" t="n"/>
       <c r="P163" s="8" t="n"/>
-      <c r="Q163" s="8" t="n"/>
+      <c r="R163" s="8" t="n"/>
     </row>
     <row r="164" ht="16.05" customHeight="1" s="10">
       <c r="A164" s="7" t="n"/>
@@ -10233,7 +10244,7 @@
       <c r="N164" s="7" t="n"/>
       <c r="O164" s="7" t="n"/>
       <c r="P164" s="7" t="n"/>
-      <c r="Q164" s="7" t="n"/>
+      <c r="R164" s="7" t="n"/>
     </row>
     <row r="165" ht="16.05" customHeight="1" s="10">
       <c r="A165" s="8" t="n"/>
@@ -10252,7 +10263,7 @@
       <c r="N165" s="8" t="n"/>
       <c r="O165" s="8" t="n"/>
       <c r="P165" s="8" t="n"/>
-      <c r="Q165" s="8" t="n"/>
+      <c r="R165" s="8" t="n"/>
     </row>
     <row r="166" ht="16.05" customHeight="1" s="10">
       <c r="A166" s="7" t="n"/>
@@ -10271,7 +10282,7 @@
       <c r="N166" s="7" t="n"/>
       <c r="O166" s="7" t="n"/>
       <c r="P166" s="7" t="n"/>
-      <c r="Q166" s="7" t="n"/>
+      <c r="R166" s="7" t="n"/>
     </row>
     <row r="167" ht="16.05" customHeight="1" s="10">
       <c r="A167" s="8" t="n"/>
@@ -10290,7 +10301,7 @@
       <c r="N167" s="8" t="n"/>
       <c r="O167" s="8" t="n"/>
       <c r="P167" s="8" t="n"/>
-      <c r="Q167" s="8" t="n"/>
+      <c r="R167" s="8" t="n"/>
     </row>
     <row r="168" ht="16.05" customHeight="1" s="10">
       <c r="A168" s="7" t="n"/>
@@ -10309,7 +10320,7 @@
       <c r="N168" s="7" t="n"/>
       <c r="O168" s="7" t="n"/>
       <c r="P168" s="7" t="n"/>
-      <c r="Q168" s="7" t="n"/>
+      <c r="R168" s="7" t="n"/>
     </row>
     <row r="169" ht="16.05" customHeight="1" s="10">
       <c r="A169" s="8" t="n"/>
@@ -10328,7 +10339,7 @@
       <c r="N169" s="8" t="n"/>
       <c r="O169" s="8" t="n"/>
       <c r="P169" s="8" t="n"/>
-      <c r="Q169" s="8" t="n"/>
+      <c r="R169" s="8" t="n"/>
     </row>
     <row r="170" ht="16.05" customHeight="1" s="10">
       <c r="A170" s="7" t="n"/>
@@ -10347,7 +10358,7 @@
       <c r="N170" s="7" t="n"/>
       <c r="O170" s="7" t="n"/>
       <c r="P170" s="7" t="n"/>
-      <c r="Q170" s="7" t="n"/>
+      <c r="R170" s="7" t="n"/>
     </row>
     <row r="171" ht="16.05" customHeight="1" s="10">
       <c r="A171" s="8" t="n"/>
@@ -10366,7 +10377,7 @@
       <c r="N171" s="8" t="n"/>
       <c r="O171" s="8" t="n"/>
       <c r="P171" s="8" t="n"/>
-      <c r="Q171" s="8" t="n"/>
+      <c r="R171" s="8" t="n"/>
     </row>
     <row r="172" ht="16.05" customHeight="1" s="10">
       <c r="A172" s="7" t="n"/>
@@ -10385,7 +10396,7 @@
       <c r="N172" s="7" t="n"/>
       <c r="O172" s="7" t="n"/>
       <c r="P172" s="7" t="n"/>
-      <c r="Q172" s="7" t="n"/>
+      <c r="R172" s="7" t="n"/>
     </row>
     <row r="173" ht="16.05" customHeight="1" s="10">
       <c r="A173" s="8" t="n"/>
@@ -10404,7 +10415,7 @@
       <c r="N173" s="8" t="n"/>
       <c r="O173" s="8" t="n"/>
       <c r="P173" s="8" t="n"/>
-      <c r="Q173" s="8" t="n"/>
+      <c r="R173" s="8" t="n"/>
     </row>
     <row r="174" ht="16.05" customHeight="1" s="10">
       <c r="A174" s="7" t="n"/>
@@ -10423,7 +10434,7 @@
       <c r="N174" s="7" t="n"/>
       <c r="O174" s="7" t="n"/>
       <c r="P174" s="7" t="n"/>
-      <c r="Q174" s="7" t="n"/>
+      <c r="R174" s="7" t="n"/>
     </row>
     <row r="175" ht="16.05" customHeight="1" s="10">
       <c r="A175" s="8" t="n"/>
@@ -10442,7 +10453,7 @@
       <c r="N175" s="8" t="n"/>
       <c r="O175" s="8" t="n"/>
       <c r="P175" s="8" t="n"/>
-      <c r="Q175" s="8" t="n"/>
+      <c r="R175" s="8" t="n"/>
     </row>
     <row r="176" ht="16.05" customHeight="1" s="10">
       <c r="A176" s="7" t="n"/>
@@ -10461,7 +10472,7 @@
       <c r="N176" s="7" t="n"/>
       <c r="O176" s="7" t="n"/>
       <c r="P176" s="7" t="n"/>
-      <c r="Q176" s="7" t="n"/>
+      <c r="R176" s="7" t="n"/>
     </row>
     <row r="177" ht="16.05" customHeight="1" s="10">
       <c r="A177" s="8" t="n"/>
@@ -10480,7 +10491,7 @@
       <c r="N177" s="8" t="n"/>
       <c r="O177" s="8" t="n"/>
       <c r="P177" s="8" t="n"/>
-      <c r="Q177" s="8" t="n"/>
+      <c r="R177" s="8" t="n"/>
     </row>
     <row r="178" ht="16.05" customHeight="1" s="10">
       <c r="A178" s="7" t="n"/>
@@ -10499,7 +10510,7 @@
       <c r="N178" s="7" t="n"/>
       <c r="O178" s="7" t="n"/>
       <c r="P178" s="7" t="n"/>
-      <c r="Q178" s="7" t="n"/>
+      <c r="R178" s="7" t="n"/>
     </row>
     <row r="179" ht="16.05" customHeight="1" s="10">
       <c r="A179" s="8" t="n"/>
@@ -10518,7 +10529,7 @@
       <c r="N179" s="8" t="n"/>
       <c r="O179" s="8" t="n"/>
       <c r="P179" s="8" t="n"/>
-      <c r="Q179" s="8" t="n"/>
+      <c r="R179" s="8" t="n"/>
     </row>
     <row r="180" ht="16.05" customHeight="1" s="10">
       <c r="A180" s="7" t="n"/>
@@ -10537,7 +10548,7 @@
       <c r="N180" s="7" t="n"/>
       <c r="O180" s="7" t="n"/>
       <c r="P180" s="7" t="n"/>
-      <c r="Q180" s="7" t="n"/>
+      <c r="R180" s="7" t="n"/>
     </row>
     <row r="181" ht="16.05" customHeight="1" s="10">
       <c r="A181" s="8" t="n"/>
@@ -10556,7 +10567,7 @@
       <c r="N181" s="8" t="n"/>
       <c r="O181" s="8" t="n"/>
       <c r="P181" s="8" t="n"/>
-      <c r="Q181" s="8" t="n"/>
+      <c r="R181" s="8" t="n"/>
     </row>
     <row r="182" ht="16.05" customHeight="1" s="10">
       <c r="A182" s="7" t="n"/>
@@ -10575,7 +10586,7 @@
       <c r="N182" s="7" t="n"/>
       <c r="O182" s="7" t="n"/>
       <c r="P182" s="7" t="n"/>
-      <c r="Q182" s="7" t="n"/>
+      <c r="R182" s="7" t="n"/>
     </row>
     <row r="183" ht="16.05" customHeight="1" s="10">
       <c r="A183" s="8" t="n"/>
@@ -10594,7 +10605,7 @@
       <c r="N183" s="8" t="n"/>
       <c r="O183" s="8" t="n"/>
       <c r="P183" s="8" t="n"/>
-      <c r="Q183" s="8" t="n"/>
+      <c r="R183" s="8" t="n"/>
     </row>
     <row r="184" ht="16.05" customHeight="1" s="10">
       <c r="A184" s="7" t="n"/>
@@ -10613,7 +10624,7 @@
       <c r="N184" s="7" t="n"/>
       <c r="O184" s="7" t="n"/>
       <c r="P184" s="7" t="n"/>
-      <c r="Q184" s="7" t="n"/>
+      <c r="R184" s="7" t="n"/>
     </row>
     <row r="185" ht="16.05" customHeight="1" s="10">
       <c r="A185" s="8" t="n"/>
@@ -10632,7 +10643,7 @@
       <c r="N185" s="8" t="n"/>
       <c r="O185" s="8" t="n"/>
       <c r="P185" s="8" t="n"/>
-      <c r="Q185" s="8" t="n"/>
+      <c r="R185" s="8" t="n"/>
     </row>
     <row r="186" ht="16.05" customHeight="1" s="10">
       <c r="A186" s="7" t="n"/>
@@ -10651,7 +10662,7 @@
       <c r="N186" s="7" t="n"/>
       <c r="O186" s="7" t="n"/>
       <c r="P186" s="7" t="n"/>
-      <c r="Q186" s="7" t="n"/>
+      <c r="R186" s="7" t="n"/>
     </row>
     <row r="187" ht="16.05" customHeight="1" s="10">
       <c r="A187" s="8" t="n"/>
@@ -10670,7 +10681,7 @@
       <c r="N187" s="8" t="n"/>
       <c r="O187" s="8" t="n"/>
       <c r="P187" s="8" t="n"/>
-      <c r="Q187" s="8" t="n"/>
+      <c r="R187" s="8" t="n"/>
     </row>
     <row r="188" ht="16.05" customHeight="1" s="10">
       <c r="A188" s="7" t="n"/>
@@ -10689,7 +10700,7 @@
       <c r="N188" s="7" t="n"/>
       <c r="O188" s="7" t="n"/>
       <c r="P188" s="7" t="n"/>
-      <c r="Q188" s="7" t="n"/>
+      <c r="R188" s="7" t="n"/>
     </row>
     <row r="189" ht="16.05" customHeight="1" s="10">
       <c r="A189" s="8" t="n"/>
@@ -10708,7 +10719,7 @@
       <c r="N189" s="8" t="n"/>
       <c r="O189" s="8" t="n"/>
       <c r="P189" s="8" t="n"/>
-      <c r="Q189" s="8" t="n"/>
+      <c r="R189" s="8" t="n"/>
     </row>
     <row r="190" ht="16.05" customHeight="1" s="10">
       <c r="A190" s="7" t="n"/>
@@ -10727,7 +10738,7 @@
       <c r="N190" s="7" t="n"/>
       <c r="O190" s="7" t="n"/>
       <c r="P190" s="7" t="n"/>
-      <c r="Q190" s="7" t="n"/>
+      <c r="R190" s="7" t="n"/>
     </row>
     <row r="191" ht="16.05" customHeight="1" s="10">
       <c r="A191" s="8" t="n"/>
@@ -10746,7 +10757,7 @@
       <c r="N191" s="8" t="n"/>
       <c r="O191" s="8" t="n"/>
       <c r="P191" s="8" t="n"/>
-      <c r="Q191" s="8" t="n"/>
+      <c r="R191" s="8" t="n"/>
     </row>
     <row r="192" ht="16.05" customHeight="1" s="10">
       <c r="A192" s="7" t="n"/>
@@ -10765,7 +10776,7 @@
       <c r="N192" s="7" t="n"/>
       <c r="O192" s="7" t="n"/>
       <c r="P192" s="7" t="n"/>
-      <c r="Q192" s="7" t="n"/>
+      <c r="R192" s="7" t="n"/>
     </row>
     <row r="193" ht="16.05" customHeight="1" s="10">
       <c r="A193" s="8" t="n"/>
@@ -10784,7 +10795,7 @@
       <c r="N193" s="8" t="n"/>
       <c r="O193" s="8" t="n"/>
       <c r="P193" s="8" t="n"/>
-      <c r="Q193" s="8" t="n"/>
+      <c r="R193" s="8" t="n"/>
     </row>
     <row r="194" ht="16.05" customHeight="1" s="10">
       <c r="A194" s="7" t="n"/>
@@ -10803,7 +10814,7 @@
       <c r="N194" s="7" t="n"/>
       <c r="O194" s="7" t="n"/>
       <c r="P194" s="7" t="n"/>
-      <c r="Q194" s="7" t="n"/>
+      <c r="R194" s="7" t="n"/>
     </row>
     <row r="195" ht="16.05" customHeight="1" s="10">
       <c r="A195" s="8" t="n"/>
@@ -10822,7 +10833,7 @@
       <c r="N195" s="8" t="n"/>
       <c r="O195" s="8" t="n"/>
       <c r="P195" s="8" t="n"/>
-      <c r="Q195" s="8" t="n"/>
+      <c r="R195" s="8" t="n"/>
     </row>
     <row r="196" ht="16.05" customHeight="1" s="10">
       <c r="A196" s="7" t="n"/>
@@ -10841,7 +10852,7 @@
       <c r="N196" s="7" t="n"/>
       <c r="O196" s="7" t="n"/>
       <c r="P196" s="7" t="n"/>
-      <c r="Q196" s="7" t="n"/>
+      <c r="R196" s="7" t="n"/>
     </row>
     <row r="197" ht="16.05" customHeight="1" s="10">
       <c r="A197" s="8" t="n"/>
@@ -10860,7 +10871,7 @@
       <c r="N197" s="8" t="n"/>
       <c r="O197" s="8" t="n"/>
       <c r="P197" s="8" t="n"/>
-      <c r="Q197" s="8" t="n"/>
+      <c r="R197" s="8" t="n"/>
     </row>
     <row r="198" ht="16.05" customHeight="1" s="10">
       <c r="A198" s="7" t="n"/>
@@ -10879,7 +10890,7 @@
       <c r="N198" s="7" t="n"/>
       <c r="O198" s="7" t="n"/>
       <c r="P198" s="7" t="n"/>
-      <c r="Q198" s="7" t="n"/>
+      <c r="R198" s="7" t="n"/>
     </row>
     <row r="199" ht="16.05" customHeight="1" s="10">
       <c r="A199" s="8" t="n"/>
@@ -10898,7 +10909,7 @@
       <c r="N199" s="8" t="n"/>
       <c r="O199" s="8" t="n"/>
       <c r="P199" s="8" t="n"/>
-      <c r="Q199" s="8" t="n"/>
+      <c r="R199" s="8" t="n"/>
     </row>
     <row r="200" ht="16.05" customHeight="1" s="10">
       <c r="A200" s="7" t="n"/>
@@ -10917,7 +10928,7 @@
       <c r="N200" s="7" t="n"/>
       <c r="O200" s="7" t="n"/>
       <c r="P200" s="7" t="n"/>
-      <c r="Q200" s="7" t="n"/>
+      <c r="R200" s="7" t="n"/>
     </row>
     <row r="201" ht="16.05" customHeight="1" s="10">
       <c r="A201" s="8" t="n"/>
@@ -10936,7 +10947,7 @@
       <c r="N201" s="8" t="n"/>
       <c r="O201" s="8" t="n"/>
       <c r="P201" s="8" t="n"/>
-      <c r="Q201" s="8" t="n"/>
+      <c r="R201" s="8" t="n"/>
     </row>
     <row r="202" ht="16.05" customHeight="1" s="10">
       <c r="A202" s="7" t="n"/>
@@ -10955,7 +10966,7 @@
       <c r="N202" s="7" t="n"/>
       <c r="O202" s="7" t="n"/>
       <c r="P202" s="7" t="n"/>
-      <c r="Q202" s="7" t="n"/>
+      <c r="R202" s="7" t="n"/>
     </row>
     <row r="203" ht="16.05" customHeight="1" s="10">
       <c r="A203" s="8" t="n"/>
@@ -10974,11 +10985,11 @@
       <c r="N203" s="8" t="n"/>
       <c r="O203" s="8" t="n"/>
       <c r="P203" s="8" t="n"/>
-      <c r="Q203" s="8" t="n"/>
+      <c r="R203" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
